--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE241"/>
+  <dimension ref="A1:AE242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24278-2023</t>
+          <t>A 8315-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45079</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1575,9 +1575,122 @@
         <v>5</v>
       </c>
       <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Småjungfrukam
+Spillkråka
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 24278-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
@@ -1586,149 +1699,36 @@
 Trana</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8315-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Småjungfrukam
-Spillkråka
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2787-2024</t>
+          <t>A 30603-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45314</v>
+        <v>46210</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1898,21 +1898,133 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Kungsfiskare
+Ägretthäger
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2787-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45314</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Nordfladdermus
@@ -1920,144 +2032,32 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 30603-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Kungsfiskare
-Ägretthäger
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
         <v/>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         <v>45729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7616-2024</t>
+          <t>A 30645-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45348</v>
+        <v>44763</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,22 +2205,22 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2229,10 +2229,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2241,148 +2241,148 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 7616-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Kösa
 Åkerkulla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30645-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44763</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8329-2026</t>
+          <t>A 2942-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2894,146 +2894,146 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Skogsbräsma
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8329-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Grönsångare
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 2942-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45315</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsbräsma
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
         <v>46252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>44504</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44860</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44690</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45231</v>
+        <v>44741</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3615,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3627,10 +3627,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3643,42 +3643,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3692,10 +3692,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45322</v>
+        <v>45174</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3720,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -3748,42 +3748,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54753-2022</t>
+          <t>A 48926-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44883</v>
+        <v>45594</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3813,20 +3813,20 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>10.8</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -3837,10 +3837,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3849,39 +3849,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
         <v>45922</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 54753-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45005</v>
+        <v>44883</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4059,46 +4059,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 61007-2024</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4108,14 +4108,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45645</v>
+        <v>45322</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4127,28 +4127,23 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4160,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4169,46 +4164,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 61007-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4218,14 +4213,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45098</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4237,23 +4232,28 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>10.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4265,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4278,42 +4278,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 18348-2022</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44685</v>
+        <v>46255</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4342,13 +4342,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4384,46 +4379,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Klotullört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4437,10 +4432,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44741</v>
+        <v>45098</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4453,7 +4448,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.4</v>
+        <v>10.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4465,10 +4460,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4489,46 +4484,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 18348-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4542,10 +4537,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45174</v>
+        <v>44685</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4557,12 +4552,17 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4582,10 +4582,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4598,42 +4598,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Klotullört</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46255</v>
+        <v>45005</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4663,13 +4663,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4703,42 +4703,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22569-2024</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45447</v>
+        <v>45231</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -4804,50 +4804,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 22569-2024 artfynd.xlsx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 22569-2024 karta.png", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 22569-2024 georefererad karta.tif", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 22569-2024 FSC-klagomål.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 22569-2024 FSC-klagomål mail.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 22569-2024 tillsynsbegäran.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 22569-2024 tillsynsbegäran mail.docx", "A 22569-2024")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 22569-2024 prioriterade fågelarter.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48926-2024</t>
+          <t>A 22569-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4861,10 +4857,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45594</v>
+        <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4877,10 +4873,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -4889,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -4901,10 +4897,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4917,42 +4913,46 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 22569-2024 artfynd.xlsx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 22569-2024 karta.png", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 22569-2024 georefererad karta.tif", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 22569-2024 FSC-klagomål.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 22569-2024 FSC-klagomål mail.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 22569-2024 tillsynsbegäran.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 22569-2024 tillsynsbegäran mail.docx", "A 22569-2024")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 22569-2024 prioriterade fågelarter.docx", "A 22569-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44686</v>
+        <v>44504</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>20.3</v>
+        <v>37.2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5006,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5018,46 +5018,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44504</v>
+        <v>44858</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>37.2</v>
+        <v>15.5</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5123,46 +5123,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>44686</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5192,20 +5192,20 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
         <v>45688</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45729</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44460</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44461</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44599</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45698</v>
+        <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6239,7 +6239,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6249,14 +6249,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45236</v>
+        <v>44621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6326,10 +6326,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44734</v>
+        <v>45532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6341,13 +6341,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6400,14 +6395,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45405</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44888</v>
+        <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6493,7 +6488,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6536,7 +6531,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6550,10 +6545,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44874</v>
+        <v>45159</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6566,7 +6561,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45342</v>
+        <v>45751</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6639,7 +6634,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6682,7 +6677,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6692,14 +6687,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44908</v>
+        <v>45113</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6711,13 +6706,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6760,7 +6750,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6774,10 +6764,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45037</v>
+        <v>45471</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6790,7 +6780,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6833,7 +6823,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6847,10 +6837,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44838</v>
+        <v>44848</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6863,7 +6853,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6906,7 +6896,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6920,10 +6910,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44890</v>
+        <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6936,7 +6926,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6979,7 +6969,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6993,10 +6983,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45398</v>
+        <v>45477</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7009,7 +6999,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.1</v>
+        <v>0.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7052,7 +7042,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7066,10 +7056,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45748</v>
+        <v>45594</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7082,7 +7072,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3.6</v>
+        <v>6.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7125,7 +7115,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7139,10 +7129,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45477</v>
+        <v>45594</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7155,7 +7145,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.5</v>
+        <v>28.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7198,7 +7188,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7212,10 +7202,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45477</v>
+        <v>45608</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7228,7 +7218,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>12.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7271,7 +7261,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 51131-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7285,10 +7275,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45323</v>
+        <v>44461</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7301,7 +7291,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7344,7 +7334,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7358,10 +7348,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44848</v>
+        <v>45887</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7374,7 +7364,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7417,7 +7407,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7427,14 +7417,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44838</v>
+        <v>44911</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7447,7 +7437,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7490,7 +7480,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7500,14 +7490,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44838</v>
+        <v>44915</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7563,7 +7553,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7577,10 +7567,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45113</v>
+        <v>45804</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7593,7 +7583,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7636,7 +7626,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7650,10 +7640,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44879</v>
+        <v>45770</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7666,7 +7656,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7709,7 +7699,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7719,14 +7709,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45113</v>
+        <v>45945</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7739,7 +7729,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7782,7 +7772,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7796,10 +7786,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45539</v>
+        <v>45477</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7812,7 +7802,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7855,7 +7845,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7865,14 +7855,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45741</v>
+        <v>45978</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7885,7 +7875,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.7</v>
+        <v>4.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7928,7 +7918,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7942,10 +7932,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45574</v>
+        <v>46023</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7958,7 +7948,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8001,7 +7991,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8015,10 +8005,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44896</v>
+        <v>46023</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8031,7 +8021,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8074,7 +8064,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8088,10 +8078,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45709</v>
+        <v>45947</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8104,7 +8094,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8147,7 +8137,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8157,14 +8147,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45824</v>
+        <v>45001</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8177,7 +8167,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8227,7 @@
         <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8293,7 +8283,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8303,14 +8293,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44970</v>
+        <v>45894</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8323,7 +8313,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45894</v>
+        <v>45372</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8396,7 +8386,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8453,10 +8443,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45820</v>
+        <v>46041</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8469,7 +8459,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8512,7 +8502,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8526,10 +8516,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45583</v>
+        <v>46038</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8542,7 +8532,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.9</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8585,7 +8575,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8599,10 +8589,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44672</v>
+        <v>45646</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8615,7 +8605,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8658,7 +8648,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8672,10 +8662,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45807</v>
+        <v>45831</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8688,7 +8678,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8731,7 +8721,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8745,10 +8735,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45807</v>
+        <v>45709</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8761,7 +8751,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8804,7 +8794,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8818,10 +8808,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44981</v>
+        <v>45919</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8834,7 +8824,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8877,7 +8867,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8891,10 +8881,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44852</v>
+        <v>45824</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8907,7 +8897,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>12.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8950,7 +8940,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8964,10 +8954,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45315</v>
+        <v>45820</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8980,7 +8970,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9023,7 +9013,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 17723-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9037,10 +9027,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46064</v>
+        <v>45037</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9053,7 +9043,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9096,7 +9086,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9106,14 +9096,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45005</v>
+        <v>46064</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9126,7 +9116,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9169,7 +9159,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9183,10 +9173,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45831</v>
+        <v>45807</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9199,7 +9189,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9242,7 +9232,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9256,10 +9246,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45919</v>
+        <v>45807</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9315,7 +9305,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9329,10 +9319,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45012</v>
+        <v>45664</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9345,7 +9335,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9388,7 +9378,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9398,14 +9388,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45001</v>
+        <v>44672</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9418,7 +9408,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9461,7 +9451,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9475,10 +9465,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45987</v>
+        <v>45190</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9491,7 +9481,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9534,7 +9524,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9548,10 +9538,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45575</v>
+        <v>45323</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9564,7 +9554,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9607,7 +9597,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9621,10 +9611,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45940</v>
+        <v>45167</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9637,7 +9627,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9680,7 +9670,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9694,10 +9684,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45755</v>
+        <v>46064</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9710,7 +9700,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9753,7 +9743,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9767,10 +9757,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45971</v>
+        <v>45940</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9783,7 +9773,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9826,7 +9816,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9840,10 +9830,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46128</v>
+        <v>45987</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9856,7 +9846,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9899,7 +9889,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9913,10 +9903,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>44596</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9929,7 +9919,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9972,7 +9962,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9986,10 +9976,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45974</v>
+        <v>45005</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10002,7 +9992,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10045,7 +10035,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10055,14 +10045,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46121</v>
+        <v>45012</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10075,7 +10065,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10118,7 +10108,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10132,10 +10122,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45982</v>
+        <v>45093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10148,7 +10138,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10198,7 @@
         <v>44838</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10281,7 +10271,7 @@
         <v>44838</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10337,7 +10327,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10351,10 +10341,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46064</v>
+        <v>44741</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10367,7 +10357,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10410,7 +10400,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10420,14 +10410,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44515</v>
+        <v>45273</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10440,7 +10430,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10483,7 +10473,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10497,10 +10487,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45700</v>
+        <v>45672</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10513,7 +10503,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10556,7 +10546,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10566,14 +10556,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45406</v>
+        <v>46128</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10586,7 +10576,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10629,7 +10619,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10639,14 +10629,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44593</v>
+        <v>46121</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10659,7 +10649,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10702,7 +10692,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10716,10 +10706,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46000</v>
+        <v>45971</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10732,7 +10722,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10775,7 +10765,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10789,10 +10779,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46000</v>
+        <v>45061</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10804,8 +10794,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10848,7 +10843,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10862,10 +10857,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45315</v>
+        <v>46064</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10878,7 +10873,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>5.4</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10921,7 +10916,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10935,10 +10930,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45093</v>
+        <v>45477</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10951,7 +10946,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10994,7 +10989,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11008,10 +11003,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45110</v>
+        <v>45974</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11024,7 +11019,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11067,7 +11062,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11081,10 +11076,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45887</v>
+        <v>45974</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11097,7 +11092,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11140,7 +11135,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11154,10 +11149,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45751</v>
+        <v>45405</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11170,7 +11165,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11213,7 +11208,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11227,10 +11222,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45770</v>
+        <v>45477</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11243,7 +11238,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11286,7 +11281,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11300,10 +11295,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45051</v>
+        <v>45982</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11315,13 +11310,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11364,7 +11354,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11378,10 +11368,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45945</v>
+        <v>45342</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11394,7 +11384,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11437,7 +11427,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11447,14 +11437,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45978</v>
+        <v>45698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11467,7 +11457,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11510,7 +11500,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11524,10 +11514,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46023</v>
+        <v>46000</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11583,7 +11573,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11597,10 +11587,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46023</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11613,7 +11603,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11656,7 +11646,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11670,10 +11660,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45947</v>
+        <v>45318</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11686,7 +11676,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11729,7 +11719,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11743,10 +11733,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45231</v>
+        <v>45093</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11759,7 +11749,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11802,7 +11792,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11816,10 +11806,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46038</v>
+        <v>44981</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11832,7 +11822,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11875,7 +11865,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11889,10 +11879,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45664</v>
+        <v>45315</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11905,7 +11895,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11948,7 +11938,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11962,10 +11952,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46041</v>
+        <v>46146</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11978,7 +11968,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12021,7 +12011,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12035,10 +12025,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45343</v>
+        <v>45057</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12051,7 +12041,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12094,7 +12084,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12108,10 +12098,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45343</v>
+        <v>44838</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12124,7 +12114,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12167,7 +12157,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12181,10 +12171,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44608</v>
+        <v>44852</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12197,7 +12187,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3</v>
+        <v>12.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12240,7 +12230,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12254,10 +12244,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45477</v>
+        <v>44593</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12270,7 +12260,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12313,7 +12303,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12327,10 +12317,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45318</v>
+        <v>45775</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12343,7 +12333,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12386,7 +12376,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12400,10 +12390,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45450</v>
+        <v>46160</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12416,7 +12406,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12459,7 +12449,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12469,14 +12459,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46064</v>
+        <v>46160</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12489,7 +12479,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12532,7 +12522,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12542,14 +12532,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44621</v>
+        <v>45618</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12562,7 +12552,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12605,7 +12595,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12619,10 +12609,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45175</v>
+        <v>45947</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12635,7 +12625,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12678,7 +12668,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12692,10 +12682,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45167</v>
+        <v>45945</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12708,7 +12698,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12751,7 +12741,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12765,10 +12755,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45618</v>
+        <v>46197</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12781,7 +12771,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12824,7 +12814,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12838,10 +12828,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44585</v>
+        <v>46198</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12854,7 +12844,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12897,7 +12887,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12911,10 +12901,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45539</v>
+        <v>45575</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12927,7 +12917,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12970,7 +12960,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12984,10 +12974,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46146</v>
+        <v>46205</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13000,7 +12990,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13043,7 +13033,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13057,10 +13047,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45001</v>
+        <v>45231</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13073,7 +13063,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13116,7 +13106,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13130,10 +13120,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44596</v>
+        <v>46209</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13146,7 +13136,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13189,7 +13179,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13203,10 +13193,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45159</v>
+        <v>45240</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13219,7 +13209,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13262,7 +13252,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13276,10 +13266,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46160</v>
+        <v>46255</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13292,7 +13282,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13335,7 +13325,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13349,10 +13339,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46160</v>
+        <v>46255</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13365,7 +13355,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13408,7 +13398,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13422,10 +13412,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45775</v>
+        <v>44573</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13438,7 +13428,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13481,7 +13471,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13495,10 +13485,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44594</v>
+        <v>46258</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13511,7 +13501,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13554,7 +13544,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13568,10 +13558,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45728</v>
+        <v>46258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13584,7 +13574,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13627,7 +13617,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13641,10 +13631,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45574</v>
+        <v>45175</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13657,7 +13647,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13700,7 +13690,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13714,10 +13704,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44838</v>
+        <v>46177</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13730,7 +13720,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13773,7 +13763,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13787,10 +13777,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44685</v>
+        <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13802,13 +13792,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13851,7 +13836,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13865,10 +13850,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45154</v>
+        <v>45322</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13881,7 +13866,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13924,7 +13909,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13938,10 +13923,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45947</v>
+        <v>46265</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13954,7 +13939,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13997,7 +13982,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14011,10 +13996,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44672</v>
+        <v>44879</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14027,7 +14012,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.6</v>
+        <v>0.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14070,7 +14055,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14084,10 +14069,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45945</v>
+        <v>46251</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14100,7 +14085,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14143,7 +14128,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14153,14 +14138,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44741</v>
+        <v>46268</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14173,7 +14158,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14216,7 +14201,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14230,10 +14215,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44573</v>
+        <v>45231</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14246,7 +14231,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14289,7 +14274,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14303,10 +14288,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45273</v>
+        <v>45574</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14319,7 +14304,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14362,7 +14347,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14376,10 +14361,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45191</v>
+        <v>44734</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14391,8 +14376,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>3.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14435,7 +14425,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14449,10 +14439,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45190</v>
+        <v>45748</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14465,7 +14455,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14508,7 +14498,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14522,10 +14512,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45534</v>
+        <v>46273</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14538,7 +14528,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14581,7 +14571,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14595,10 +14585,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46197</v>
+        <v>46178</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14611,7 +14601,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14654,7 +14644,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14668,10 +14658,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45261</v>
+        <v>46196</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14684,7 +14674,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14727,7 +14717,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14741,10 +14731,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45005</v>
+        <v>46191</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14757,7 +14747,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14800,7 +14790,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14810,14 +14800,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46198</v>
+        <v>44970</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14830,7 +14820,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14873,7 +14863,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14887,10 +14877,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44860</v>
+        <v>44685</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14902,8 +14892,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14946,7 +14941,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14960,10 +14955,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46205</v>
+        <v>45534</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14976,7 +14971,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15019,7 +15014,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15033,10 +15028,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45061</v>
+        <v>44838</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15048,13 +15043,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15097,7 +15087,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15111,10 +15101,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45240</v>
+        <v>46184</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15127,7 +15117,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15170,7 +15160,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15184,10 +15174,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46209</v>
+        <v>46279</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15200,7 +15190,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15243,7 +15233,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15257,10 +15247,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45231</v>
+        <v>44896</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15273,7 +15263,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15316,7 +15306,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15330,10 +15320,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44734</v>
+        <v>46136</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15345,13 +15335,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>9.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15394,7 +15379,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15404,14 +15389,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46255</v>
+        <v>44515</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15424,7 +15409,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15467,7 +15452,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15481,10 +15466,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45322</v>
+        <v>45741</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15497,7 +15482,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15540,7 +15525,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15554,10 +15539,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46258</v>
+        <v>44734</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15569,8 +15554,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15613,7 +15603,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15627,10 +15617,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46255</v>
+        <v>45338</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15643,7 +15633,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15686,7 +15676,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15700,10 +15690,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45526</v>
+        <v>44888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15716,7 +15706,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15759,7 +15749,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15773,10 +15763,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46177</v>
+        <v>44672</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15789,7 +15779,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15832,7 +15822,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15846,10 +15836,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45338</v>
+        <v>45343</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15905,7 +15895,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15919,10 +15909,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46258</v>
+        <v>45343</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15935,7 +15925,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15978,7 +15968,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15992,10 +15982,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45057</v>
+        <v>45315</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16008,7 +15998,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.7</v>
+        <v>5.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16051,7 +16041,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16065,10 +16055,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44984</v>
+        <v>45398</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16081,7 +16071,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.4</v>
+        <v>4.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16124,7 +16114,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16138,10 +16128,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46265</v>
+        <v>45005</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16154,7 +16144,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16197,7 +16187,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16211,10 +16201,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45532</v>
+        <v>45273</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16227,7 +16217,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16270,7 +16260,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16280,14 +16270,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46268</v>
+        <v>44594</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16300,7 +16290,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16343,7 +16333,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16357,10 +16347,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45273</v>
+        <v>44874</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16373,7 +16363,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16416,7 +16406,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16430,10 +16420,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45216</v>
+        <v>44908</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16443,6 +16433,11 @@
       <c r="G196" t="inlineStr">
         <is>
           <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -16489,7 +16484,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16503,10 +16498,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45216</v>
+        <v>45755</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16519,7 +16514,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16562,7 +16557,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16576,10 +16571,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46251</v>
+        <v>44838</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16592,7 +16587,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16635,7 +16630,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16649,10 +16644,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45372</v>
+        <v>44838</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16665,7 +16660,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16708,7 +16703,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16722,10 +16717,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46178</v>
+        <v>45191</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16738,7 +16733,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16781,7 +16776,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16795,10 +16790,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46273</v>
+        <v>45154</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16811,7 +16806,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16854,7 +16849,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16868,10 +16863,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45041</v>
+        <v>44860</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16884,7 +16879,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16927,7 +16922,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16941,10 +16936,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46196</v>
+        <v>45113</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16957,7 +16952,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17000,7 +16995,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17014,10 +17009,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46184</v>
+        <v>45216</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17025,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17073,7 +17068,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17087,10 +17082,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45327</v>
+        <v>45216</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17103,7 +17098,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17146,7 +17141,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17160,10 +17155,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45093</v>
+        <v>45450</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17176,7 +17171,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17219,7 +17214,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17233,10 +17228,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46191</v>
+        <v>45477</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17249,7 +17244,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17292,7 +17287,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17306,10 +17301,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46136</v>
+        <v>45526</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17322,7 +17317,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17365,7 +17360,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17379,10 +17374,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45685</v>
+        <v>45001</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17395,7 +17390,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17438,7 +17433,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17452,10 +17447,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45646</v>
+        <v>45539</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17468,7 +17463,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17511,7 +17506,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17525,10 +17520,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45672</v>
+        <v>45051</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17540,8 +17535,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17584,7 +17584,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17598,10 +17598,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45477</v>
+        <v>45685</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17671,10 +17671,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>44551</v>
+        <v>45700</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17686,13 +17686,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17735,7 +17730,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17749,10 +17744,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45568</v>
+        <v>45261</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17765,7 +17760,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17808,7 +17803,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17822,10 +17817,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45715</v>
+        <v>45041</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17838,7 +17833,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>4.5</v>
+        <v>0.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17881,7 +17876,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17895,10 +17890,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45471</v>
+        <v>45327</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17911,7 +17906,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17954,7 +17949,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17968,10 +17963,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45791</v>
+        <v>44890</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17984,7 +17979,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18027,7 +18022,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18037,14 +18032,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45645</v>
+        <v>44984</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18056,13 +18051,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18105,7 +18095,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18119,10 +18109,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45728</v>
+        <v>44608</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18135,7 +18125,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18178,7 +18168,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18192,10 +18182,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45600</v>
+        <v>45574</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18208,7 +18198,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18251,7 +18241,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18265,10 +18255,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45594</v>
+        <v>45728</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18281,7 +18271,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>6.3</v>
+        <v>3.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18324,7 +18314,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18338,10 +18328,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45608</v>
+        <v>45236</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18354,7 +18344,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>12.3</v>
+        <v>1.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18397,7 +18387,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18411,10 +18401,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45594</v>
+        <v>45568</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18427,7 +18417,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>28.4</v>
+        <v>2.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18470,7 +18460,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18480,14 +18470,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44911</v>
+        <v>44551</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18499,8 +18489,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18543,7 +18538,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18553,14 +18548,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44915</v>
+        <v>45600</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18573,7 +18568,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18616,7 +18611,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 51131-2021</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18630,10 +18625,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44461</v>
+        <v>45715</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18646,7 +18641,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18689,7 +18684,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18703,10 +18698,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45804</v>
+        <v>45728</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18719,7 +18714,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18762,7 +18757,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18776,10 +18771,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45477</v>
+        <v>45791</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18792,7 +18787,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18835,24 +18830,24 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>S 2442-2022</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44691</v>
+        <v>45645</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18864,8 +18859,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>12.4</v>
+        <v>2.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18908,7 +18908,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>S 4383-2023</t>
+          <t>S 2442-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18922,10 +18922,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45265</v>
+        <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18981,7 +18981,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S 8937-2021</t>
+          <t>S 4383-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18995,10 +18995,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44509</v>
+        <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>35.9</v>
+        <v>18.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S 3693-2023</t>
+          <t>S 8937-2021</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19068,10 +19068,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45218</v>
+        <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>35.7</v>
+        <v>35.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19127,7 +19127,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 221-2025</t>
+          <t>S 3693-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19141,10 +19141,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45680</v>
+        <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>13.8</v>
+        <v>35.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19200,7 +19200,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 3468-2024</t>
+          <t>S 221-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19214,10 +19214,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45539</v>
+        <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>10.2</v>
+        <v>13.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19273,7 +19273,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 2441-2023</t>
+          <t>S 3468-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45114</v>
+        <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19346,7 +19346,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 3794-2024</t>
+          <t>S 2441-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19356,14 +19356,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45558</v>
+        <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19375,13 +19375,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19424,7 +19419,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 792-2025</t>
+          <t>S 3794-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19434,14 +19429,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45729</v>
+        <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19453,8 +19448,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>12.9</v>
+        <v>3.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19497,7 +19497,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 310-2025</t>
+          <t>S 792-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19511,10 +19511,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45688</v>
+        <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>16</v>
+        <v>12.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19570,7 +19570,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 1522-2025</t>
+          <t>S 310-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19584,10 +19584,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45791</v>
+        <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>30.6</v>
+        <v>16</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19643,148 +19643,221 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
+          <t>S 1522-2025</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="n">
+        <v>45791</v>
+      </c>
+      <c r="E240" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241" ht="15" customHeight="1">
+      <c r="A241" t="inlineStr">
+        <is>
           <t>S 1063-2026</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
+      <c r="C241" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D240" s="1" t="n">
+      <c r="D241" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="E240" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I240" t="n">
+      <c r="E241" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
         <v>23.5</v>
       </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>0</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" s="2" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>0</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>S 1492-2026</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D241" s="1" t="n">
+      <c r="D242" s="1" t="n">
         <v>46162</v>
       </c>
-      <c r="E241" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I241" t="n">
+      <c r="E242" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="P241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" t="n">
-        <v>0</v>
-      </c>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="inlineStr"/>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
+      <c r="V242" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE242"/>
+  <dimension ref="A1:AE243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8315-2026</t>
+          <t>A 42692-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46064</v>
+        <v>44832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,6 +1578,115 @@
         <v>4</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril
+Loppstarr
+Ängsstarr
+Bandpraktmossa
+Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42692-2022 artfynd.xlsx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42692-2022 karta.png", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42692-2022 georefererad karta.tif", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42692-2022 FSC-klagomål.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42692-2022 FSC-klagomål mail.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42692-2022 tillsynsbegäran.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42692-2022 tillsynsbegäran mail.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 8315-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Småjungfrukam
@@ -1586,111 +1695,111 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 24278-2023</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>45079</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>5</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>5</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
@@ -1699,152 +1808,43 @@
 Trana</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AE11">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 42692-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril
-Loppstarr
-Ängsstarr
-Bandpraktmossa
-Sankt pers nycklar</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42692-2022 artfynd.xlsx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42692-2022 karta.png", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42692-2022 georefererad karta.tif", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42692-2022 FSC-klagomål.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42692-2022 FSC-klagomål mail.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42692-2022 tillsynsbegäran.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42692-2022 tillsynsbegäran mail.docx", "A 42692-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30603-2026</t>
+          <t>A 2787-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46210</v>
+        <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1898,21 +1898,129 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Nordfladdermus
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 30603-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Kungsfiskare
@@ -1920,151 +2028,43 @@
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2787-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45314</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Nordfladdermus
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12111-2025</t>
+          <t>A 30645-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45729</v>
+        <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,259 +2130,259 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 7616-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Kösa
+Åkerkulla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 12111-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45729</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tofsvipa
 Tornseglare
 Gröngöling</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 30645-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44763</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 7616-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45348</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Kösa
-Åkerkulla
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2942-2024</t>
+          <t>A 8329-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45315</v>
+        <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,31 +2854,31 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.2</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2894,146 +2894,146 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Grönsångare
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 2942-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45315</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Skogsbräsma
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 8329-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
         <v/>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
         <v>46252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>44504</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44860</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44690</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 18348-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44741</v>
+        <v>44685</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,11 +3602,16 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3615,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3627,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3643,42 +3648,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Klotullört</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3692,10 +3697,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45174</v>
+        <v>45231</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3708,7 +3713,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3720,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3732,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3748,42 +3753,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 48926-2024</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3797,10 +3802,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45594</v>
+        <v>45322</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3813,7 +3818,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10.8</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3825,10 +3830,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3849,46 +3854,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 54753-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3902,10 +3907,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45922</v>
+        <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3918,10 +3923,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3930,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -3942,10 +3947,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3958,42 +3963,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54753-2022</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4007,10 +4012,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44883</v>
+        <v>45922</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4023,20 +4028,20 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -4047,10 +4052,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4063,42 +4068,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4112,10 +4117,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45322</v>
+        <v>45005</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,13 +4133,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4143,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4152,10 +4157,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4164,39 +4169,39 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
@@ -4220,7 +4225,7 @@
         <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4313,7 +4318,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4327,10 +4332,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46255</v>
+        <v>44741</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4343,20 +4348,20 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -4367,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4379,46 +4384,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4432,10 +4437,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45098</v>
+        <v>45174</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4448,7 +4453,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4460,10 +4465,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4484,46 +4489,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18348-2022</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4537,10 +4542,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44685</v>
+        <v>46255</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4552,13 +4557,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4594,46 +4594,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Klotullört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45005</v>
+        <v>45098</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4663,23 +4663,23 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
@@ -4687,10 +4687,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4703,42 +4703,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 22569-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4752,10 +4752,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45231</v>
+        <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -4804,46 +4804,50 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 22569-2024 artfynd.xlsx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 22569-2024 karta.png", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 22569-2024 georefererad karta.tif", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 22569-2024 FSC-klagomål.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 22569-2024 FSC-klagomål mail.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 22569-2024 tillsynsbegäran.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 22569-2024 tillsynsbegäran mail.docx", "A 22569-2024")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 22569-2024 prioriterade fågelarter.docx", "A 22569-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22569-2024</t>
+          <t>A 48926-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4857,10 +4861,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45447</v>
+        <v>45594</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4873,20 +4877,20 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>10.8</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -4897,10 +4901,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4913,46 +4917,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 22569-2024 artfynd.xlsx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 22569-2024 karta.png", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 22569-2024 georefererad karta.tif", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 22569-2024 FSC-klagomål.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 22569-2024 FSC-klagomål mail.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 22569-2024 tillsynsbegäran.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 22569-2024 tillsynsbegäran mail.docx", "A 22569-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 22569-2024 prioriterade fågelarter.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44504</v>
+        <v>44686</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4982,20 +4982,20 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>37.2</v>
+        <v>20.3</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
@@ -5006,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5018,46 +5018,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44858</v>
+        <v>44504</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>15.5</v>
+        <v>37.2</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5123,46 +5123,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44686</v>
+        <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5192,10 +5192,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>20.3</v>
+        <v>15.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
         <v>45688</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45729</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44460</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44461</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5726-2022</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44596</v>
+        <v>45405</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 65203-2021</t>
+          <t>A 6042-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6030,14 +6030,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44515</v>
+        <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6042-2022</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44599</v>
+        <v>45236</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44585</v>
+        <v>44734</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6195,8 +6195,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6239,7 +6244,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6249,14 +6254,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44621</v>
+        <v>45154</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6269,7 +6274,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6312,7 +6317,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 5726-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6326,10 +6331,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45532</v>
+        <v>44596</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6342,7 +6347,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6385,7 +6390,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6395,14 +6400,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45406</v>
+        <v>44874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6415,7 +6420,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6458,7 +6463,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6472,10 +6477,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45110</v>
+        <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6487,8 +6492,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6531,7 +6541,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6545,10 +6555,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45159</v>
+        <v>45342</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6561,7 +6571,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6604,7 +6614,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6618,10 +6628,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45751</v>
+        <v>44888</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6634,7 +6644,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6677,7 +6687,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 17723-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6687,14 +6697,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45113</v>
+        <v>45037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6707,7 +6717,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>7.8</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6750,7 +6760,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6764,10 +6774,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45471</v>
+        <v>44672</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6780,7 +6790,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6823,7 +6833,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 65203-2021</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6833,14 +6843,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44848</v>
+        <v>44515</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6853,7 +6863,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6896,7 +6906,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6910,10 +6920,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45583</v>
+        <v>44838</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6926,7 +6936,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6969,7 +6979,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6983,10 +6993,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45477</v>
+        <v>44890</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6999,7 +7009,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.3</v>
+        <v>7.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7042,7 +7052,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7056,10 +7066,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45594</v>
+        <v>45398</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7072,7 +7082,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7115,7 +7125,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7129,10 +7139,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45594</v>
+        <v>45698</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7145,7 +7155,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>28.4</v>
+        <v>2.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7188,7 +7198,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7202,10 +7212,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45608</v>
+        <v>45748</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7218,7 +7228,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>12.3</v>
+        <v>3.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7261,7 +7271,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51131-2021</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7275,10 +7285,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44461</v>
+        <v>44741</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7291,7 +7301,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7334,7 +7344,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7348,10 +7358,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45887</v>
+        <v>45477</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7364,7 +7374,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7407,7 +7417,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7417,14 +7427,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44911</v>
+        <v>45477</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7437,7 +7447,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7480,7 +7490,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7490,14 +7500,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44915</v>
+        <v>45323</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7510,7 +7520,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7553,7 +7563,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7567,10 +7577,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45804</v>
+        <v>45987</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7583,7 +7593,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7626,7 +7636,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7640,10 +7650,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45770</v>
+        <v>44848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7656,7 +7666,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7699,7 +7709,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7713,10 +7723,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45945</v>
+        <v>44838</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7729,7 +7739,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7772,7 +7782,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7786,10 +7796,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45477</v>
+        <v>44838</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7802,7 +7812,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7845,7 +7855,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7855,14 +7865,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45978</v>
+        <v>44573</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7875,7 +7885,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7918,7 +7928,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7932,10 +7942,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46023</v>
+        <v>45113</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7948,7 +7958,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7991,7 +8001,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8005,10 +8015,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46023</v>
+        <v>45273</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8021,7 +8031,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8064,7 +8074,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8078,10 +8088,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45947</v>
+        <v>45894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8094,7 +8104,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8137,7 +8147,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8147,14 +8157,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45001</v>
+        <v>45894</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8167,7 +8177,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8210,7 +8220,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8224,10 +8234,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45894</v>
+        <v>44879</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8240,7 +8250,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8283,7 +8293,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8293,14 +8303,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45894</v>
+        <v>45113</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8313,7 +8323,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8356,7 +8366,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8370,10 +8380,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45372</v>
+        <v>45539</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8386,7 +8396,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8429,7 +8439,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8443,10 +8453,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46041</v>
+        <v>45831</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8459,7 +8469,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8502,7 +8512,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8516,10 +8526,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46038</v>
+        <v>45741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8532,7 +8542,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8575,7 +8585,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8589,10 +8599,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45646</v>
+        <v>45191</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8605,7 +8615,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8648,7 +8658,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8662,10 +8672,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45831</v>
+        <v>45190</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8678,7 +8688,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8721,7 +8731,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8735,10 +8745,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45709</v>
+        <v>46128</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8751,7 +8761,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8811,7 +8821,7 @@
         <v>45919</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8867,7 +8877,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8881,10 +8891,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45824</v>
+        <v>45574</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8897,7 +8907,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8940,7 +8950,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8950,14 +8960,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45820</v>
+        <v>46121</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8970,7 +8980,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9013,7 +9023,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9027,10 +9037,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45037</v>
+        <v>44896</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9043,7 +9053,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9086,7 +9096,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9096,14 +9106,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46064</v>
+        <v>45534</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9116,7 +9126,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9159,7 +9169,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9173,10 +9183,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45807</v>
+        <v>46064</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9189,7 +9199,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9232,7 +9242,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9246,10 +9256,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45807</v>
+        <v>45261</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9262,7 +9272,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9305,7 +9315,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9319,10 +9329,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45664</v>
+        <v>45005</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9335,7 +9345,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9378,7 +9388,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9392,10 +9402,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44672</v>
+        <v>45940</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9408,7 +9418,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9451,7 +9461,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9461,14 +9471,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45190</v>
+        <v>44970</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9481,7 +9491,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9524,7 +9534,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9538,10 +9548,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45323</v>
+        <v>45583</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9554,7 +9564,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9597,7 +9607,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9611,10 +9621,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45167</v>
+        <v>44672</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9627,7 +9637,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9670,7 +9680,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9684,10 +9694,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46064</v>
+        <v>44981</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9700,7 +9710,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9743,7 +9753,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9757,10 +9767,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45940</v>
+        <v>44852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9773,7 +9783,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>12.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9816,7 +9826,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9830,10 +9840,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45987</v>
+        <v>45315</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9846,7 +9856,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9889,7 +9899,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9903,10 +9913,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44596</v>
+        <v>45005</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9919,7 +9929,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9962,7 +9972,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9976,10 +9986,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45005</v>
+        <v>45971</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9992,7 +10002,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10035,7 +10045,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10049,10 +10059,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45012</v>
+        <v>45974</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10065,7 +10075,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10108,7 +10118,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10122,10 +10132,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45093</v>
+        <v>45974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10138,7 +10148,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10181,7 +10191,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10195,10 +10205,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44838</v>
+        <v>45012</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10211,7 +10221,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10254,7 +10264,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10264,14 +10274,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44838</v>
+        <v>45001</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10284,7 +10294,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10327,7 +10337,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10341,10 +10351,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44741</v>
+        <v>45575</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10357,7 +10367,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.3</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10400,7 +10410,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10414,10 +10424,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45273</v>
+        <v>45982</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10430,7 +10440,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10473,7 +10483,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10487,10 +10497,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45672</v>
+        <v>44860</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10503,7 +10513,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10546,7 +10556,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10560,10 +10570,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46128</v>
+        <v>46146</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10576,7 +10586,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10619,7 +10629,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10629,14 +10639,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46121</v>
+        <v>46000</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10649,7 +10659,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10692,7 +10702,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10706,10 +10716,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45971</v>
+        <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10722,7 +10732,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10765,7 +10775,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10779,10 +10789,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45061</v>
+        <v>45887</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10794,13 +10804,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10843,7 +10848,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10857,10 +10862,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46064</v>
+        <v>45770</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10873,7 +10878,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10916,7 +10921,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10930,10 +10935,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45477</v>
+        <v>46160</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10946,7 +10951,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10989,7 +10994,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11003,10 +11008,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45974</v>
+        <v>45755</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11019,7 +11024,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11062,7 +11067,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11076,10 +11081,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45974</v>
+        <v>46160</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11092,7 +11097,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11135,7 +11140,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11149,10 +11154,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45405</v>
+        <v>45945</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11165,7 +11170,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11208,7 +11213,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11222,10 +11227,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45477</v>
+        <v>45061</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11237,8 +11242,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11281,7 +11291,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11291,14 +11301,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45982</v>
+        <v>45978</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11311,7 +11321,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11354,7 +11364,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11368,10 +11378,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45342</v>
+        <v>46023</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11384,7 +11394,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11427,7 +11437,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11441,10 +11451,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45698</v>
+        <v>46023</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11457,7 +11467,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11500,7 +11510,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11514,10 +11524,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46000</v>
+        <v>45947</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11530,7 +11540,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11573,7 +11583,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11587,10 +11597,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45775</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11603,7 +11613,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11646,7 +11656,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11660,10 +11670,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45318</v>
+        <v>44838</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11676,7 +11686,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.5</v>
+        <v>0.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11719,7 +11729,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11733,10 +11743,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45093</v>
+        <v>44838</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11749,7 +11759,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11792,7 +11802,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11802,14 +11812,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44981</v>
+        <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11822,7 +11832,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11865,7 +11875,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11879,10 +11889,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45315</v>
+        <v>46038</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11895,7 +11905,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11938,7 +11948,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11952,10 +11962,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46146</v>
+        <v>45240</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11968,7 +11978,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12011,7 +12021,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12025,10 +12035,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45057</v>
+        <v>45700</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12041,7 +12051,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12084,7 +12094,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12098,10 +12108,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44838</v>
+        <v>46041</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12114,7 +12124,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12157,7 +12167,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12167,14 +12177,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44852</v>
+        <v>45406</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12187,7 +12197,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>12.3</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12247,7 +12257,7 @@
         <v>44593</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12303,7 +12313,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12317,10 +12327,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45775</v>
+        <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12333,7 +12343,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12376,7 +12386,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12390,10 +12400,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46160</v>
+        <v>45945</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12406,7 +12416,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12449,7 +12459,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12463,10 +12473,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46160</v>
+        <v>45315</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12479,7 +12489,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12522,7 +12532,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12536,10 +12546,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45618</v>
+        <v>45093</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12552,7 +12562,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12595,7 +12605,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12609,10 +12619,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45947</v>
+        <v>45110</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12625,7 +12635,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12668,7 +12678,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12682,10 +12692,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45945</v>
+        <v>45751</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12698,7 +12708,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12741,7 +12751,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12755,10 +12765,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46197</v>
+        <v>45051</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12770,8 +12780,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12814,7 +12829,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12824,14 +12839,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46198</v>
+        <v>46064</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12844,7 +12859,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12887,7 +12902,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12901,10 +12916,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45575</v>
+        <v>45231</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12917,7 +12932,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12960,7 +12975,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12974,10 +12989,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46205</v>
+        <v>46064</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12990,7 +13005,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13033,7 +13048,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13047,10 +13062,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45231</v>
+        <v>45664</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13063,7 +13078,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13106,7 +13121,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13120,10 +13135,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46209</v>
+        <v>44734</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13135,8 +13150,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13179,7 +13199,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13193,10 +13213,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45240</v>
+        <v>45322</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13252,7 +13272,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13266,10 +13286,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46255</v>
+        <v>45343</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13282,7 +13302,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13325,7 +13345,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13339,10 +13359,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46255</v>
+        <v>45343</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13355,7 +13375,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13398,7 +13418,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13412,10 +13432,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44573</v>
+        <v>45526</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13428,7 +13448,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.6</v>
+        <v>0.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13471,7 +13491,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13485,10 +13505,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46258</v>
+        <v>46197</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13501,7 +13521,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13544,7 +13564,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13558,10 +13578,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46258</v>
+        <v>44608</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13574,7 +13594,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13617,7 +13637,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13631,10 +13651,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45175</v>
+        <v>45477</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13647,7 +13667,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13690,7 +13710,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13704,10 +13724,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46177</v>
+        <v>45318</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13720,7 +13740,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13763,7 +13783,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13777,10 +13797,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45539</v>
+        <v>45450</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13793,7 +13813,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13836,7 +13856,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13850,10 +13870,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45322</v>
+        <v>45338</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13866,7 +13886,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13909,7 +13929,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13923,10 +13943,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46265</v>
+        <v>46198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13939,7 +13959,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13982,7 +14002,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13996,10 +14016,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44879</v>
+        <v>45057</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14012,7 +14032,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14055,7 +14075,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14065,14 +14085,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46251</v>
+        <v>44621</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14085,7 +14105,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14128,7 +14148,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14138,14 +14158,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46268</v>
+        <v>45175</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14158,7 +14178,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14201,7 +14221,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14215,10 +14235,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45231</v>
+        <v>45167</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14231,7 +14251,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14274,7 +14294,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14288,10 +14308,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45574</v>
+        <v>45618</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14304,7 +14324,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14347,7 +14367,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14361,10 +14381,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44734</v>
+        <v>44585</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14376,13 +14396,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>9.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14425,7 +14440,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14439,10 +14454,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45748</v>
+        <v>45539</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14455,7 +14470,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14498,7 +14513,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14512,10 +14527,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46273</v>
+        <v>46205</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14528,7 +14543,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14571,7 +14586,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14585,10 +14600,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46178</v>
+        <v>45001</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14601,7 +14616,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14644,7 +14659,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14658,10 +14673,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46196</v>
+        <v>44596</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14674,7 +14689,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14717,7 +14732,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14731,10 +14746,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46191</v>
+        <v>44984</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14747,7 +14762,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.5</v>
+        <v>0.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14790,7 +14805,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14800,14 +14815,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44970</v>
+        <v>46209</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14820,7 +14835,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14863,7 +14878,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14877,10 +14892,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44685</v>
+        <v>45159</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14892,13 +14907,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14941,7 +14951,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14955,10 +14965,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45534</v>
+        <v>45231</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14971,7 +14981,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15014,7 +15024,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15028,10 +15038,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44838</v>
+        <v>46255</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15044,7 +15054,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15087,7 +15097,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15101,10 +15111,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46184</v>
+        <v>46258</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15117,7 +15127,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15160,7 +15170,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15174,10 +15184,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46279</v>
+        <v>46255</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15190,7 +15200,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15233,7 +15243,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15247,10 +15257,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44896</v>
+        <v>45532</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15263,7 +15273,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15306,7 +15316,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15320,10 +15330,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46136</v>
+        <v>44594</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15336,7 +15346,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15379,7 +15389,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15389,14 +15399,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44515</v>
+        <v>46258</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15409,7 +15419,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15452,7 +15462,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15466,10 +15476,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45741</v>
+        <v>45728</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15482,7 +15492,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15525,7 +15535,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15539,10 +15549,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44734</v>
+        <v>45574</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15554,13 +15564,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15603,7 +15608,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15617,10 +15622,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45338</v>
+        <v>44838</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15633,7 +15638,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15676,7 +15681,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15690,10 +15695,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44888</v>
+        <v>44685</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15705,8 +15710,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15749,7 +15759,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15763,10 +15773,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44672</v>
+        <v>45273</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15779,7 +15789,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15822,7 +15832,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15836,10 +15846,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45343</v>
+        <v>45216</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15852,7 +15862,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15895,7 +15905,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15909,10 +15919,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45343</v>
+        <v>45216</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15925,7 +15935,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15968,7 +15978,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15982,10 +15992,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45315</v>
+        <v>46265</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15998,7 +16008,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16041,7 +16051,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16055,10 +16065,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45398</v>
+        <v>45372</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16071,7 +16081,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16114,7 +16124,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16124,14 +16134,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45005</v>
+        <v>46268</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16144,7 +16154,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16187,7 +16197,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16201,10 +16211,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45273</v>
+        <v>46251</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16217,7 +16227,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16260,7 +16270,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16274,10 +16284,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44594</v>
+        <v>46178</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16290,7 +16300,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16333,7 +16343,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16347,10 +16357,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44874</v>
+        <v>45041</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16363,7 +16373,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16406,7 +16416,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16420,10 +16430,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44908</v>
+        <v>46273</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16435,13 +16445,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16484,7 +16489,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16498,10 +16503,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45755</v>
+        <v>46196</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16514,7 +16519,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16557,7 +16562,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16571,10 +16576,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44838</v>
+        <v>45327</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16630,7 +16635,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16644,10 +16649,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44838</v>
+        <v>45093</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16660,7 +16665,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16703,7 +16708,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16717,10 +16722,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45191</v>
+        <v>46191</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16733,7 +16738,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16776,7 +16781,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16790,10 +16795,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45154</v>
+        <v>45685</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16806,7 +16811,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16849,7 +16854,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16863,10 +16868,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>44860</v>
+        <v>45646</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16879,7 +16884,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16922,7 +16927,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16936,10 +16941,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45113</v>
+        <v>45672</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16952,7 +16957,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16995,7 +17000,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17009,10 +17014,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45216</v>
+        <v>45477</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17025,7 +17030,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17068,7 +17073,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17082,10 +17087,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45216</v>
+        <v>46184</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17141,7 +17146,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17155,10 +17160,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45450</v>
+        <v>46177</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17171,7 +17176,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17214,7 +17219,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17228,10 +17233,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45477</v>
+        <v>46279</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17244,7 +17249,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17287,7 +17292,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17301,10 +17306,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45526</v>
+        <v>46136</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17317,7 +17322,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17360,7 +17365,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17374,10 +17379,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45001</v>
+        <v>46280</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17390,7 +17395,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17433,7 +17438,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17447,10 +17452,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45539</v>
+        <v>44551</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17462,8 +17467,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17506,7 +17516,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17520,10 +17530,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45051</v>
+        <v>45568</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17535,13 +17545,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17584,7 +17589,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17598,10 +17603,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45685</v>
+        <v>45715</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17614,7 +17619,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.3</v>
+        <v>4.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17657,7 +17662,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17671,10 +17676,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45700</v>
+        <v>45471</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17687,7 +17692,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17730,7 +17735,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17744,10 +17749,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45261</v>
+        <v>45791</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17760,7 +17765,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17803,7 +17808,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17813,14 +17818,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45041</v>
+        <v>45645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17832,8 +17837,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17876,7 +17886,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17890,10 +17900,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45327</v>
+        <v>45728</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17906,7 +17916,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17949,7 +17959,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17963,10 +17973,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44890</v>
+        <v>45600</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17979,7 +17989,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>7.7</v>
+        <v>3.8</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18022,7 +18032,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18036,10 +18046,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44984</v>
+        <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18052,7 +18062,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18095,7 +18105,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18109,10 +18119,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44608</v>
+        <v>45608</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18125,7 +18135,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>3</v>
+        <v>12.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18168,7 +18178,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18182,10 +18192,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45574</v>
+        <v>45594</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18198,7 +18208,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>3.1</v>
+        <v>28.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18241,7 +18251,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18251,14 +18261,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45728</v>
+        <v>44911</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18271,7 +18281,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18314,7 +18324,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18324,14 +18334,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45236</v>
+        <v>44915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18344,7 +18354,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18387,7 +18397,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 51131-2021</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18401,10 +18411,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45568</v>
+        <v>44461</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18417,7 +18427,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18460,7 +18470,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18474,10 +18484,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44551</v>
+        <v>45804</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18489,13 +18499,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18538,7 +18543,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18552,10 +18557,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45600</v>
+        <v>45477</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18568,7 +18573,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18611,7 +18616,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18625,10 +18630,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45715</v>
+        <v>45709</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18641,7 +18646,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18684,7 +18689,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18698,10 +18703,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45728</v>
+        <v>45824</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18714,7 +18719,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18757,7 +18762,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18771,10 +18776,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45791</v>
+        <v>45820</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18787,7 +18792,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18830,7 +18835,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18840,14 +18845,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45645</v>
+        <v>45807</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18859,13 +18864,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18908,24 +18908,24 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>S 2442-2022</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44691</v>
+        <v>45807</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>12.4</v>
+        <v>1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18981,7 +18981,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S 4383-2023</t>
+          <t>S 2442-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18995,10 +18995,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45265</v>
+        <v>44691</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19011,7 +19011,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>18.9</v>
+        <v>12.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19054,7 +19054,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S 8937-2021</t>
+          <t>S 4383-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19068,10 +19068,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44509</v>
+        <v>45265</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>35.9</v>
+        <v>18.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19127,7 +19127,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 3693-2023</t>
+          <t>S 8937-2021</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19141,10 +19141,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45218</v>
+        <v>44509</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>35.7</v>
+        <v>35.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19200,7 +19200,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 221-2025</t>
+          <t>S 3693-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19214,10 +19214,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45680</v>
+        <v>45218</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>13.8</v>
+        <v>35.7</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19273,7 +19273,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 3468-2024</t>
+          <t>S 221-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45539</v>
+        <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>10.2</v>
+        <v>13.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19346,7 +19346,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 2441-2023</t>
+          <t>S 3468-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19360,10 +19360,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45114</v>
+        <v>45539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19419,7 +19419,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 3794-2024</t>
+          <t>S 2441-2023</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19429,14 +19429,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45558</v>
+        <v>45114</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19448,13 +19448,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19497,7 +19492,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 792-2025</t>
+          <t>S 3794-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19507,14 +19502,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45729</v>
+        <v>45558</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19526,8 +19521,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>12.9</v>
+        <v>3.2</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19570,7 +19570,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 310-2025</t>
+          <t>S 792-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19584,10 +19584,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45688</v>
+        <v>45729</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>16</v>
+        <v>12.9</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19643,7 +19643,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S 1522-2025</t>
+          <t>S 310-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19657,10 +19657,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45791</v>
+        <v>45688</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>30.6</v>
+        <v>16</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19716,148 +19716,221 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
+          <t>S 1522-2025</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>45791</v>
+      </c>
+      <c r="E241" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>0</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242" ht="15" customHeight="1">
+      <c r="A242" t="inlineStr">
+        <is>
           <t>S 1063-2026</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D241" s="1" t="n">
+      <c r="D242" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="E241" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I241" t="n">
+      <c r="E242" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
         <v>23.5</v>
       </c>
-      <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="P241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" t="n">
-        <v>0</v>
-      </c>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
+      <c r="V242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>S 1492-2026</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C243" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D242" s="1" t="n">
+      <c r="D243" s="1" t="n">
         <v>46162</v>
       </c>
-      <c r="E242" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I242" t="n">
+      <c r="E243" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J242" t="n">
-        <v>0</v>
-      </c>
-      <c r="K242" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="n">
-        <v>0</v>
-      </c>
-      <c r="N242" t="n">
-        <v>0</v>
-      </c>
-      <c r="O242" t="n">
-        <v>0</v>
-      </c>
-      <c r="P242" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
-      <c r="S242" t="n">
-        <v>0</v>
-      </c>
-      <c r="T242" t="n">
-        <v>0</v>
-      </c>
-      <c r="U242" t="n">
-        <v>0</v>
-      </c>
-      <c r="V242" s="2" t="inlineStr"/>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="n">
+        <v>0</v>
+      </c>
+      <c r="V243" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42692-2022</t>
+          <t>A 8315-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44832</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1578,6 +1578,232 @@
         <v>4</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Småjungfrukam
+Spillkråka
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 24278-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Spillkråka
+Sångsvan
+Trana</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 42692-2022</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Brunfläckig pärlemorfjäril
 Loppstarr
@@ -1586,258 +1812,32 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42692-2022 artfynd.xlsx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42692-2022 karta.png", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42692-2022 georefererad karta.tif", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42692-2022 FSC-klagomål.docx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42692-2022 FSC-klagomål mail.docx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42692-2022 tillsynsbegäran.docx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42692-2022 tillsynsbegäran mail.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8315-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Småjungfrukam
-Spillkråka
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 24278-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45079</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>5</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Spillkråka
-Sångsvan
-Trana</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
         <v/>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>46210</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30645-2022</t>
+          <t>A 12111-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44763</v>
+        <v>45729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,259 +2130,259 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tofsvipa
+Tornseglare
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30645-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44763</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
 Nattviol</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 7616-2024</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45348</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>4.2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Kösa
 Åkerkulla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 12111-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45729</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tofsvipa
-Tornseglare
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8329-2026</t>
+          <t>A 2942-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2894,146 +2894,146 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Skogsbräsma
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8329-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Grönsångare
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 2942-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45315</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsbräsma
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
         <v>46252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>44504</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44860</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44690</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 18348-2022</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44685</v>
+        <v>44741</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3602,26 +3602,21 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>5.4</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3632,10 +3627,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3648,42 +3643,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Klotullört</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3697,10 +3692,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45231</v>
+        <v>45174</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3713,7 +3708,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3725,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3737,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3753,42 +3748,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 54753-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3802,10 +3797,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45322</v>
+        <v>44883</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3818,10 +3813,10 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -3833,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3842,10 +3837,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3858,42 +3853,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54753-2022</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3907,10 +3902,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44883</v>
+        <v>45922</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3923,20 +3918,20 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -3947,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3963,42 +3958,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4012,10 +4007,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45922</v>
+        <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4028,7 +4023,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4040,10 +4035,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4068,42 +4063,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 61007-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4113,14 +4108,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45005</v>
+        <v>45645</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4132,18 +4127,23 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -4173,42 +4173,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61007-2024</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4218,14 +4218,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45098</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4237,28 +4237,23 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>10.3</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4270,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4283,42 +4278,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 18348-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4332,10 +4327,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44741</v>
+        <v>44685</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4347,11 +4342,16 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>5.4</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -4372,10 +4372,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4388,42 +4388,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Klotullört</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45174</v>
+        <v>45005</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4453,19 +4453,19 @@
         </is>
       </c>
       <c r="I37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4477,10 +4477,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4489,39 +4489,39 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
         <v>46255</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45098</v>
+        <v>45231</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.3</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -4687,10 +4687,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4699,39 +4699,39 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
@@ -4755,7 +4755,7 @@
         <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>45594</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4966,10 +4966,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44686</v>
+        <v>44504</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4982,10 +4982,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>20.3</v>
+        <v>37.2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5006,10 +5006,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5018,46 +5018,46 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5071,10 +5071,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44504</v>
+        <v>44858</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>37.2</v>
+        <v>15.5</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5123,46 +5123,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>44686</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5192,20 +5192,20 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5232,35 +5232,35 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
@@ -5284,7 +5284,7 @@
         <v>45688</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45729</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>45251</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>44882</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>44460</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5818,7 +5818,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44461</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 5726-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5961,10 +5961,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45405</v>
+        <v>44596</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6020,7 +6020,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6042-2022</t>
+          <t>A 65203-2021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6030,14 +6030,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44599</v>
+        <v>44515</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6093,7 +6093,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 6042-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45236</v>
+        <v>44599</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6180,10 +6180,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44734</v>
+        <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6195,13 +6195,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6244,7 +6239,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6254,14 +6249,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45154</v>
+        <v>44621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6274,7 +6269,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6317,7 +6312,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5726-2022</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6331,10 +6326,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44596</v>
+        <v>45532</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6347,7 +6342,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6390,7 +6385,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6400,14 +6395,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44874</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6420,7 +6415,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6463,7 +6458,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6477,10 +6472,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44908</v>
+        <v>45110</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6492,13 +6487,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6541,7 +6531,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6555,10 +6545,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45342</v>
+        <v>45159</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6571,7 +6561,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6614,7 +6604,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6628,10 +6618,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44888</v>
+        <v>45751</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6644,7 +6634,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6687,7 +6677,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6697,14 +6687,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45037</v>
+        <v>45113</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6717,7 +6707,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>7.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6760,7 +6750,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6774,10 +6764,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44672</v>
+        <v>45477</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6790,7 +6780,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6833,7 +6823,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 65203-2021</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6843,14 +6833,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44515</v>
+        <v>44848</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6863,7 +6853,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6906,7 +6896,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6920,10 +6910,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44838</v>
+        <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6936,7 +6926,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6979,7 +6969,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6989,14 +6979,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44890</v>
+        <v>45001</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7009,7 +6999,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7052,7 +7042,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7066,10 +7056,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45398</v>
+        <v>45608</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7082,7 +7072,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.1</v>
+        <v>12.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7125,7 +7115,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7139,10 +7129,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45698</v>
+        <v>45947</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7155,7 +7145,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7198,7 +7188,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 51131-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7212,10 +7202,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45748</v>
+        <v>44461</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7228,7 +7218,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7271,7 +7261,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7281,14 +7271,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44741</v>
+        <v>44911</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7301,7 +7291,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7344,7 +7334,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7358,10 +7348,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45477</v>
+        <v>45372</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7374,7 +7364,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7417,7 +7407,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7427,14 +7417,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45477</v>
+        <v>44915</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7447,7 +7437,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7490,7 +7480,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7504,10 +7494,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45323</v>
+        <v>45804</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7520,7 +7510,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7563,7 +7553,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7577,10 +7567,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45987</v>
+        <v>45646</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7593,7 +7583,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7636,7 +7626,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7650,10 +7640,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44848</v>
+        <v>45477</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7666,7 +7656,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7709,7 +7699,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7723,10 +7713,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44838</v>
+        <v>45894</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7739,7 +7729,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7782,7 +7772,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7796,10 +7786,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44838</v>
+        <v>45894</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7812,7 +7802,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7855,7 +7845,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 17723-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7869,10 +7859,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44573</v>
+        <v>45037</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7885,7 +7875,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7928,7 +7918,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7942,10 +7932,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45113</v>
+        <v>45664</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7958,7 +7948,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8001,7 +7991,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8015,10 +8005,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45273</v>
+        <v>45709</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8031,7 +8021,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8074,7 +8064,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8088,10 +8078,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45894</v>
+        <v>45831</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8104,7 +8094,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>4.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8147,7 +8137,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8161,10 +8151,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45894</v>
+        <v>44672</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8177,7 +8167,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8220,7 +8210,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8234,10 +8224,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44879</v>
+        <v>45190</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8250,7 +8240,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8293,7 +8283,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8303,14 +8293,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45113</v>
+        <v>45323</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8323,7 +8313,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8366,7 +8356,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8380,10 +8370,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45539</v>
+        <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8396,7 +8386,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8439,7 +8429,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8453,10 +8443,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45831</v>
+        <v>45824</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8469,7 +8459,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8512,7 +8502,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8526,10 +8516,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45741</v>
+        <v>45919</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8542,7 +8532,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8585,7 +8575,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8599,10 +8589,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45191</v>
+        <v>45820</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8615,7 +8605,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8658,7 +8648,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8672,10 +8662,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45190</v>
+        <v>46041</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8688,7 +8678,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8731,7 +8721,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8745,10 +8735,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46128</v>
+        <v>45807</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8761,7 +8751,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8804,7 +8794,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8818,10 +8808,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45919</v>
+        <v>44596</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8834,7 +8824,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8877,7 +8867,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8891,10 +8881,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45574</v>
+        <v>45807</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8907,7 +8897,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8950,7 +8940,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8960,14 +8950,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46121</v>
+        <v>46038</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9023,7 +9013,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9037,10 +9027,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44896</v>
+        <v>45005</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9053,7 +9043,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9096,7 +9086,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9110,10 +9100,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45534</v>
+        <v>45012</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9126,7 +9116,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.6</v>
+        <v>0.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9169,7 +9159,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9183,10 +9173,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46064</v>
+        <v>45093</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9199,7 +9189,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9242,7 +9232,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9256,10 +9246,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45261</v>
+        <v>44838</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9272,7 +9262,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9315,7 +9305,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9329,10 +9319,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45005</v>
+        <v>44838</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9345,7 +9335,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>4.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9405,7 +9395,7 @@
         <v>45940</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9461,7 +9451,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9471,14 +9461,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44970</v>
+        <v>44741</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9491,7 +9481,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9534,7 +9524,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9548,10 +9538,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45583</v>
+        <v>45273</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9564,7 +9554,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9607,7 +9597,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9621,10 +9611,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44672</v>
+        <v>45672</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9680,7 +9670,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9694,10 +9684,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44981</v>
+        <v>45061</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9709,8 +9699,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9753,7 +9748,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9767,10 +9762,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44852</v>
+        <v>45971</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9783,7 +9778,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>12.3</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9826,7 +9821,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9836,14 +9831,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45315</v>
+        <v>46064</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9856,7 +9851,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9899,7 +9894,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9913,10 +9908,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45005</v>
+        <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9929,7 +9924,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9972,7 +9967,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9986,10 +9981,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45971</v>
+        <v>45405</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10002,7 +9997,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10045,7 +10040,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10059,10 +10054,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45974</v>
+        <v>45477</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10075,7 +10070,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.7</v>
+        <v>7.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10118,7 +10113,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10135,7 +10130,7 @@
         <v>45974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10148,7 +10143,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10191,7 +10186,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10205,10 +10200,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45012</v>
+        <v>45974</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10221,7 +10216,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10264,7 +10259,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10274,14 +10269,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45001</v>
+        <v>45342</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10294,7 +10289,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10337,7 +10332,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10351,10 +10346,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45575</v>
+        <v>45698</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10367,7 +10362,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10422,7 @@
         <v>45982</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10483,7 +10478,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10497,10 +10492,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44860</v>
+        <v>46064</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10513,7 +10508,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10556,7 +10551,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10570,10 +10565,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46146</v>
+        <v>45987</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10586,7 +10581,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10641,7 @@
         <v>46000</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10719,7 +10714,7 @@
         <v>46000</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10775,7 +10770,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10789,10 +10784,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45887</v>
+        <v>45318</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10805,7 +10800,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10848,7 +10843,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10862,10 +10857,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45770</v>
+        <v>45887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10878,7 +10873,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10921,7 +10916,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10935,10 +10930,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46160</v>
+        <v>45093</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10951,7 +10946,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10994,7 +10989,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11008,10 +11003,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45755</v>
+        <v>45770</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11024,7 +11019,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11067,7 +11062,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11081,10 +11076,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46160</v>
+        <v>45945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11097,7 +11092,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11140,7 +11135,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11150,14 +11145,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45945</v>
+        <v>45978</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11170,7 +11165,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11213,7 +11208,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11227,10 +11222,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45061</v>
+        <v>46023</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11242,13 +11237,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11291,7 +11281,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11301,14 +11291,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45978</v>
+        <v>46023</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11321,7 +11311,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4.7</v>
+        <v>0.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11364,7 +11354,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11378,10 +11368,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46023</v>
+        <v>44981</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11394,7 +11384,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11437,7 +11427,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11451,10 +11441,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46023</v>
+        <v>45315</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11467,7 +11457,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11510,7 +11500,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11524,10 +11514,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45947</v>
+        <v>45057</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11540,7 +11530,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11583,7 +11573,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11597,10 +11587,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45775</v>
+        <v>44838</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11613,7 +11603,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11656,7 +11646,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11670,10 +11660,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44838</v>
+        <v>44852</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11686,7 +11676,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.3</v>
+        <v>12.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11729,7 +11719,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11743,10 +11733,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44838</v>
+        <v>44593</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11759,7 +11749,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11802,7 +11792,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11812,14 +11802,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44515</v>
+        <v>45618</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11832,7 +11822,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11875,7 +11865,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11889,10 +11879,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46038</v>
+        <v>46128</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11905,7 +11895,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11948,7 +11938,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11958,14 +11948,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45240</v>
+        <v>46121</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11978,7 +11968,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12021,7 +12011,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12035,10 +12025,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45700</v>
+        <v>45575</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12051,7 +12041,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12094,7 +12084,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12108,10 +12098,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46041</v>
+        <v>46064</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12124,7 +12114,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12167,7 +12157,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12177,14 +12167,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45406</v>
+        <v>45240</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12197,7 +12187,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12240,7 +12230,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12254,10 +12244,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44593</v>
+        <v>44573</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12270,7 +12260,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12313,7 +12303,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12327,10 +12317,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45947</v>
+        <v>45175</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12343,7 +12333,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12386,7 +12376,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12400,10 +12390,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45945</v>
+        <v>45539</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12416,7 +12406,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12459,7 +12449,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12473,10 +12463,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45315</v>
+        <v>45322</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12489,7 +12479,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12532,7 +12522,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12546,10 +12536,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45093</v>
+        <v>44879</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12562,7 +12552,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12605,7 +12595,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12619,10 +12609,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45110</v>
+        <v>45231</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12635,7 +12625,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12678,7 +12668,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12692,10 +12682,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45751</v>
+        <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12708,7 +12698,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12751,7 +12741,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12765,10 +12755,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45051</v>
+        <v>44734</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12782,11 +12772,11 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12829,7 +12819,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12839,14 +12829,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46064</v>
+        <v>45748</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12859,7 +12849,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.2</v>
+        <v>3.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12902,7 +12892,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12912,14 +12902,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45231</v>
+        <v>44970</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12932,7 +12922,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12975,7 +12965,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12989,10 +12979,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46064</v>
+        <v>44685</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13004,8 +12994,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13048,7 +13043,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13062,10 +13057,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45664</v>
+        <v>45534</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13078,7 +13073,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>7.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13121,7 +13116,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13135,10 +13130,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44734</v>
+        <v>44838</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13150,13 +13145,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>9.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13199,7 +13189,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13213,10 +13203,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45322</v>
+        <v>46146</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13229,7 +13219,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13272,7 +13262,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13286,10 +13276,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45343</v>
+        <v>44896</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13302,7 +13292,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13345,7 +13335,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13355,14 +13345,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45343</v>
+        <v>44515</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13375,7 +13365,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13418,7 +13408,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13432,10 +13422,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45526</v>
+        <v>45741</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13448,7 +13438,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13491,7 +13481,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13505,10 +13495,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46197</v>
+        <v>44734</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13520,8 +13510,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.8</v>
+        <v>0.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13564,7 +13559,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13578,10 +13573,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44608</v>
+        <v>45338</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13594,7 +13589,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13637,7 +13632,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13651,10 +13646,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45477</v>
+        <v>45775</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13667,7 +13662,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13710,7 +13705,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13724,10 +13719,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45318</v>
+        <v>46160</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13740,7 +13735,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13783,7 +13778,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13797,10 +13792,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45450</v>
+        <v>46160</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13813,7 +13808,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13856,7 +13851,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13870,10 +13865,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45338</v>
+        <v>44888</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13886,7 +13881,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13929,7 +13924,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13943,10 +13938,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46198</v>
+        <v>44672</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13959,7 +13954,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14002,7 +13997,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14016,10 +14011,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45057</v>
+        <v>45343</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14032,7 +14027,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14075,7 +14070,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14085,14 +14080,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44621</v>
+        <v>45343</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14105,7 +14100,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14148,7 +14143,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14162,10 +14157,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45175</v>
+        <v>45315</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14178,7 +14173,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14221,7 +14216,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14235,10 +14230,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45167</v>
+        <v>45398</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14251,7 +14246,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14294,7 +14289,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14308,10 +14303,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45618</v>
+        <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14324,7 +14319,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14367,7 +14362,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14381,10 +14376,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44585</v>
+        <v>45005</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14397,7 +14392,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14440,7 +14435,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14454,10 +14449,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45539</v>
+        <v>45273</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14470,7 +14465,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14513,7 +14508,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14527,10 +14522,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46205</v>
+        <v>45945</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14543,7 +14538,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14586,7 +14581,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14600,10 +14595,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45001</v>
+        <v>44594</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14616,7 +14611,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14659,7 +14654,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14673,10 +14668,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44596</v>
+        <v>44874</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14689,7 +14684,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14732,7 +14727,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14746,10 +14741,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44984</v>
+        <v>44908</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14761,8 +14756,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14805,7 +14805,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14819,10 +14819,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46209</v>
+        <v>45755</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14878,7 +14878,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14892,10 +14892,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45159</v>
+        <v>44838</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14951,7 +14951,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14965,10 +14965,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45231</v>
+        <v>44838</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15038,10 +15038,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46255</v>
+        <v>45191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15097,7 +15097,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15111,10 +15111,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46258</v>
+        <v>45154</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15170,7 +15170,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15184,10 +15184,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46255</v>
+        <v>44860</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15243,7 +15243,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15257,10 +15257,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45532</v>
+        <v>45113</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15316,7 +15316,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15330,10 +15330,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44594</v>
+        <v>46197</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15389,7 +15389,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15403,10 +15403,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46258</v>
+        <v>45216</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15462,7 +15462,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15476,10 +15476,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45728</v>
+        <v>45216</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15535,7 +15535,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15549,10 +15549,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45574</v>
+        <v>46198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15608,7 +15608,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15622,10 +15622,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44838</v>
+        <v>45450</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15695,10 +15695,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44685</v>
+        <v>45477</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15710,13 +15710,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15759,7 +15754,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15773,10 +15768,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45273</v>
+        <v>45526</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15789,7 +15784,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15832,7 +15827,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15846,10 +15841,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45216</v>
+        <v>46205</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15862,7 +15857,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15905,7 +15900,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15919,10 +15914,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45216</v>
+        <v>45001</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15935,7 +15930,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15978,7 +15973,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15992,10 +15987,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46265</v>
+        <v>45231</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16008,7 +16003,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16051,7 +16046,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16065,10 +16060,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45372</v>
+        <v>46209</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16081,7 +16076,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16124,7 +16119,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16134,14 +16129,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46268</v>
+        <v>46255</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16154,7 +16149,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16197,7 +16192,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16211,10 +16206,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46251</v>
+        <v>45539</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16227,7 +16222,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16270,7 +16265,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16284,10 +16279,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46178</v>
+        <v>46255</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16300,7 +16295,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16343,7 +16338,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16357,10 +16352,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45041</v>
+        <v>46258</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16373,7 +16368,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16416,7 +16411,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16430,10 +16425,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46273</v>
+        <v>45051</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16443,6 +16438,11 @@
       <c r="G196" t="inlineStr">
         <is>
           <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -16489,7 +16489,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16503,10 +16503,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46196</v>
+        <v>46258</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16562,7 +16562,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16576,10 +16576,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45327</v>
+        <v>45685</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16635,7 +16635,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16649,10 +16649,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45093</v>
+        <v>45700</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16708,7 +16708,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16722,10 +16722,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46191</v>
+        <v>45261</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16781,7 +16781,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16795,10 +16795,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45685</v>
+        <v>46265</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16854,7 +16854,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16868,10 +16868,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45646</v>
+        <v>46251</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16884,7 +16884,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16927,7 +16927,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16937,14 +16937,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45672</v>
+        <v>46268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17000,7 +17000,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45477</v>
+        <v>45041</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17087,10 +17087,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46184</v>
+        <v>45327</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17103,7 +17103,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17146,7 +17146,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17160,10 +17160,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46177</v>
+        <v>44890</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>3.9</v>
+        <v>7.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17219,7 +17219,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17233,10 +17233,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17292,7 +17292,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17306,10 +17306,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46136</v>
+        <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17365,7 +17365,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 38003-2026</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17379,10 +17379,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46280</v>
+        <v>46178</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17438,7 +17438,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17452,10 +17452,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44551</v>
+        <v>46191</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17467,13 +17467,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17516,7 +17511,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17530,10 +17525,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45568</v>
+        <v>44608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17546,7 +17541,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17589,7 +17584,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17603,10 +17598,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45715</v>
+        <v>45574</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17619,7 +17614,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17662,7 +17657,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17676,10 +17671,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45471</v>
+        <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17692,7 +17687,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17735,7 +17730,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17749,10 +17744,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45791</v>
+        <v>46279</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17765,7 +17760,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17808,7 +17803,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17818,14 +17813,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45645</v>
+        <v>45236</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17837,13 +17832,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17886,7 +17876,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17900,10 +17890,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45728</v>
+        <v>46136</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17916,7 +17906,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17959,7 +17949,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17973,10 +17963,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45600</v>
+        <v>46184</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17989,7 +17979,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18032,7 +18022,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18046,10 +18036,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45594</v>
+        <v>46177</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18062,7 +18052,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18105,7 +18095,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18119,10 +18109,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45608</v>
+        <v>46280</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18135,7 +18125,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>12.3</v>
+        <v>3.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18178,7 +18168,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18192,10 +18182,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45594</v>
+        <v>45568</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18208,7 +18198,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>28.4</v>
+        <v>2.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18251,7 +18241,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18261,14 +18251,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44911</v>
+        <v>46196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18281,7 +18271,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18324,7 +18314,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18334,14 +18324,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44915</v>
+        <v>44551</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18353,8 +18343,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18397,7 +18392,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 51131-2021</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18411,10 +18406,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44461</v>
+        <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18427,7 +18422,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18470,7 +18465,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18484,10 +18479,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45804</v>
+        <v>45715</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18500,7 +18495,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18543,7 +18538,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18557,10 +18552,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45477</v>
+        <v>45728</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18573,7 +18568,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18616,7 +18611,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18630,10 +18625,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45709</v>
+        <v>45791</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18646,7 +18641,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18689,7 +18684,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18699,14 +18694,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45824</v>
+        <v>45645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18718,8 +18713,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18762,7 +18762,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18776,10 +18776,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45820</v>
+        <v>45471</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18835,7 +18835,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18849,10 +18849,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45807</v>
+        <v>45594</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18908,7 +18908,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18922,10 +18922,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45807</v>
+        <v>45594</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1</v>
+        <v>28.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18998,7 +18998,7 @@
         <v>44691</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19071,7 +19071,7 @@
         <v>45265</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>44509</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
         <v>45218</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45539</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45114</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45558</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45729</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45688</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>45791</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>46127</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>46162</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24278-2023</t>
+          <t>A 8315-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45079</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1575,9 +1575,122 @@
         <v>5</v>
       </c>
       <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Småjungfrukam
+Spillkråka
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 24278-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
@@ -1586,149 +1699,36 @@
 Trana</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8315-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Småjungfrukam
-Spillkråka
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>46210</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12111-2025</t>
+          <t>A 30645-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45729</v>
+        <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,259 +2130,259 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 7616-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Kösa
+Åkerkulla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 12111-2025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45729</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tofsvipa
 Tornseglare
 Gröngöling</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 30645-2022</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44763</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 7616-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45348</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Kösa
-Åkerkulla
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8329-2026</t>
+          <t>A 2942-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2894,259 +2894,259 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Skogsbräsma
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8329-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Grönsångare
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 33910-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Guldlockmossa</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 33910-2026 artfynd.xlsx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 33910-2026 karta.png", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 33910-2026 georefererad karta.tif", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 33910-2026 FSC-klagomål.docx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 33910-2026 FSC-klagomål mail.docx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 33910-2026 tillsynsbegäran.docx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 33910-2026 tillsynsbegäran mail.docx", "A 33910-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 2942-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45315</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Skogsbräsma
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24597-2026</t>
+          <t>A 38317-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46170</v>
+        <v>46282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3203,159 +3203,159 @@
         <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>2</v>
       </c>
       <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A 24597-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
         <v>4</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>4</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24597-2026 artfynd.xlsx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24597-2026 karta.png", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24597-2026 georefererad karta.tif", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24597-2026 FSC-klagomål.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24597-2026 FSC-klagomål mail.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24597-2026 tillsynsbegäran.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24597-2026 tillsynsbegäran mail.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24597-2026 prioriterade fågelarter.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 38317-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
         <v/>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45231</v>
+        <v>44741</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3733,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3749,42 +3749,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45322</v>
+        <v>45174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3826,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3854,35 +3854,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45005</v>
+        <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4024,23 +4024,23 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
@@ -4048,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4060,46 +4060,46 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 61007-2024</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4109,14 +4109,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45645</v>
+        <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4128,25 +4128,20 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4161,7 +4156,7 @@
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4170,46 +4165,46 @@
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 61007-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4219,14 +4214,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45922</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4238,20 +4233,25 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4266,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4275,39 +4275,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
         <v>45098</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44685</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4543,10 +4543,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46255</v>
+        <v>45005</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4599,42 +4599,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44741</v>
+        <v>45231</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4704,42 +4704,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45174</v>
+        <v>46255</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,11 +4769,11 @@
         </is>
       </c>
       <c r="I40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4793,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4805,39 +4805,39 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45594</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44686</v>
+        <v>44504</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>20.3</v>
+        <v>37.2</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5112,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5124,46 +5124,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44504</v>
+        <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>37.2</v>
+        <v>15.5</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5229,46 +5229,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44858</v>
+        <v>44686</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,20 +5298,20 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5338,35 +5338,35 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44538</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44461</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44599</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45698</v>
+        <v>45532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45405</v>
+        <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44874</v>
+        <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44888</v>
+        <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45342</v>
+        <v>45110</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44908</v>
+        <v>45159</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6666,13 +6666,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6715,7 +6710,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6729,10 +6724,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45037</v>
+        <v>45751</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6745,7 +6740,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6788,7 +6783,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6798,14 +6793,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44890</v>
+        <v>45113</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6818,7 +6813,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6861,7 +6856,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6875,10 +6870,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44838</v>
+        <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6891,7 +6886,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6934,7 +6929,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6948,10 +6943,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45398</v>
+        <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6964,7 +6959,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7007,7 +7002,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7021,10 +7016,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45748</v>
+        <v>44848</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7037,7 +7032,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7080,7 +7075,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7090,14 +7085,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45236</v>
+        <v>45001</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7110,7 +7105,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7153,7 +7148,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7167,10 +7162,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45477</v>
+        <v>45372</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7183,7 +7178,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7226,7 +7221,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7240,10 +7235,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45477</v>
+        <v>45646</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7256,7 +7251,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7299,7 +7294,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 17723-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7313,10 +7308,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45323</v>
+        <v>45037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7329,7 +7324,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5.1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7372,7 +7367,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7386,10 +7381,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44734</v>
+        <v>45664</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7401,13 +7396,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7450,7 +7440,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7464,10 +7454,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44848</v>
+        <v>44672</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7480,7 +7470,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7523,7 +7513,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7537,10 +7527,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44838</v>
+        <v>45190</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7553,7 +7543,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7596,7 +7586,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7610,10 +7600,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44838</v>
+        <v>45323</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7626,7 +7616,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7669,7 +7659,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7683,10 +7673,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45113</v>
+        <v>45167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7699,7 +7689,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7742,7 +7732,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7756,10 +7746,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44879</v>
+        <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7772,7 +7762,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7815,7 +7805,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7825,14 +7815,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45113</v>
+        <v>45005</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7845,7 +7835,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7888,7 +7878,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7902,10 +7892,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45539</v>
+        <v>45012</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7918,7 +7908,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7961,7 +7951,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7975,10 +7965,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45741</v>
+        <v>45093</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7991,7 +7981,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8034,7 +8024,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8048,10 +8038,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45574</v>
+        <v>44838</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8064,7 +8054,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8107,7 +8097,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8121,10 +8111,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44896</v>
+        <v>44838</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8137,7 +8127,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8180,7 +8170,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8194,10 +8184,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46064</v>
+        <v>44741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8210,7 +8200,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8253,7 +8243,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8267,10 +8257,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45987</v>
+        <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8283,7 +8273,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8326,7 +8316,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8336,14 +8326,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44970</v>
+        <v>45672</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8356,7 +8346,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8399,7 +8389,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8413,10 +8403,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45709</v>
+        <v>45061</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8428,8 +8418,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8472,7 +8467,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8486,10 +8481,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45824</v>
+        <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8502,7 +8497,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8545,7 +8540,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8559,10 +8554,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45820</v>
+        <v>45405</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8575,7 +8570,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8618,7 +8613,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8632,10 +8627,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45583</v>
+        <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8648,7 +8643,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4.9</v>
+        <v>7.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8691,7 +8686,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8705,10 +8700,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44672</v>
+        <v>45342</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8721,7 +8716,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8764,7 +8759,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8778,10 +8773,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44981</v>
+        <v>45698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8794,7 +8789,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8837,7 +8832,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44852</v>
+        <v>45894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8867,7 +8862,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>12.3</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8910,7 +8905,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45315</v>
+        <v>45894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8940,7 +8935,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8983,7 +8978,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8997,10 +8992,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45807</v>
+        <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9013,7 +9008,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9056,7 +9051,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9070,10 +9065,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45005</v>
+        <v>45831</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9086,7 +9081,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9129,7 +9124,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45807</v>
+        <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9159,7 +9154,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9202,7 +9197,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9216,10 +9211,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45012</v>
+        <v>45919</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9232,7 +9227,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9275,7 +9270,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45894</v>
+        <v>44981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9305,7 +9300,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9348,7 +9343,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9358,14 +9353,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45001</v>
+        <v>45315</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9378,7 +9373,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9421,7 +9416,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9435,10 +9430,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46128</v>
+        <v>45057</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9451,7 +9446,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9494,7 +9489,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45575</v>
+        <v>44838</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9524,7 +9519,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9567,7 +9562,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9581,10 +9576,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45894</v>
+        <v>46146</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9597,7 +9592,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9640,7 +9635,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9650,14 +9645,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46121</v>
+        <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9670,7 +9665,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>12.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9713,7 +9708,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9727,10 +9722,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46064</v>
+        <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9743,7 +9738,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9786,7 +9781,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9800,10 +9795,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45831</v>
+        <v>45940</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9816,7 +9811,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.4</v>
+        <v>0.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9859,7 +9854,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9873,10 +9868,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45919</v>
+        <v>45618</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9889,7 +9884,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9932,7 +9927,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9946,10 +9941,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45755</v>
+        <v>45575</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10005,7 +10000,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44838</v>
+        <v>45240</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10035,7 +10030,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10078,7 +10073,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10092,10 +10087,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44838</v>
+        <v>45971</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10108,7 +10103,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.9</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10151,7 +10146,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10161,14 +10156,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44515</v>
+        <v>44573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10181,7 +10176,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10224,7 +10219,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10238,10 +10233,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45700</v>
+        <v>45175</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10254,7 +10249,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10297,7 +10292,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10307,14 +10302,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45406</v>
+        <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10327,7 +10322,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10370,7 +10365,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10384,10 +10379,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44593</v>
+        <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10400,7 +10395,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10443,7 +10438,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10457,10 +10452,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45315</v>
+        <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10473,7 +10468,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10516,7 +10511,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10530,10 +10525,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45093</v>
+        <v>45322</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10546,7 +10541,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10589,7 +10584,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10603,10 +10598,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45110</v>
+        <v>44879</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10619,7 +10614,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10662,7 +10657,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10676,10 +10671,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10692,7 +10687,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10735,7 +10730,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10749,10 +10744,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45751</v>
+        <v>45231</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10765,7 +10760,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10808,7 +10803,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10822,10 +10817,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45051</v>
+        <v>45775</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10837,13 +10832,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10886,7 +10876,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10900,10 +10890,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46160</v>
+        <v>45574</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10916,7 +10906,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10959,7 +10949,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10973,10 +10963,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46160</v>
+        <v>44734</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10988,8 +10978,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>3.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11032,7 +11027,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11046,10 +11041,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45231</v>
+        <v>45748</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11062,7 +11057,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11105,7 +11100,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45940</v>
+        <v>46160</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11135,7 +11130,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11178,7 +11173,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11192,10 +11187,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45775</v>
+        <v>46160</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11208,7 +11203,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11251,7 +11246,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11261,14 +11256,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45664</v>
+        <v>44970</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11281,7 +11276,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11324,7 +11319,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11338,10 +11333,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45343</v>
+        <v>44685</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11353,8 +11348,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11397,7 +11397,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11411,10 +11411,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45343</v>
+        <v>45534</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11470,7 +11470,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11484,10 +11484,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44608</v>
+        <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11543,7 +11543,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11557,10 +11557,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45477</v>
+        <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11630,10 +11630,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45318</v>
+        <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11689,7 +11689,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11703,10 +11703,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45450</v>
+        <v>44896</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11762,7 +11762,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11776,10 +11776,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45947</v>
+        <v>45887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11835,7 +11835,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11845,14 +11845,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45945</v>
+        <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11908,7 +11908,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11918,14 +11918,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44621</v>
+        <v>45770</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11981,7 +11981,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11995,10 +11995,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45175</v>
+        <v>45945</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12054,7 +12054,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12068,10 +12068,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45167</v>
+        <v>45741</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12137,14 +12137,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45618</v>
+        <v>45978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12200,7 +12200,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44585</v>
+        <v>46023</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12273,7 +12273,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45539</v>
+        <v>46023</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12360,10 +12360,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45001</v>
+        <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12419,7 +12419,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12433,10 +12433,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44596</v>
+        <v>44734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12448,8 +12448,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12492,7 +12497,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12506,10 +12511,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46197</v>
+        <v>45338</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12522,7 +12527,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12565,7 +12570,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12579,10 +12584,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45159</v>
+        <v>45947</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12595,7 +12600,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12638,7 +12643,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12652,10 +12657,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45971</v>
+        <v>44888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12668,7 +12673,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12711,7 +12716,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12725,10 +12730,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46198</v>
+        <v>44672</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12741,7 +12746,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12784,7 +12789,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12798,10 +12803,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45974</v>
+        <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12814,7 +12819,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12857,7 +12862,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12871,10 +12876,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45974</v>
+        <v>45343</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12887,7 +12892,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12930,7 +12935,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12944,10 +12949,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46205</v>
+        <v>45343</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12960,7 +12965,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13003,7 +13008,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13017,10 +13022,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45982</v>
+        <v>46038</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13033,7 +13038,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13076,7 +13081,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13090,10 +13095,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44594</v>
+        <v>45315</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13106,7 +13111,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13149,7 +13154,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13163,10 +13168,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45728</v>
+        <v>45945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13179,7 +13184,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13222,7 +13227,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13236,10 +13241,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45574</v>
+        <v>45398</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13252,7 +13257,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>4.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13295,7 +13300,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13309,10 +13314,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44838</v>
+        <v>45005</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13325,7 +13330,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13368,7 +13373,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13382,10 +13387,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44685</v>
+        <v>45273</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13397,13 +13402,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13446,7 +13446,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13456,14 +13456,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45154</v>
+        <v>46064</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46209</v>
+        <v>44594</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13592,7 +13592,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13606,10 +13606,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44672</v>
+        <v>44874</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13665,7 +13665,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13679,10 +13679,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45231</v>
+        <v>46064</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13752,10 +13752,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46255</v>
+        <v>44908</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13767,8 +13767,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13811,7 +13816,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13825,10 +13830,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46258</v>
+        <v>45987</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13841,7 +13846,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13884,7 +13889,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13898,10 +13903,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46255</v>
+        <v>45755</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13914,7 +13919,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13957,7 +13962,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13971,10 +13976,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44741</v>
+        <v>44838</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13987,7 +13992,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.3</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14030,7 +14035,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14044,10 +14049,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46258</v>
+        <v>44838</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14103,7 +14108,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14117,10 +14122,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46000</v>
+        <v>45191</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14133,7 +14138,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14176,7 +14181,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14190,10 +14195,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46000</v>
+        <v>45154</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14206,7 +14211,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14249,7 +14254,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14263,10 +14268,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46265</v>
+        <v>44860</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14279,7 +14284,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14322,7 +14327,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14332,14 +14337,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46268</v>
+        <v>45113</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14352,7 +14357,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14395,7 +14400,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14409,10 +14414,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44573</v>
+        <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14425,7 +14430,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14468,7 +14473,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14482,10 +14487,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45273</v>
+        <v>46198</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14498,7 +14503,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14541,7 +14546,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14555,10 +14560,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46251</v>
+        <v>45216</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14571,7 +14576,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14614,7 +14619,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14628,10 +14633,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45887</v>
+        <v>45216</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14687,7 +14692,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14701,10 +14706,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46178</v>
+        <v>45450</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14717,7 +14722,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14760,7 +14765,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14774,10 +14779,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45191</v>
+        <v>45477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14790,7 +14795,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14833,7 +14838,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14847,10 +14852,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46273</v>
+        <v>46128</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14863,7 +14868,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14906,7 +14911,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14920,10 +14925,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45190</v>
+        <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14936,7 +14941,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14979,7 +14984,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14989,14 +14994,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45534</v>
+        <v>46121</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15009,7 +15014,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>7.6</v>
+        <v>1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15052,7 +15057,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15066,10 +15071,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45770</v>
+        <v>45001</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15082,7 +15087,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15125,7 +15130,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15139,10 +15144,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45945</v>
+        <v>46064</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15155,7 +15160,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15198,7 +15203,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15212,10 +15217,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45261</v>
+        <v>45539</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15228,7 +15233,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15271,7 +15276,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15281,14 +15286,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45978</v>
+        <v>46205</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15301,7 +15306,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15344,7 +15349,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15358,10 +15363,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46191</v>
+        <v>45051</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15373,8 +15378,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15417,7 +15427,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15431,10 +15441,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45005</v>
+        <v>45231</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15447,7 +15457,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15490,7 +15500,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15504,10 +15514,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46023</v>
+        <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15520,7 +15530,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15563,7 +15573,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15577,10 +15587,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46023</v>
+        <v>46209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15593,7 +15603,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15636,7 +15646,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15650,10 +15660,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45947</v>
+        <v>45700</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15666,7 +15676,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15709,7 +15719,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15723,10 +15733,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46184</v>
+        <v>45261</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15739,7 +15749,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15782,7 +15792,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15796,10 +15806,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46177</v>
+        <v>46255</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15812,7 +15822,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15855,7 +15865,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15869,10 +15879,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46279</v>
+        <v>46255</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15885,7 +15895,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15928,7 +15938,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15942,10 +15952,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46136</v>
+        <v>46258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15958,7 +15968,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16001,7 +16011,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38003-2026</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16015,10 +16025,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46280</v>
+        <v>45041</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16031,7 +16041,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16074,7 +16084,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16088,10 +16098,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44860</v>
+        <v>45327</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16104,7 +16114,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16147,7 +16157,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38392-2026</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16161,10 +16171,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46282</v>
+        <v>46258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16177,7 +16187,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16220,7 +16230,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16234,10 +16244,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46196</v>
+        <v>44890</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16250,7 +16260,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4</v>
+        <v>7.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16293,7 +16303,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16307,10 +16317,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45061</v>
+        <v>44984</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16322,13 +16332,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16371,7 +16376,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16385,10 +16390,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45240</v>
+        <v>44608</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16401,7 +16406,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16444,7 +16449,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16458,10 +16463,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46038</v>
+        <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16474,7 +16479,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16517,7 +16522,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16531,10 +16536,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46041</v>
+        <v>46265</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16547,7 +16552,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16590,7 +16595,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16604,10 +16609,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44734</v>
+        <v>45728</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16619,13 +16624,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>9.300000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16668,7 +16668,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16682,10 +16682,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45322</v>
+        <v>46251</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16741,7 +16741,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16755,10 +16755,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45526</v>
+        <v>45236</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16828,10 +16828,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46064</v>
+        <v>46268</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>5.2</v>
+        <v>2.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16901,10 +16901,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45338</v>
+        <v>46273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16960,7 +16960,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16974,10 +16974,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45057</v>
+        <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17033,7 +17033,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17047,10 +17047,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44984</v>
+        <v>46191</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17106,7 +17106,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45532</v>
+        <v>45568</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17179,7 +17179,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17193,10 +17193,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45273</v>
+        <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17208,8 +17208,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17252,7 +17257,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17266,10 +17271,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45216</v>
+        <v>46279</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17282,7 +17287,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17325,7 +17330,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17339,10 +17344,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45216</v>
+        <v>46136</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17355,7 +17360,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17398,7 +17403,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17412,10 +17417,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45372</v>
+        <v>46184</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17428,7 +17433,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17471,7 +17476,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17485,10 +17490,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45041</v>
+        <v>45600</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17501,7 +17506,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17544,7 +17549,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17558,10 +17563,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45327</v>
+        <v>45715</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17574,7 +17579,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17617,7 +17622,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17631,10 +17636,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45093</v>
+        <v>46177</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17647,7 +17652,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17690,7 +17695,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17704,10 +17709,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45685</v>
+        <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17720,7 +17725,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17763,7 +17768,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17777,10 +17782,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45646</v>
+        <v>45791</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17793,7 +17798,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17836,7 +17841,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17850,10 +17855,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45672</v>
+        <v>46280</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17866,7 +17871,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17909,7 +17914,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17919,14 +17924,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45477</v>
+        <v>45645</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17938,8 +17943,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I216" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17982,7 +17992,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17996,10 +18006,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44551</v>
+        <v>45471</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18011,13 +18021,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18060,7 +18065,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 38392-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18074,10 +18079,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45568</v>
+        <v>46282</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18090,7 +18095,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18133,7 +18138,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18147,10 +18152,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45715</v>
+        <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18163,7 +18168,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18206,7 +18211,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18220,10 +18225,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45471</v>
+        <v>45594</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18236,7 +18241,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.7</v>
+        <v>28.4</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18279,7 +18284,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18293,10 +18298,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45791</v>
+        <v>46196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18309,7 +18314,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18352,7 +18357,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18362,14 +18367,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45645</v>
+        <v>45608</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18381,13 +18386,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>2.2</v>
+        <v>12.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18430,7 +18430,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 51131-2021</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45728</v>
+        <v>44461</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18503,7 +18503,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18513,14 +18513,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45600</v>
+        <v>44911</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18586,14 +18586,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45594</v>
+        <v>44915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18649,7 +18649,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18663,10 +18663,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45608</v>
+        <v>45804</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>12.3</v>
+        <v>0.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18736,10 +18736,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45594</v>
+        <v>45477</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>28.4</v>
+        <v>0.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18795,7 +18795,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18805,14 +18805,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44911</v>
+        <v>45709</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18878,14 +18878,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>44915</v>
+        <v>45824</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 51131-2021</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18955,10 +18955,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>44461</v>
+        <v>45820</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19014,7 +19014,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19028,10 +19028,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45804</v>
+        <v>45807</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19087,7 +19087,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19101,10 +19101,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45477</v>
+        <v>45807</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19177,7 +19177,7 @@
         <v>44691</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44509</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45218</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45680</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45114</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45558</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45688</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45791</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46127</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46162</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>45079</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>46210</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45348</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45729</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46064</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44741</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45098</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44685</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>45005</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45231</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>46255</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45594</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44504</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44686</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44460</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44538</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44461</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>44515</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>44599</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>45406</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>44585</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6581,7 +6581,7 @@
         <v>45110</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>45159</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>45751</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6800,7 +6800,7 @@
         <v>45113</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>45583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         <v>44848</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45001</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
         <v>45372</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>45646</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         <v>45037</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         <v>45664</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44672</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7530,7 +7530,7 @@
         <v>45190</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         <v>45323</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         <v>45167</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45005</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         <v>45012</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45093</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44838</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44838</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44741</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>45273</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45672</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45061</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>45405</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45342</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45698</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>45894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>45831</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45919</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45315</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45057</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44838</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>46146</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44852</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44593</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45940</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>45618</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>45575</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>45240</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45971</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>44573</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10236,7 +10236,7 @@
         <v>45175</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10309,7 +10309,7 @@
         <v>45539</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>45974</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>45974</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>45322</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>44879</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>45982</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45231</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45775</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
         <v>45574</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10966,7 +10966,7 @@
         <v>44734</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45748</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>46160</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46160</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44970</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44685</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>45534</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>46000</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>46000</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>44896</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44515</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45770</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45945</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45741</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45978</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>46023</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>46023</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44734</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>45338</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>45947</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44888</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>44672</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12806,7 +12806,7 @@
         <v>46041</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12879,7 +12879,7 @@
         <v>45343</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>45343</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13025,7 +13025,7 @@
         <v>46038</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13098,7 +13098,7 @@
         <v>45315</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13171,7 +13171,7 @@
         <v>45945</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13244,7 +13244,7 @@
         <v>45398</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45005</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45273</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>46064</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44594</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44874</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>46064</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44908</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>45987</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13906,7 +13906,7 @@
         <v>45755</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44838</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>44838</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45191</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45154</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44860</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45113</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>46197</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>46198</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45216</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>45216</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45450</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>45477</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14855,7 +14855,7 @@
         <v>46128</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>46121</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15074,7 +15074,7 @@
         <v>45001</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>46064</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45539</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>46205</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45051</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45231</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45685</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>46209</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45700</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45261</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>46255</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>46255</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>46258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45041</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45327</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>46258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44890</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44984</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44608</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>46265</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45728</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46251</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>45236</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>46268</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46273</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>46191</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45568</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>46279</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46136</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>46184</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>45600</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45715</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46177</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45728</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45791</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46280</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>45645</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45471</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>46282</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18155,7 +18155,7 @@
         <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18228,7 +18228,7 @@
         <v>45594</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>46196</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45608</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>44461</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44911</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18593,7 +18593,7 @@
         <v>44915</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>45804</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18739,7 +18739,7 @@
         <v>45477</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45709</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45824</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45820</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45807</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45807</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44691</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>44509</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45218</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45680</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45539</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19615,7 +19615,7 @@
         <v>45114</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45558</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>45729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45688</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45791</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>46127</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>46162</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE245"/>
+  <dimension ref="A1:AE242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>45079</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2787-2024</t>
+          <t>A 30603-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45314</v>
+        <v>46210</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1898,21 +1898,133 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Kungsfiskare
+Ägretthäger
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2787-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45314</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Nordfladdermus
@@ -1920,144 +2032,32 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 30603-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Kungsfiskare
-Ägretthäger
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
         <v/>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45348</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>45729</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>46064</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46252</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>44741</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45322</v>
+        <v>45922</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4064,42 +4064,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45922</v>
+        <v>45322</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4169,35 +4169,35 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
         <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45098</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>44685</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>45005</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45231</v>
+        <v>46255</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -4700,46 +4700,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46255</v>
+        <v>45231</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -4805,39 +4805,39 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45594</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44504</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44686</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 51197-2021</t>
+          <t>A 54738-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44460</v>
+        <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 54738-2022</t>
+          <t>A 70982-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44883</v>
+        <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 70982-2021</t>
+          <t>A 5726-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44538</v>
+        <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5980,7 +5980,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 51120-2021</t>
+          <t>A 65203-2021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5990,14 +5990,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44461</v>
+        <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 5726-2022</t>
+          <t>A 6042-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6067,10 +6067,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44596</v>
+        <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6126,7 +6126,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 65203-2021</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6136,14 +6136,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44515</v>
+        <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 6042-2022</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6209,14 +6209,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44599</v>
+        <v>44621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>45532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44621</v>
+        <v>45406</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45406</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44585</v>
+        <v>45159</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45110</v>
+        <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6647,14 +6647,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45159</v>
+        <v>45113</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>7.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6710,7 +6710,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6724,10 +6724,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45751</v>
+        <v>45477</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6783,7 +6783,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6793,14 +6793,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45113</v>
+        <v>44848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.8</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45477</v>
+        <v>45583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6929,7 +6929,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6939,14 +6939,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45583</v>
+        <v>45001</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.9</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7002,7 +7002,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7016,10 +7016,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44848</v>
+        <v>45372</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7075,7 +7075,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7085,14 +7085,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45001</v>
+        <v>45646</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7148,7 +7148,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 17723-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45372</v>
+        <v>45037</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7221,7 +7221,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45646</v>
+        <v>45664</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45037</v>
+        <v>44672</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7367,7 +7367,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45664</v>
+        <v>45190</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44672</v>
+        <v>45323</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7513,7 +7513,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45190</v>
+        <v>45167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7586,7 +7586,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7600,10 +7600,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45323</v>
+        <v>45005</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7659,7 +7659,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45167</v>
+        <v>44596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44596</v>
+        <v>45012</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7805,7 +7805,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45005</v>
+        <v>45093</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7878,7 +7878,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45012</v>
+        <v>44741</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>4.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7951,7 +7951,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7965,10 +7965,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45093</v>
+        <v>44838</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8024,7 +8024,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8041,7 +8041,7 @@
         <v>44838</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>4.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8111,10 +8111,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44838</v>
+        <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4.9</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44741</v>
+        <v>45672</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8243,7 +8243,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45273</v>
+        <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8316,7 +8316,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45672</v>
+        <v>45061</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8345,8 +8345,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8389,7 +8394,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8403,10 +8408,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45061</v>
+        <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8418,13 +8423,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8484,7 +8484,7 @@
         <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
         <v>45405</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45342</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8773,10 +8773,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45698</v>
+        <v>45831</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8832,7 +8832,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45894</v>
+        <v>45698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8905,7 +8905,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8919,10 +8919,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45894</v>
+        <v>45919</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8978,7 +8978,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45318</v>
+        <v>46146</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9051,7 +9051,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9065,10 +9065,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45831</v>
+        <v>45318</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9081,7 +9081,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.4</v>
+        <v>6.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9124,7 +9124,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45093</v>
+        <v>45940</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9197,7 +9197,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9211,10 +9211,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45919</v>
+        <v>45093</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9287,7 +9287,7 @@
         <v>44981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45315</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9430,10 +9430,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45057</v>
+        <v>45775</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9489,7 +9489,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9503,10 +9503,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44838</v>
+        <v>46160</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9576,10 +9576,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46146</v>
+        <v>45057</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9635,7 +9635,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9649,10 +9649,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44852</v>
+        <v>46160</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>12.3</v>
+        <v>3.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9708,7 +9708,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9722,10 +9722,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44593</v>
+        <v>44838</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9738,7 +9738,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9781,7 +9781,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9795,10 +9795,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45940</v>
+        <v>45971</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9854,7 +9854,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9868,10 +9868,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45618</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9927,7 +9927,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9941,10 +9941,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45575</v>
+        <v>45974</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10000,7 +10000,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10014,10 +10014,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45240</v>
+        <v>44852</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>12.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10073,7 +10073,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10087,10 +10087,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45971</v>
+        <v>44593</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10146,7 +10146,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10160,10 +10160,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44573</v>
+        <v>45618</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10219,7 +10219,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45175</v>
+        <v>45982</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10292,7 +10292,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45539</v>
+        <v>45575</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10365,7 +10365,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10379,10 +10379,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45974</v>
+        <v>45947</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10395,7 +10395,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10438,7 +10438,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10452,10 +10452,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45974</v>
+        <v>46000</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10511,7 +10511,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45322</v>
+        <v>46000</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10584,7 +10584,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10598,10 +10598,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44879</v>
+        <v>45945</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10614,7 +10614,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10657,7 +10657,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10671,10 +10671,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45982</v>
+        <v>45240</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10730,7 +10730,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45231</v>
+        <v>45887</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10803,7 +10803,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10817,10 +10817,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45775</v>
+        <v>44573</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10876,7 +10876,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45574</v>
+        <v>45175</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10949,7 +10949,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10963,10 +10963,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44734</v>
+        <v>45539</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10978,13 +10978,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>9.300000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11027,7 +11022,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11041,10 +11036,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45748</v>
+        <v>45770</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11057,7 +11052,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11100,7 +11095,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11114,10 +11109,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46160</v>
+        <v>45945</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11130,7 +11125,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11173,7 +11168,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11187,10 +11182,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46160</v>
+        <v>45322</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11203,7 +11198,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11246,7 +11241,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11256,14 +11251,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44970</v>
+        <v>45978</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11276,7 +11271,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11319,7 +11314,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11333,10 +11328,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44685</v>
+        <v>46023</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11346,11 +11341,6 @@
       <c r="G126" t="inlineStr">
         <is>
           <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -11397,7 +11387,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11411,10 +11401,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45534</v>
+        <v>46023</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11427,7 +11417,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>7.6</v>
+        <v>0.7</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11470,7 +11460,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11484,10 +11474,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46000</v>
+        <v>45947</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11500,7 +11490,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11543,7 +11533,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11557,10 +11547,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44838</v>
+        <v>44879</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11573,7 +11563,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11616,7 +11606,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11630,10 +11620,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46000</v>
+        <v>45231</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11646,7 +11636,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11689,7 +11679,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11703,10 +11693,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44896</v>
+        <v>45574</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11719,7 +11709,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11762,7 +11752,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11776,10 +11766,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45887</v>
+        <v>46041</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11792,7 +11782,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11835,7 +11825,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11845,14 +11835,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44515</v>
+        <v>46038</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11865,7 +11855,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11908,7 +11898,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11922,10 +11912,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45770</v>
+        <v>44734</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11937,8 +11927,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11981,7 +11976,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11995,10 +11990,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45945</v>
+        <v>45748</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12011,7 +12006,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12054,7 +12049,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12064,14 +12059,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45741</v>
+        <v>44970</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12084,7 +12079,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12127,7 +12122,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12137,14 +12132,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45978</v>
+        <v>44685</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12156,8 +12151,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12200,7 +12200,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12214,10 +12214,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46023</v>
+        <v>46197</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12273,7 +12273,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12287,10 +12287,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46023</v>
+        <v>45534</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>7.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12360,10 +12360,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45947</v>
+        <v>44838</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12419,7 +12419,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12433,10 +12433,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44734</v>
+        <v>44896</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12448,13 +12448,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12497,7 +12492,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12507,14 +12502,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45338</v>
+        <v>46064</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12527,7 +12522,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12570,7 +12565,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12584,10 +12579,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45947</v>
+        <v>46198</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12600,7 +12595,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12643,7 +12638,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12653,14 +12648,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44888</v>
+        <v>44515</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12673,7 +12668,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12716,7 +12711,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12730,10 +12725,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44672</v>
+        <v>46064</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12746,7 +12741,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12789,7 +12784,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12803,10 +12798,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46041</v>
+        <v>45741</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12819,7 +12814,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12862,7 +12857,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12876,10 +12871,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45343</v>
+        <v>45987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12892,7 +12887,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12935,7 +12930,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12949,10 +12944,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45343</v>
+        <v>44734</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12964,8 +12959,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13008,7 +13008,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13022,10 +13022,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46038</v>
+        <v>45338</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13081,7 +13081,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45315</v>
+        <v>44888</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13154,7 +13154,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13168,10 +13168,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45945</v>
+        <v>44672</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13227,7 +13227,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13241,10 +13241,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45398</v>
+        <v>45343</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13300,7 +13300,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13314,10 +13314,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45005</v>
+        <v>45343</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13373,7 +13373,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13387,10 +13387,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45273</v>
+        <v>45315</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13446,7 +13446,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13456,14 +13456,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46064</v>
+        <v>45398</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13533,10 +13533,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44594</v>
+        <v>46205</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13592,7 +13592,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13606,10 +13606,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44874</v>
+        <v>46128</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13665,7 +13665,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13679,10 +13679,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46064</v>
+        <v>45005</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13748,14 +13748,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44908</v>
+        <v>46121</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13767,13 +13767,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13816,7 +13811,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13830,10 +13825,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45987</v>
+        <v>45273</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13846,7 +13841,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13889,7 +13884,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13903,10 +13898,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45755</v>
+        <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13919,7 +13914,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13962,7 +13957,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13976,10 +13971,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44838</v>
+        <v>44594</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13992,7 +13987,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14035,7 +14030,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14049,10 +14044,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44838</v>
+        <v>44874</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14065,7 +14060,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14108,7 +14103,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14122,10 +14117,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45191</v>
+        <v>44908</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14137,8 +14132,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14181,7 +14181,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45154</v>
+        <v>45231</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14268,10 +14268,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44860</v>
+        <v>45755</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14327,7 +14327,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14341,10 +14341,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45113</v>
+        <v>46209</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14400,7 +14400,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14414,10 +14414,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46197</v>
+        <v>44838</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14473,7 +14473,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46198</v>
+        <v>44838</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45216</v>
+        <v>45191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14619,7 +14619,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14633,10 +14633,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45216</v>
+        <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14706,10 +14706,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45450</v>
+        <v>45154</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14765,7 +14765,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45477</v>
+        <v>46255</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14838,7 +14838,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14852,10 +14852,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46128</v>
+        <v>44860</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14911,7 +14911,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14925,10 +14925,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45526</v>
+        <v>45113</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14994,14 +14994,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46121</v>
+        <v>46258</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15057,7 +15057,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15071,10 +15071,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45001</v>
+        <v>46258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15130,7 +15130,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15144,10 +15144,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46064</v>
+        <v>45216</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15203,7 +15203,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45539</v>
+        <v>45216</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15290,10 +15290,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46205</v>
+        <v>45450</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15349,7 +15349,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15363,10 +15363,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45051</v>
+        <v>45477</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15378,13 +15378,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15427,7 +15422,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15441,10 +15436,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45231</v>
+        <v>45526</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15457,7 +15452,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15500,7 +15495,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15514,10 +15509,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45685</v>
+        <v>46265</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15530,7 +15525,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15573,7 +15568,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15587,10 +15582,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46209</v>
+        <v>45001</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15603,7 +15598,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15646,7 +15641,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15660,10 +15655,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45700</v>
+        <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15676,7 +15671,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15719,7 +15714,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15729,14 +15724,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45261</v>
+        <v>46268</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15749,7 +15744,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15792,7 +15787,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15806,10 +15801,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46255</v>
+        <v>45539</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15822,7 +15817,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15865,7 +15860,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15879,10 +15874,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46255</v>
+        <v>46273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15895,7 +15890,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15938,7 +15933,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15952,10 +15947,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46258</v>
+        <v>46191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15968,7 +15963,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16011,7 +16006,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16025,10 +16020,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45041</v>
+        <v>45051</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16040,8 +16035,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16084,7 +16084,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16098,10 +16098,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45327</v>
+        <v>46279</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16157,7 +16157,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16171,10 +16171,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46258</v>
+        <v>45685</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16230,7 +16230,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16244,10 +16244,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44890</v>
+        <v>45700</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16303,7 +16303,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16317,10 +16317,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44984</v>
+        <v>46136</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16376,7 +16376,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16390,10 +16390,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44608</v>
+        <v>45261</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16449,7 +16449,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45574</v>
+        <v>46184</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16536,10 +16536,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46265</v>
+        <v>46177</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16595,7 +16595,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16609,10 +16609,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45728</v>
+        <v>46280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16668,7 +16668,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 38392-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16682,10 +16682,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46251</v>
+        <v>46282</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16741,7 +16741,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16755,10 +16755,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45236</v>
+        <v>46196</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16824,14 +16824,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46268</v>
+        <v>45041</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16901,10 +16901,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46273</v>
+        <v>45327</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16977,7 +16977,7 @@
         <v>46178</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17047,10 +17047,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46191</v>
+        <v>44890</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17106,7 +17106,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45568</v>
+        <v>44984</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17179,7 +17179,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17193,10 +17193,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44551</v>
+        <v>44608</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17208,13 +17208,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17257,7 +17252,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17271,10 +17266,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46279</v>
+        <v>45574</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17287,7 +17282,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17330,7 +17325,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17344,10 +17339,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46136</v>
+        <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17360,7 +17355,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17403,7 +17398,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17417,10 +17412,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46184</v>
+        <v>45236</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17433,7 +17428,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17476,7 +17471,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17490,10 +17485,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45600</v>
+        <v>45568</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17506,7 +17501,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17549,7 +17544,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17563,10 +17558,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45715</v>
+        <v>44551</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17578,8 +17573,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17622,7 +17622,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46177</v>
+        <v>45600</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17709,10 +17709,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45728</v>
+        <v>45715</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17768,7 +17768,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17782,10 +17782,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45791</v>
+        <v>45728</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17841,7 +17841,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 38003-2026</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17855,10 +17855,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46280</v>
+        <v>45791</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17931,7 +17931,7 @@
         <v>45645</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45471</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 38392-2026</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46282</v>
+        <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18138,7 +18138,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18155,7 +18155,7 @@
         <v>45594</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>6.3</v>
+        <v>28.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18225,10 +18225,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45594</v>
+        <v>45608</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>28.4</v>
+        <v>12.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18284,7 +18284,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18294,14 +18294,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46196</v>
+        <v>44911</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18357,7 +18357,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18367,14 +18367,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45608</v>
+        <v>44915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>12.3</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18430,7 +18430,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 51131-2021</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>44461</v>
+        <v>45804</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18503,7 +18503,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18513,14 +18513,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44911</v>
+        <v>45477</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18586,14 +18586,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44915</v>
+        <v>45709</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18649,7 +18649,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18663,10 +18663,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45804</v>
+        <v>45824</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18736,10 +18736,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45477</v>
+        <v>45820</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>0.9</v>
+        <v>3.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18795,7 +18795,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18809,10 +18809,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45709</v>
+        <v>45807</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18882,10 +18882,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45824</v>
+        <v>45807</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>8.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18941,24 +18941,24 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>S 2442-2022</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45820</v>
+        <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.8</v>
+        <v>12.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19014,24 +19014,24 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>S 4383-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45807</v>
+        <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>3.3</v>
+        <v>18.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19087,24 +19087,24 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>S 8937-2021</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45807</v>
+        <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>35.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -19160,7 +19160,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 2442-2022</t>
+          <t>S 3693-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -19174,10 +19174,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44691</v>
+        <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>12.4</v>
+        <v>35.7</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -19233,7 +19233,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 4383-2023</t>
+          <t>S 221-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -19247,10 +19247,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45265</v>
+        <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>18.9</v>
+        <v>13.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 8937-2021</t>
+          <t>S 3468-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -19320,10 +19320,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44509</v>
+        <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>35.9</v>
+        <v>10.2</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19379,7 +19379,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 3693-2023</t>
+          <t>S 2441-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19393,10 +19393,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45218</v>
+        <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>35.7</v>
+        <v>12</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19452,7 +19452,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 221-2025</t>
+          <t>S 3794-2024</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19462,14 +19462,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45680</v>
+        <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19481,8 +19481,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>13.8</v>
+        <v>3.2</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19525,7 +19530,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 3468-2024</t>
+          <t>S 792-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19539,10 +19544,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45539</v>
+        <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19555,7 +19560,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>10.2</v>
+        <v>12.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19598,7 +19603,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 2441-2023</t>
+          <t>S 310-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19612,10 +19617,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45114</v>
+        <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19628,7 +19633,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19671,7 +19676,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S 3794-2024</t>
+          <t>S 1522-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19681,14 +19686,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45558</v>
+        <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19700,13 +19705,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I240" t="n">
-        <v>3.2</v>
+        <v>30.6</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19749,7 +19749,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 792-2025</t>
+          <t>S 1063-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19763,10 +19763,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45729</v>
+        <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>12.9</v>
+        <v>23.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19819,10 +19819,10 @@
       </c>
       <c r="V241" s="2" t="inlineStr"/>
     </row>
-    <row r="242" ht="15" customHeight="1">
+    <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 310-2025</t>
+          <t>S 1492-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19836,10 +19836,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45688</v>
+        <v>46162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>16</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19891,225 +19891,6 @@
         <v>0</v>
       </c>
       <c r="V242" s="2" t="inlineStr"/>
-    </row>
-    <row r="243" ht="15" customHeight="1">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>S 1522-2025</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D243" s="1" t="n">
-        <v>45791</v>
-      </c>
-      <c r="E243" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I243" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="J243" t="n">
-        <v>0</v>
-      </c>
-      <c r="K243" t="n">
-        <v>0</v>
-      </c>
-      <c r="L243" t="n">
-        <v>0</v>
-      </c>
-      <c r="M243" t="n">
-        <v>0</v>
-      </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>0</v>
-      </c>
-      <c r="P243" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0</v>
-      </c>
-      <c r="S243" t="n">
-        <v>0</v>
-      </c>
-      <c r="T243" t="n">
-        <v>0</v>
-      </c>
-      <c r="U243" t="n">
-        <v>0</v>
-      </c>
-      <c r="V243" s="2" t="inlineStr"/>
-    </row>
-    <row r="244" ht="15" customHeight="1">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>S 1063-2026</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D244" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="E244" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I244" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="J244" t="n">
-        <v>0</v>
-      </c>
-      <c r="K244" t="n">
-        <v>0</v>
-      </c>
-      <c r="L244" t="n">
-        <v>0</v>
-      </c>
-      <c r="M244" t="n">
-        <v>0</v>
-      </c>
-      <c r="N244" t="n">
-        <v>0</v>
-      </c>
-      <c r="O244" t="n">
-        <v>0</v>
-      </c>
-      <c r="P244" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
-      <c r="S244" t="n">
-        <v>0</v>
-      </c>
-      <c r="T244" t="n">
-        <v>0</v>
-      </c>
-      <c r="U244" t="n">
-        <v>0</v>
-      </c>
-      <c r="V244" s="2" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>S 1492-2026</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D245" s="1" t="n">
-        <v>46162</v>
-      </c>
-      <c r="E245" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I245" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J245" t="n">
-        <v>0</v>
-      </c>
-      <c r="K245" t="n">
-        <v>0</v>
-      </c>
-      <c r="L245" t="n">
-        <v>0</v>
-      </c>
-      <c r="M245" t="n">
-        <v>0</v>
-      </c>
-      <c r="N245" t="n">
-        <v>0</v>
-      </c>
-      <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="P245" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0</v>
-      </c>
-      <c r="S245" t="n">
-        <v>0</v>
-      </c>
-      <c r="T245" t="n">
-        <v>0</v>
-      </c>
-      <c r="U245" t="n">
-        <v>0</v>
-      </c>
-      <c r="V245" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8315-2026</t>
+          <t>A 24278-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46064</v>
+        <v>45079</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1575,9 +1575,231 @@
         <v>5</v>
       </c>
       <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Spillkråka
+Sångsvan
+Trana</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 42692-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44832</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril
+Loppstarr
+Ängsstarr
+Bandpraktmossa
+Sankt pers nycklar</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42692-2022 artfynd.xlsx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42692-2022 karta.png", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42692-2022 georefererad karta.tif", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42692-2022 FSC-klagomål.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42692-2022 FSC-klagomål mail.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42692-2022 tillsynsbegäran.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42692-2022 tillsynsbegäran mail.docx", "A 42692-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 8315-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Småjungfrukam
@@ -1586,265 +1808,43 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 24278-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45079</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Spillkråka
-Sångsvan
-Trana</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 42692-2022</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44832</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Brunfläckig pärlemorfjäril
-Loppstarr
-Ängsstarr
-Bandpraktmossa
-Sankt pers nycklar</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42692-2022 artfynd.xlsx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42692-2022 karta.png", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42692-2022 georefererad karta.tif", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42692-2022 FSC-klagomål.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42692-2022 FSC-klagomål mail.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42692-2022 tillsynsbegäran.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42692-2022 tillsynsbegäran mail.docx", "A 42692-2022")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30603-2026</t>
+          <t>A 2787-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46210</v>
+        <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1898,21 +1898,129 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Nordfladdermus
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 30603-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Kungsfiskare
@@ -1920,151 +2028,43 @@
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2787-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45314</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Nordfladdermus
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30645-2022</t>
+          <t>A 7616-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44763</v>
+        <v>45348</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,259 +2130,259 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Kösa
+Åkerkulla
+Skogsödla</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 12111-2025</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45729</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tofsvipa
+Tornseglare
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 30645-2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>44763</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
 Nattviol</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 7616-2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45348</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Kösa
-Åkerkulla
-Skogsödla</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 12111-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45729</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tofsvipa
-Tornseglare
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2942-2024</t>
+          <t>A 38317-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45315</v>
+        <v>46282</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,20 +2854,20 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -2890,362 +2890,362 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 2942-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45315</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Skogsbräsma
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 33910-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Fällmossa
+Guldlockmossa</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 33910-2026 artfynd.xlsx", "A 33910-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 33910-2026 karta.png", "A 33910-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 33910-2026 georefererad karta.tif", "A 33910-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 33910-2026 FSC-klagomål.docx", "A 33910-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 33910-2026 FSC-klagomål mail.docx", "A 33910-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 33910-2026 tillsynsbegäran.docx", "A 33910-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 33910-2026 tillsynsbegäran mail.docx", "A 33910-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 8329-2026</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
+      <c r="D25" s="1" t="n">
         <v>46064</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>2.2</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>2</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U25" t="n">
         <v>2</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Spillkråka</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 33910-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46252</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Fällmossa
-Guldlockmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 33910-2026 artfynd.xlsx", "A 33910-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 33910-2026 karta.png", "A 33910-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 33910-2026 georefererad karta.tif", "A 33910-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 33910-2026 FSC-klagomål.docx", "A 33910-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 33910-2026 FSC-klagomål mail.docx", "A 33910-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 33910-2026 tillsynsbegäran.docx", "A 33910-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 33910-2026 tillsynsbegäran mail.docx", "A 33910-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 38317-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
         <v/>
       </c>
     </row>
@@ -3269,7 +3269,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 48926-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44741</v>
+        <v>45594</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>10.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3745,46 +3745,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45174</v>
+        <v>45231</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3854,42 +3854,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54753-2022</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44883</v>
+        <v>45322</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3919,23 +3919,23 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3959,42 +3959,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 54753-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45922</v>
+        <v>44883</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -4048,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4064,42 +4064,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45322</v>
+        <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4169,42 +4169,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61007-2024</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45098</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4233,28 +4233,23 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>10.3</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4266,7 +4261,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4279,42 +4274,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4328,10 +4323,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45098</v>
+        <v>45005</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4344,13 +4339,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.3</v>
+        <v>0.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4359,7 +4354,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4368,10 +4363,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4384,35 +4379,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
@@ -4436,7 +4431,7 @@
         <v>44685</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4529,7 +4524,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 61007-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4539,14 +4534,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45005</v>
+        <v>45645</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4558,18 +4553,23 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4599,42 +4599,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46255</v>
+        <v>44741</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4664,20 +4664,20 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4700,46 +4700,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45231</v>
+        <v>45174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4793,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4809,35 +4809,35 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48926-2024</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45594</v>
+        <v>46255</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10.8</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5023,42 +5023,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44504</v>
+        <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5088,20 +5088,20 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>37.2</v>
+        <v>20.3</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
@@ -5112,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5124,46 +5124,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>44504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>15.5</v>
+        <v>37.2</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5229,46 +5229,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44686</v>
+        <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>20.3</v>
+        <v>15.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5338,35 +5338,35 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44585</v>
+        <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6209,14 +6209,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44621</v>
+        <v>45405</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45532</v>
+        <v>45715</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45406</v>
+        <v>45755</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>45236</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45159</v>
+        <v>45471</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45751</v>
+        <v>45791</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6647,14 +6647,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45113</v>
+        <v>44734</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6666,8 +6666,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>7.8</v>
+        <v>0.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6710,7 +6715,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6724,10 +6729,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45477</v>
+        <v>44874</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6740,7 +6745,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6783,7 +6788,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6797,10 +6802,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44848</v>
+        <v>44908</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6810,6 +6815,11 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -6856,7 +6866,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6866,14 +6876,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45583</v>
+        <v>45645</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6885,8 +6895,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6929,7 +6944,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6939,14 +6954,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45001</v>
+        <v>45342</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6959,7 +6974,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7002,7 +7017,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7016,10 +7031,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45372</v>
+        <v>45728</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7075,7 +7090,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7089,10 +7104,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45646</v>
+        <v>44888</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7105,7 +7120,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7165,7 +7180,7 @@
         <v>45037</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7221,7 +7236,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7235,10 +7250,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45664</v>
+        <v>45600</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7251,7 +7266,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7294,7 +7309,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7308,10 +7323,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44672</v>
+        <v>44838</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7324,7 +7339,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7367,7 +7382,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7381,10 +7396,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45190</v>
+        <v>44838</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7397,7 +7412,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7440,7 +7455,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7454,10 +7469,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45323</v>
+        <v>44838</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7470,7 +7485,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7513,7 +7528,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7523,14 +7538,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45167</v>
+        <v>44515</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7543,7 +7558,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7586,7 +7601,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7600,10 +7615,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45005</v>
+        <v>44890</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7616,7 +7631,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>7.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7659,7 +7674,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7673,10 +7688,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44596</v>
+        <v>45700</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7689,7 +7704,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7732,7 +7747,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7746,10 +7761,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45012</v>
+        <v>45398</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7762,7 +7777,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7805,7 +7820,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7815,14 +7830,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45093</v>
+        <v>45406</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7835,7 +7850,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7878,7 +7893,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7892,10 +7907,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44741</v>
+        <v>44593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7908,7 +7923,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7951,7 +7966,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7965,10 +7980,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44838</v>
+        <v>45748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7981,7 +7996,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8024,7 +8039,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8038,10 +8053,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44838</v>
+        <v>45315</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8054,7 +8069,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8097,7 +8112,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8111,10 +8126,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45273</v>
+        <v>45093</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8127,7 +8142,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8170,7 +8185,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8184,10 +8199,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45672</v>
+        <v>45110</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8200,7 +8215,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8243,7 +8258,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8257,10 +8272,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45894</v>
+        <v>45477</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8273,7 +8288,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>7.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8316,7 +8331,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8330,10 +8345,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45061</v>
+        <v>45477</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8345,13 +8360,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8394,7 +8404,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8408,10 +8418,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45894</v>
+        <v>45594</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8424,7 +8434,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8467,7 +8477,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8481,10 +8491,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45477</v>
+        <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8497,7 +8507,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>12.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8540,7 +8550,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8554,10 +8564,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45405</v>
+        <v>45594</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8570,7 +8580,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>28.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8613,7 +8623,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8627,10 +8637,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45477</v>
+        <v>45751</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8643,7 +8653,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8686,7 +8696,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8700,10 +8710,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45342</v>
+        <v>45051</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8715,8 +8725,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8759,7 +8774,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8769,14 +8784,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45831</v>
+        <v>44911</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8789,7 +8804,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8832,7 +8847,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8846,10 +8861,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45698</v>
+        <v>45894</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8862,7 +8877,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8905,7 +8920,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8919,10 +8934,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45919</v>
+        <v>45894</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8935,7 +8950,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8978,7 +8993,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8992,10 +9007,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46146</v>
+        <v>45323</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9008,7 +9023,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9051,7 +9066,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9065,10 +9080,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45318</v>
+        <v>44848</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9081,7 +9096,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9124,7 +9139,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9138,10 +9153,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45940</v>
+        <v>44838</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9169,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9197,7 +9212,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9211,10 +9226,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45093</v>
+        <v>44838</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9242,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9270,7 +9285,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9284,10 +9299,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44981</v>
+        <v>45231</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9300,7 +9315,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9343,7 +9358,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9353,14 +9368,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45315</v>
+        <v>44915</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9373,7 +9388,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9416,7 +9431,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9430,10 +9445,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45775</v>
+        <v>45113</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9446,7 +9461,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9489,7 +9504,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9503,10 +9518,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46160</v>
+        <v>45664</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9519,7 +9534,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9562,7 +9577,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9576,10 +9591,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45057</v>
+        <v>44879</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9592,7 +9607,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9635,7 +9650,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9649,10 +9664,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46160</v>
+        <v>45831</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9665,7 +9680,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9708,7 +9723,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9722,10 +9737,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44838</v>
+        <v>45343</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9738,7 +9753,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9781,7 +9796,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9795,10 +9810,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45971</v>
+        <v>45343</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9811,7 +9826,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9854,7 +9869,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9868,10 +9883,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9884,7 +9899,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9927,7 +9942,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9941,10 +9956,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45974</v>
+        <v>45477</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9957,7 +9972,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10000,7 +10015,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10014,10 +10029,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44852</v>
+        <v>45318</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10030,7 +10045,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>12.3</v>
+        <v>6.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10073,7 +10088,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10087,10 +10102,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44593</v>
+        <v>45450</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10103,7 +10118,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10146,7 +10161,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10160,10 +10175,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45618</v>
+        <v>45919</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10176,7 +10191,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10219,7 +10234,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10233,10 +10248,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45982</v>
+        <v>45804</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10249,7 +10264,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10292,7 +10307,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10302,14 +10317,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45575</v>
+        <v>45113</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10322,7 +10337,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>7.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10365,7 +10380,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10379,10 +10394,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45947</v>
+        <v>45539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10395,7 +10410,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10438,7 +10453,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10448,14 +10463,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46000</v>
+        <v>44621</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10468,7 +10483,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10511,7 +10526,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10525,10 +10540,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46000</v>
+        <v>45477</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10541,7 +10556,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10584,7 +10599,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10598,10 +10613,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45945</v>
+        <v>45175</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10614,7 +10629,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10657,7 +10672,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10671,10 +10686,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45240</v>
+        <v>45167</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10687,7 +10702,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10730,7 +10745,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10744,10 +10759,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45887</v>
+        <v>45618</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10760,7 +10775,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10803,7 +10818,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10817,10 +10832,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44573</v>
+        <v>45741</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10833,7 +10848,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10876,7 +10891,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10890,10 +10905,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45175</v>
+        <v>44585</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10906,7 +10921,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10966,7 +10981,7 @@
         <v>45539</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11022,7 +11037,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11036,10 +11051,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45770</v>
+        <v>45940</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11052,7 +11067,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11095,7 +11110,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11109,10 +11124,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45945</v>
+        <v>45574</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11125,7 +11140,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11168,7 +11183,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11182,10 +11197,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45322</v>
+        <v>44896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11198,7 +11213,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11241,7 +11256,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11251,14 +11266,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45978</v>
+        <v>45001</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11271,7 +11286,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11314,7 +11329,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11328,10 +11343,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46023</v>
+        <v>44596</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11344,7 +11359,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11387,7 +11402,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11401,10 +11416,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46023</v>
+        <v>45159</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11460,7 +11475,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11470,14 +11485,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45947</v>
+        <v>44970</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11490,7 +11505,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11533,7 +11548,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11547,10 +11562,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44879</v>
+        <v>45583</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11563,7 +11578,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11606,7 +11621,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11620,10 +11635,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45231</v>
+        <v>44672</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11636,7 +11651,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11679,7 +11694,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11693,10 +11708,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45574</v>
+        <v>44981</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11709,7 +11724,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11752,7 +11767,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11766,10 +11781,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46041</v>
+        <v>44852</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11782,7 +11797,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>12.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11825,7 +11840,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11839,10 +11854,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46038</v>
+        <v>45315</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11855,7 +11870,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11898,7 +11913,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11912,10 +11927,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44734</v>
+        <v>45971</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11927,13 +11942,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11976,7 +11986,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11990,10 +12000,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45748</v>
+        <v>45005</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12006,7 +12016,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12049,7 +12059,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12059,14 +12069,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44970</v>
+        <v>45974</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12079,7 +12089,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12122,7 +12132,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12136,10 +12146,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44685</v>
+        <v>45974</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12151,13 +12161,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12200,7 +12205,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12214,10 +12219,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46197</v>
+        <v>44594</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12230,7 +12235,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12273,7 +12278,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12287,10 +12292,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45534</v>
+        <v>45728</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12303,7 +12308,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12346,7 +12351,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12360,10 +12365,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44838</v>
+        <v>45574</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12376,7 +12381,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12419,7 +12424,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12433,10 +12438,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44896</v>
+        <v>44838</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12449,7 +12454,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12492,7 +12497,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12502,14 +12507,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46064</v>
+        <v>44685</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12521,8 +12526,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>5.2</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12565,7 +12575,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12579,10 +12589,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46198</v>
+        <v>45012</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12595,7 +12605,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12638,7 +12648,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12648,14 +12658,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44515</v>
+        <v>45982</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12668,7 +12678,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12711,7 +12721,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12721,14 +12731,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46064</v>
+        <v>45001</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12741,7 +12751,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12784,7 +12794,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12798,10 +12808,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45741</v>
+        <v>45154</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12814,7 +12824,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12857,7 +12867,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12871,10 +12881,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45987</v>
+        <v>45575</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12887,7 +12897,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12930,7 +12940,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12944,10 +12954,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44734</v>
+        <v>44672</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12959,13 +12969,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13008,7 +13013,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13022,10 +13027,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45338</v>
+        <v>46023</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13038,7 +13043,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13081,7 +13086,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13095,10 +13100,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44888</v>
+        <v>46023</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13111,7 +13116,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13154,7 +13159,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13168,10 +13173,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44672</v>
+        <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13184,7 +13189,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13227,7 +13232,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13241,10 +13246,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45343</v>
+        <v>46000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13257,7 +13262,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13300,7 +13305,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13314,10 +13319,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45343</v>
+        <v>46000</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13330,7 +13335,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13373,7 +13378,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13387,10 +13392,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45315</v>
+        <v>44741</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13403,7 +13408,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13446,7 +13451,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13460,10 +13465,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45398</v>
+        <v>45887</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13476,7 +13481,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13519,7 +13524,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13533,10 +13538,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46205</v>
+        <v>45709</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13549,7 +13554,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13592,7 +13597,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13606,10 +13611,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46128</v>
+        <v>46038</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13622,7 +13627,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13665,7 +13670,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13679,10 +13684,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45005</v>
+        <v>45824</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13695,7 +13700,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13738,7 +13743,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13748,14 +13753,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46121</v>
+        <v>46041</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13768,7 +13773,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13811,7 +13816,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13825,10 +13830,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45273</v>
+        <v>45770</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13884,7 +13889,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13898,10 +13903,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46064</v>
+        <v>45945</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13914,7 +13919,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13957,7 +13962,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13971,10 +13976,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44594</v>
+        <v>44573</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13987,7 +13992,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.9</v>
+        <v>4.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14030,7 +14035,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14044,10 +14049,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44874</v>
+        <v>45273</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14060,7 +14065,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14103,7 +14108,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14113,14 +14118,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44908</v>
+        <v>45978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14132,13 +14137,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14181,7 +14181,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45231</v>
+        <v>45191</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14268,10 +14268,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45755</v>
+        <v>45190</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14327,7 +14327,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14341,10 +14341,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46209</v>
+        <v>45534</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14400,7 +14400,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14410,14 +14410,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>44838</v>
+        <v>46064</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14473,7 +14473,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44838</v>
+        <v>46178</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45191</v>
+        <v>45261</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14619,7 +14619,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14633,10 +14633,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46255</v>
+        <v>46184</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14692,7 +14692,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14706,10 +14706,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45154</v>
+        <v>45005</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14765,7 +14765,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46255</v>
+        <v>46064</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14838,7 +14838,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14852,10 +14852,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44860</v>
+        <v>46265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14911,7 +14911,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14925,10 +14925,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45113</v>
+        <v>45987</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46258</v>
+        <v>46136</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15057,7 +15057,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15071,10 +15071,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15144,10 +15144,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45216</v>
+        <v>45820</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15203,7 +15203,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45216</v>
+        <v>44860</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15290,10 +15290,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45450</v>
+        <v>45061</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15305,8 +15305,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15349,7 +15354,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15363,10 +15368,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45477</v>
+        <v>45807</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15379,7 +15384,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15422,7 +15427,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15436,10 +15441,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45526</v>
+        <v>45240</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15452,7 +15457,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15495,7 +15500,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15509,10 +15514,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46265</v>
+        <v>45807</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15525,7 +15530,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15568,7 +15573,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15582,10 +15587,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45001</v>
+        <v>46128</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15598,7 +15603,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15641,7 +15646,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15651,14 +15656,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46251</v>
+        <v>46121</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15671,7 +15676,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15714,7 +15719,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15724,14 +15729,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46268</v>
+        <v>44734</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15743,8 +15748,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15787,7 +15797,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15801,10 +15811,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45539</v>
+        <v>45322</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15817,7 +15827,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15860,7 +15870,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15874,10 +15884,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46273</v>
+        <v>45526</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15890,7 +15900,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15933,7 +15943,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15947,10 +15957,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46191</v>
+        <v>46064</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15963,7 +15973,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16006,7 +16016,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16020,10 +16030,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45051</v>
+        <v>45338</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16035,13 +16045,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16084,7 +16089,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16098,10 +16103,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46279</v>
+        <v>45057</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16114,7 +16119,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16157,7 +16162,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16171,10 +16176,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45685</v>
+        <v>44984</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16187,7 +16192,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16230,7 +16235,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16244,10 +16249,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45700</v>
+        <v>45532</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16303,7 +16308,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16317,10 +16322,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46136</v>
+        <v>45273</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16333,7 +16338,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16376,7 +16381,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16390,10 +16395,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45261</v>
+        <v>45216</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16406,7 +16411,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16449,7 +16454,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16463,10 +16468,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46184</v>
+        <v>45216</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16522,7 +16527,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16536,10 +16541,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46177</v>
+        <v>45372</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16552,7 +16557,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16595,7 +16600,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 38003-2026</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16609,10 +16614,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46280</v>
+        <v>45041</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16625,7 +16630,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.6</v>
+        <v>0.2</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16668,7 +16673,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 38392-2026</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16682,10 +16687,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46282</v>
+        <v>45327</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16698,7 +16703,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16741,7 +16746,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16755,10 +16760,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46196</v>
+        <v>45093</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16771,7 +16776,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16814,7 +16819,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16828,10 +16833,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45041</v>
+        <v>45685</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16844,7 +16849,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16887,7 +16892,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16901,10 +16906,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45327</v>
+        <v>45646</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16917,7 +16922,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16960,7 +16965,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16974,10 +16979,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46178</v>
+        <v>45672</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16990,7 +16995,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17033,7 +17038,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17047,10 +17052,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44890</v>
+        <v>45477</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17063,7 +17068,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>7.7</v>
+        <v>0.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17106,7 +17111,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17120,10 +17125,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44984</v>
+        <v>46146</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17136,7 +17141,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17179,7 +17184,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17193,10 +17198,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44608</v>
+        <v>44551</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17208,8 +17213,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17252,7 +17262,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17266,10 +17276,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45574</v>
+        <v>45568</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17282,7 +17292,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17325,7 +17335,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17339,10 +17349,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45728</v>
+        <v>46160</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17355,7 +17365,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17398,7 +17408,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17412,10 +17422,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45236</v>
+        <v>46160</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17428,7 +17438,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17471,7 +17481,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17485,10 +17495,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45568</v>
+        <v>45775</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17501,7 +17511,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17544,7 +17554,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17558,10 +17568,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>44551</v>
+        <v>45947</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17573,13 +17583,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17622,7 +17627,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17636,10 +17641,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45600</v>
+        <v>45945</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17652,7 +17657,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17695,7 +17700,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17709,10 +17714,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45715</v>
+        <v>46197</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17725,7 +17730,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17768,7 +17773,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17782,10 +17787,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45728</v>
+        <v>46198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17798,7 +17803,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17841,7 +17846,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17855,10 +17860,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45791</v>
+        <v>46205</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17871,7 +17876,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17914,7 +17919,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17924,14 +17929,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45645</v>
+        <v>46209</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17943,13 +17948,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18006,10 +18006,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45471</v>
+        <v>45231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18065,7 +18065,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45594</v>
+        <v>46255</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18138,7 +18138,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18152,10 +18152,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45594</v>
+        <v>46258</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>28.4</v>
+        <v>1.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18225,10 +18225,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45608</v>
+        <v>46255</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>12.3</v>
+        <v>1.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18284,7 +18284,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18294,14 +18294,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44911</v>
+        <v>46258</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18357,7 +18357,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18371,10 +18371,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44915</v>
+        <v>46268</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18430,7 +18430,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45804</v>
+        <v>46251</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18503,7 +18503,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18517,10 +18517,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45477</v>
+        <v>46273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18590,10 +18590,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45709</v>
+        <v>46191</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18649,7 +18649,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18663,10 +18663,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45824</v>
+        <v>46177</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18736,10 +18736,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45820</v>
+        <v>46280</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18795,7 +18795,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 38392-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18809,10 +18809,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45807</v>
+        <v>46282</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18882,10 +18882,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45807</v>
+        <v>46196</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24278-2023</t>
+          <t>A 8315-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45079</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1575,9 +1575,122 @@
         <v>5</v>
       </c>
       <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Småjungfrukam
+Spillkråka
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 24278-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
@@ -1586,111 +1699,111 @@
 Trana</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 42692-2022</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>44832</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>5.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S12" t="n">
         <v>5</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U12" t="n">
         <v>4</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Brunfläckig pärlemorfjäril
 Loppstarr
@@ -1699,145 +1812,32 @@
 Sankt pers nycklar</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42692-2022 artfynd.xlsx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42692-2022 karta.png", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42692-2022 georefererad karta.tif", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42692-2022 FSC-klagomål.docx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42692-2022 FSC-klagomål mail.docx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42692-2022 tillsynsbegäran.docx", "A 42692-2022")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42692-2022 tillsynsbegäran mail.docx", "A 42692-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 8315-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Småjungfrukam
-Spillkråka
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
         <v/>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
         <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>46210</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 7616-2024</t>
+          <t>A 30645-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45348</v>
+        <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,259 +2130,259 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>3</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Murgröna
+Nattviol</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 7616-2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Kösa
 Åkerkulla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 12111-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45729</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>3.7</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>2</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Tofsvipa
 Tornseglare
 Gröngöling</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 30645-2022</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44763</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Murgröna
-Nattviol</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 38317-2026</t>
+          <t>A 2942-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46282</v>
+        <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,19 +2854,19 @@
         </is>
       </c>
       <c r="I22" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2878,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>2</v>
@@ -2890,472 +2890,472 @@
         <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsbräsma
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8329-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 38317-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gullpudra</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 2942-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 24597-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>45315</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="D25" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J25" t="n">
         <v>2</v>
       </c>
-      <c r="T23" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsbräsma
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare</t>
+        </is>
+      </c>
+      <c r="W25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24597-2026 artfynd.xlsx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="X25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24597-2026 karta.png", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="Y25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24597-2026 georefererad karta.tif", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AA25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24597-2026 FSC-klagomål.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AB25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24597-2026 FSC-klagomål mail.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AC25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24597-2026 tillsynsbegäran.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AD25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24597-2026 tillsynsbegäran mail.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24597-2026 prioriterade fågelarter.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 33910-2026</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D24" s="1" t="n">
+      <c r="D26" s="1" t="n">
         <v>46252</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>2</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Fällmossa
 Guldlockmossa</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 33910-2026 artfynd.xlsx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 33910-2026 karta.png", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 33910-2026 georefererad karta.tif", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 33910-2026 FSC-klagomål.docx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 33910-2026 FSC-klagomål mail.docx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 33910-2026 tillsynsbegäran.docx", "A 33910-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 33910-2026 tillsynsbegäran mail.docx", "A 33910-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 8329-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A 24597-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4</v>
-      </c>
-      <c r="U26" t="n">
-        <v>4</v>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare</t>
-        </is>
-      </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24597-2026 artfynd.xlsx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24597-2026 karta.png", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24597-2026 georefererad karta.tif", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24597-2026 FSC-klagomål.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24597-2026 FSC-klagomål mail.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24597-2026 tillsynsbegäran.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24597-2026 tillsynsbegäran mail.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24597-2026 prioriterade fågelarter.docx", "A 24597-2026")</f>
         <v/>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 48926-2024</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45594</v>
+        <v>44741</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10.8</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3745,46 +3745,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45231</v>
+        <v>45174</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3854,42 +3854,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 54753-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45322</v>
+        <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3934,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3959,42 +3959,42 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54753-2022</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44883</v>
+        <v>45922</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4024,20 +4024,20 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -4048,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4064,42 +4064,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45922</v>
+        <v>45322</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4169,42 +4169,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 61007-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45098</v>
+        <v>45645</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4233,23 +4233,28 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>10.3</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4261,7 +4266,7 @@
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4274,42 +4279,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4323,10 +4328,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45005</v>
+        <v>45098</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4339,23 +4344,23 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
@@ -4363,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4379,35 +4384,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
@@ -4431,7 +4436,7 @@
         <v>44685</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4524,7 +4529,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61007-2024</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4534,14 +4539,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45645</v>
+        <v>45005</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4553,22 +4558,17 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4599,42 +4599,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44741</v>
+        <v>46255</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4688,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4700,46 +4700,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45174</v>
+        <v>45231</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4793,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4809,35 +4809,35 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
         <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 48926-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46255</v>
+        <v>45594</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4983,20 +4983,20 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>10.8</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
@@ -5007,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5023,42 +5023,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44686</v>
+        <v>44504</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>20.3</v>
+        <v>37.2</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5112,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5124,46 +5124,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44504</v>
+        <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>37.2</v>
+        <v>15.5</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5229,46 +5229,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44858</v>
+        <v>44686</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,20 +5298,20 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5338,35 +5338,35 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45698</v>
+        <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45405</v>
+        <v>45532</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6282,14 +6282,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45715</v>
+        <v>44621</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45755</v>
+        <v>45406</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45236</v>
+        <v>45110</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6491,7 +6491,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6505,10 +6505,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45471</v>
+        <v>45159</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6578,10 +6578,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45791</v>
+        <v>45751</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6637,7 +6637,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6647,14 +6647,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44734</v>
+        <v>45113</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6666,13 +6666,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>7.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6715,7 +6710,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6729,10 +6724,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44874</v>
+        <v>44848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6745,7 +6740,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6788,7 +6783,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6802,10 +6797,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44908</v>
+        <v>45477</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6817,13 +6812,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6866,7 +6856,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6876,14 +6866,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45645</v>
+        <v>45583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6895,13 +6885,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6944,7 +6929,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6954,14 +6939,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45342</v>
+        <v>45001</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6974,7 +6959,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.1</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7017,7 +7002,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7031,10 +7016,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45728</v>
+        <v>45372</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7090,7 +7075,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7104,10 +7089,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44888</v>
+        <v>45646</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7120,7 +7105,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7180,7 +7165,7 @@
         <v>45037</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7236,7 +7221,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7250,10 +7235,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45600</v>
+        <v>45664</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7266,7 +7251,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7309,7 +7294,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7323,10 +7308,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44838</v>
+        <v>44672</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7339,7 +7324,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7382,7 +7367,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7396,10 +7381,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44838</v>
+        <v>45190</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7412,7 +7397,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7455,7 +7440,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7469,10 +7454,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44838</v>
+        <v>45323</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7485,7 +7470,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7528,7 +7513,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7538,14 +7523,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44515</v>
+        <v>45167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7558,7 +7543,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7601,7 +7586,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7615,10 +7600,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44890</v>
+        <v>44596</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7631,7 +7616,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7674,7 +7659,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7688,10 +7673,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45700</v>
+        <v>45005</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7704,7 +7689,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7747,7 +7732,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7761,10 +7746,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45398</v>
+        <v>45012</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7777,7 +7762,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7820,7 +7805,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7830,14 +7815,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45406</v>
+        <v>45093</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7850,7 +7835,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7893,7 +7878,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7907,10 +7892,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44593</v>
+        <v>44838</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7923,7 +7908,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7966,7 +7951,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7980,10 +7965,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45748</v>
+        <v>44838</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7996,7 +7981,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8039,7 +8024,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8053,10 +8038,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45315</v>
+        <v>44741</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8069,7 +8054,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8112,7 +8097,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8126,10 +8111,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45093</v>
+        <v>45273</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8142,7 +8127,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8185,7 +8170,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8199,10 +8184,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45110</v>
+        <v>45672</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8215,7 +8200,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8258,7 +8243,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8272,10 +8257,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45477</v>
+        <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8288,7 +8273,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8331,7 +8316,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8345,10 +8330,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45477</v>
+        <v>45894</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8361,7 +8346,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8404,7 +8389,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8418,10 +8403,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45594</v>
+        <v>45061</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8433,8 +8418,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>6.3</v>
+        <v>1.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8477,7 +8467,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8491,10 +8481,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45608</v>
+        <v>45477</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8507,7 +8497,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>12.3</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8550,7 +8540,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8564,10 +8554,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45594</v>
+        <v>45405</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8580,7 +8570,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>28.4</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8623,7 +8613,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8637,10 +8627,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45751</v>
+        <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8653,7 +8643,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8696,7 +8686,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8710,10 +8700,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45051</v>
+        <v>45342</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8725,13 +8715,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8774,7 +8759,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8784,14 +8769,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44911</v>
+        <v>45831</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8804,7 +8789,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8847,7 +8832,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8861,10 +8846,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45894</v>
+        <v>45698</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8877,7 +8862,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8920,7 +8905,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8934,10 +8919,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45894</v>
+        <v>45919</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8950,7 +8935,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8993,7 +8978,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9007,10 +8992,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45323</v>
+        <v>45318</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9023,7 +9008,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>6.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9066,7 +9051,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9080,10 +9065,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44848</v>
+        <v>45940</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9096,7 +9081,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9139,7 +9124,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9153,10 +9138,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44838</v>
+        <v>45093</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9169,7 +9154,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9212,7 +9197,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9226,10 +9211,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44838</v>
+        <v>44981</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9242,7 +9227,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9285,7 +9270,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9299,10 +9284,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45231</v>
+        <v>45315</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9315,7 +9300,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9358,7 +9343,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9368,14 +9353,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44915</v>
+        <v>45057</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9388,7 +9373,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9431,7 +9416,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9445,10 +9430,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45113</v>
+        <v>44838</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9461,7 +9446,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9504,7 +9489,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9518,10 +9503,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45664</v>
+        <v>44852</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9534,7 +9519,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9577,7 +9562,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9591,10 +9576,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44879</v>
+        <v>45971</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9607,7 +9592,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9650,7 +9635,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9664,10 +9649,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45831</v>
+        <v>44593</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9680,7 +9665,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9723,7 +9708,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9737,10 +9722,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45343</v>
+        <v>45618</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9753,7 +9738,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9796,7 +9781,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9810,10 +9795,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45343</v>
+        <v>45974</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9826,7 +9811,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9869,7 +9854,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9883,10 +9868,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44608</v>
+        <v>45974</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9899,7 +9884,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9942,7 +9927,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9956,10 +9941,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45477</v>
+        <v>45575</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9972,7 +9957,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10015,7 +10000,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10029,10 +10014,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45318</v>
+        <v>45982</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10045,7 +10030,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10088,7 +10073,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10102,10 +10087,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45450</v>
+        <v>46146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10118,7 +10103,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10161,7 +10146,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10175,10 +10160,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45919</v>
+        <v>45240</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10191,7 +10176,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10234,7 +10219,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10248,10 +10233,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45804</v>
+        <v>46000</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10264,7 +10249,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10307,7 +10292,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10317,14 +10302,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45113</v>
+        <v>46000</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10337,7 +10322,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7.8</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10380,7 +10365,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10394,10 +10379,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45539</v>
+        <v>44573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10410,7 +10395,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10453,7 +10438,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10463,14 +10448,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44621</v>
+        <v>45175</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10483,7 +10468,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10526,7 +10511,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10540,10 +10525,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45477</v>
+        <v>45539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10556,7 +10541,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10599,7 +10584,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10613,10 +10598,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45175</v>
+        <v>45887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10629,7 +10614,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10672,7 +10657,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10686,10 +10671,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45167</v>
+        <v>45322</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10702,7 +10687,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10745,7 +10730,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10759,10 +10744,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45618</v>
+        <v>45775</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10775,7 +10760,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10818,7 +10803,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10832,10 +10817,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45741</v>
+        <v>44879</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10848,7 +10833,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10891,7 +10876,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10905,10 +10890,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44585</v>
+        <v>45770</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10921,7 +10906,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10964,7 +10949,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10978,10 +10963,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45539</v>
+        <v>45945</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10994,7 +10979,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11037,7 +11022,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11051,10 +11036,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45940</v>
+        <v>46160</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11067,7 +11052,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11110,7 +11095,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11120,14 +11105,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45574</v>
+        <v>45978</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11140,7 +11125,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11183,7 +11168,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11197,10 +11182,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44896</v>
+        <v>46023</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11213,7 +11198,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11256,7 +11241,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11270,10 +11255,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45001</v>
+        <v>46023</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11286,7 +11271,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11329,7 +11314,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11343,10 +11328,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44596</v>
+        <v>45947</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11359,7 +11344,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11402,7 +11387,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11416,10 +11401,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45159</v>
+        <v>46160</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11432,7 +11417,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11475,7 +11460,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11485,14 +11470,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44970</v>
+        <v>45231</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11505,7 +11490,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11548,7 +11533,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11562,10 +11547,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45583</v>
+        <v>45574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11578,7 +11563,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11621,7 +11606,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11635,10 +11620,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44672</v>
+        <v>44734</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11650,8 +11635,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11694,7 +11684,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11708,10 +11698,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44981</v>
+        <v>45748</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11724,7 +11714,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11767,7 +11757,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11781,10 +11771,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44852</v>
+        <v>46041</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11797,7 +11787,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>12.3</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11840,7 +11830,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11854,10 +11844,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45315</v>
+        <v>46038</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11870,7 +11860,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11913,7 +11903,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11923,14 +11913,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45971</v>
+        <v>44970</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11943,7 +11933,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11986,7 +11976,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12000,10 +11990,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45005</v>
+        <v>44685</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12015,8 +12005,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12059,7 +12054,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12073,10 +12068,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45974</v>
+        <v>45534</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12089,7 +12084,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.7</v>
+        <v>7.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12132,7 +12127,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12146,10 +12141,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45974</v>
+        <v>44838</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12162,7 +12157,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12205,7 +12200,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12219,10 +12214,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44594</v>
+        <v>44896</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12235,7 +12230,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12278,7 +12273,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12288,14 +12283,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45728</v>
+        <v>44515</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12308,7 +12303,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12351,7 +12346,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12365,10 +12360,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45574</v>
+        <v>45741</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12424,7 +12419,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12434,14 +12429,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44838</v>
+        <v>46064</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12454,7 +12449,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12497,7 +12492,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12511,10 +12506,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44685</v>
+        <v>44734</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12528,11 +12523,11 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12575,7 +12570,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12589,10 +12584,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45012</v>
+        <v>45338</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12605,7 +12600,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12648,7 +12643,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12662,10 +12657,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45982</v>
+        <v>45947</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12678,7 +12673,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12721,7 +12716,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12731,14 +12726,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45001</v>
+        <v>46064</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12751,7 +12746,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12794,7 +12789,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12808,10 +12803,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45154</v>
+        <v>45987</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12824,7 +12819,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12867,7 +12862,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12881,10 +12876,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45575</v>
+        <v>44888</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12897,7 +12892,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12940,7 +12935,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 50553-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12954,10 +12949,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44672</v>
+        <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12970,7 +12965,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13013,7 +13008,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13027,10 +13022,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46023</v>
+        <v>44672</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13043,7 +13038,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13086,7 +13081,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13100,10 +13095,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46023</v>
+        <v>45343</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13116,7 +13111,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13159,7 +13154,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13173,10 +13168,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45947</v>
+        <v>45343</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13189,7 +13184,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13232,7 +13227,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13246,10 +13241,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46000</v>
+        <v>45315</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13262,7 +13257,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>5.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13305,7 +13300,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13319,10 +13314,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46000</v>
+        <v>45398</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13335,7 +13330,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13378,7 +13373,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13392,10 +13387,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44741</v>
+        <v>45005</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13408,7 +13403,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13451,7 +13446,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13465,10 +13460,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45887</v>
+        <v>45273</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13481,7 +13476,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13524,7 +13519,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13538,10 +13533,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45709</v>
+        <v>46128</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13554,7 +13549,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13597,7 +13592,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13607,14 +13602,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46038</v>
+        <v>46121</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13670,7 +13665,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13684,10 +13679,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45824</v>
+        <v>44594</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13700,7 +13695,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>8.199999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13743,7 +13738,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13757,10 +13752,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46041</v>
+        <v>44874</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13773,7 +13768,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13816,7 +13811,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13830,10 +13825,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45770</v>
+        <v>44908</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13845,8 +13840,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13889,7 +13889,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13903,10 +13903,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45945</v>
+        <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13919,7 +13919,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13962,7 +13962,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13976,10 +13976,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44573</v>
+        <v>46197</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14035,7 +14035,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14049,10 +14049,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45273</v>
+        <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14108,7 +14108,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 28849-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14118,14 +14118,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45978</v>
+        <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14181,7 +14181,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14195,10 +14195,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45191</v>
+        <v>44838</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14254,7 +14254,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14268,10 +14268,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45190</v>
+        <v>44838</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14341,10 +14341,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45534</v>
+        <v>45191</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14400,7 +14400,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14410,14 +14410,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46064</v>
+        <v>45154</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14473,7 +14473,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46178</v>
+        <v>44860</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45261</v>
+        <v>45113</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14619,7 +14619,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14633,10 +14633,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46184</v>
+        <v>46205</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14692,7 +14692,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14706,10 +14706,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45005</v>
+        <v>45216</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14765,7 +14765,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14779,10 +14779,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46064</v>
+        <v>45216</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14838,7 +14838,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14852,10 +14852,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46265</v>
+        <v>45450</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14911,7 +14911,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14925,10 +14925,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45987</v>
+        <v>45477</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14984,7 +14984,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14998,10 +14998,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46136</v>
+        <v>45231</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15057,7 +15057,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15071,10 +15071,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46279</v>
+        <v>45526</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15144,10 +15144,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45820</v>
+        <v>46209</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15203,7 +15203,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44860</v>
+        <v>46255</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15290,10 +15290,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45061</v>
+        <v>45001</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15305,13 +15305,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15354,7 +15349,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15368,10 +15363,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45807</v>
+        <v>46255</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15384,7 +15379,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15427,7 +15422,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15441,10 +15436,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45240</v>
+        <v>46258</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15457,7 +15452,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15500,7 +15495,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15514,10 +15509,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45807</v>
+        <v>45539</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15530,7 +15525,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15573,7 +15568,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15587,10 +15582,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46128</v>
+        <v>46258</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15603,7 +15598,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15646,7 +15641,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15656,14 +15651,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46121</v>
+        <v>45051</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15675,8 +15670,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15719,7 +15719,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15733,10 +15733,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44734</v>
+        <v>45685</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15748,13 +15748,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>9.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15797,7 +15792,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15811,10 +15806,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45322</v>
+        <v>45700</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15827,7 +15822,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15870,7 +15865,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15884,10 +15879,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45526</v>
+        <v>46251</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15900,7 +15895,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15943,7 +15938,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15957,10 +15952,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46064</v>
+        <v>45261</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15973,7 +15968,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16016,7 +16011,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16026,14 +16021,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45338</v>
+        <v>46268</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16046,7 +16041,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16089,7 +16084,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16103,10 +16098,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45057</v>
+        <v>46273</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16119,7 +16114,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16162,7 +16157,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16176,10 +16171,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44984</v>
+        <v>46191</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16192,7 +16187,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16235,7 +16230,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16249,10 +16244,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45532</v>
+        <v>45041</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16265,7 +16260,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16308,7 +16303,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16322,10 +16317,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45273</v>
+        <v>45327</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16338,7 +16333,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16381,7 +16376,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16395,10 +16390,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45216</v>
+        <v>44890</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16411,7 +16406,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.5</v>
+        <v>7.7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16454,7 +16449,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16468,10 +16463,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45216</v>
+        <v>44984</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16484,7 +16479,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16527,7 +16522,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16541,10 +16536,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45372</v>
+        <v>44608</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16557,7 +16552,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16600,7 +16595,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16614,10 +16609,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45041</v>
+        <v>46177</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16630,7 +16625,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16673,7 +16668,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16687,10 +16682,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45327</v>
+        <v>45574</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16703,7 +16698,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16746,7 +16741,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16760,10 +16755,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45093</v>
+        <v>45728</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16776,7 +16771,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16819,7 +16814,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16833,10 +16828,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45685</v>
+        <v>46280</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16849,7 +16844,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16892,7 +16887,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 38392-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16906,10 +16901,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45646</v>
+        <v>46282</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16922,7 +16917,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16965,7 +16960,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16979,10 +16974,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45672</v>
+        <v>45236</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16995,7 +16990,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17038,7 +17033,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17052,10 +17047,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45477</v>
+        <v>46196</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17068,7 +17063,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.3</v>
+        <v>4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17111,7 +17106,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17125,10 +17120,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46146</v>
+        <v>46178</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17141,7 +17136,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17184,7 +17179,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17198,10 +17193,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>44551</v>
+        <v>45568</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17213,13 +17208,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17262,7 +17252,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17276,10 +17266,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45568</v>
+        <v>44551</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17291,8 +17281,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17335,7 +17330,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17349,10 +17344,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46160</v>
+        <v>45600</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17365,7 +17360,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17408,7 +17403,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17422,10 +17417,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46160</v>
+        <v>45715</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17438,7 +17433,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17481,7 +17476,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17495,10 +17490,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45775</v>
+        <v>45728</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17511,7 +17506,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17554,7 +17549,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17568,10 +17563,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45947</v>
+        <v>45791</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17584,7 +17579,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17627,7 +17622,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 50553-2025</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17637,14 +17632,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45945</v>
+        <v>45645</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17656,8 +17651,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17700,7 +17700,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17714,10 +17714,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46197</v>
+        <v>46279</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17773,7 +17773,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28849-2026</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17787,10 +17787,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46198</v>
+        <v>45471</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17860,10 +17860,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46205</v>
+        <v>45594</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17919,7 +17919,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17933,10 +17933,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46209</v>
+        <v>46184</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18006,10 +18006,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45231</v>
+        <v>46136</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18065,7 +18065,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18079,10 +18079,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46255</v>
+        <v>45594</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18095,7 +18095,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>0.9</v>
+        <v>28.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18138,7 +18138,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18152,10 +18152,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18211,7 +18211,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18225,10 +18225,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46255</v>
+        <v>45608</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.2</v>
+        <v>12.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18284,7 +18284,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18294,14 +18294,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46258</v>
+        <v>44911</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18357,7 +18357,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18371,10 +18371,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46268</v>
+        <v>44915</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18430,7 +18430,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46251</v>
+        <v>45804</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18503,7 +18503,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18517,10 +18517,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46273</v>
+        <v>45477</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18576,7 +18576,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18590,10 +18590,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46191</v>
+        <v>45709</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18649,7 +18649,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18663,10 +18663,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46177</v>
+        <v>45824</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18722,7 +18722,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 38003-2026</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18736,10 +18736,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46280</v>
+        <v>45820</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18752,7 +18752,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18795,7 +18795,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 38392-2026</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18809,10 +18809,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46282</v>
+        <v>45807</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18882,10 +18882,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46196</v>
+        <v>45807</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8315-2026</t>
+          <t>A 24278-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46064</v>
+        <v>45079</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1575,9 +1575,122 @@
         <v>5</v>
       </c>
       <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Björktrast
+Rödvingetrast
+Spillkråka
+Sångsvan
+Trana</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 8315-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Småjungfrukam
@@ -1586,149 +1699,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 24278-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45079</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Björktrast
-Rödvingetrast
-Spillkråka
-Sångsvan
-Trana</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 2787-2024</t>
+          <t>A 30603-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45314</v>
+        <v>46210</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1898,21 +1898,133 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Kungsfiskare
+Ägretthäger
+Fiskgjuse</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 2787-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45314</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>4</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Brunlångöra
 Nordfladdermus
@@ -1920,144 +2032,32 @@
 Vattenfladdermus</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 30603-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Kungsfiskare
-Ägretthäger
-Fiskgjuse</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
         <v/>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 7616-2024</t>
+          <t>A 12111-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45348</v>
+        <v>45729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2237,152 +2237,152 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Tofsvipa
+Tornseglare
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 7616-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45348</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Kösa
 Åkerkulla
 Skogsödla</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 7616-2024 artfynd.xlsx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 7616-2024 karta.png", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 7616-2024 georefererad karta.tif", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 7616-2024 FSC-klagomål.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 7616-2024 FSC-klagomål mail.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 7616-2024 tillsynsbegäran.docx", "A 7616-2024")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 7616-2024 tillsynsbegäran mail.docx", "A 7616-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 12111-2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45729</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tofsvipa
-Tornseglare
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
         <v/>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 2942-2024</t>
+          <t>A 8329-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45315</v>
+        <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,31 +2854,31 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.2</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2894,153 +2894,153 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Grönsångare
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 2942-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45315</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Skogsbräsma
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 8329-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 38317-2026</t>
+          <t>A 24597-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46282</v>
+        <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>5.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3097,159 +3097,159 @@
         <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24597-2026 artfynd.xlsx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24597-2026 karta.png", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24597-2026 georefererad karta.tif", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24597-2026 FSC-klagomål.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24597-2026 FSC-klagomål mail.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24597-2026 tillsynsbegäran.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24597-2026 tillsynsbegäran mail.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24597-2026 prioriterade fågelarter.docx", "A 24597-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 38317-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gullpudra</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 24597-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46170</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>4</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24597-2026 artfynd.xlsx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24597-2026 karta.png", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24597-2026 georefererad karta.tif", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24597-2026 FSC-klagomål.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24597-2026 FSC-klagomål mail.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24597-2026 tillsynsbegäran.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24597-2026 tillsynsbegäran mail.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24597-2026 prioriterade fågelarter.docx", "A 24597-2026")</f>
         <v/>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         <v>46252</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44741</v>
+        <v>45231</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3733,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3749,42 +3749,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45174</v>
+        <v>45322</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3814,22 +3814,22 @@
         </is>
       </c>
       <c r="I31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3854,35 +3854,35 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 48926-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45922</v>
+        <v>45594</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>10.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
@@ -4068,38 +4068,38 @@
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45322</v>
+        <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4141,10 +4141,10 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4169,42 +4169,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 61007-2024</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45645</v>
+        <v>45005</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4233,22 +4233,17 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4263,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4279,42 +4274,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Kungsfiskare</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 61007-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4324,14 +4319,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45098</v>
+        <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4343,23 +4338,28 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>10.3</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4384,42 +4384,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Kungsfiskare</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 61007-2024 artfynd.xlsx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 61007-2024 karta.png", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 61007-2024 georefererad karta.tif", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 61007-2024 FSC-klagomål.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 61007-2024 FSC-klagomål mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 61007-2024 tillsynsbegäran.docx", "A 61007-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 61007-2024 tillsynsbegäran mail.docx", "A 61007-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 18348-2022</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44685</v>
+        <v>46255</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4448,13 +4448,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4490,46 +4485,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Klotullört</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4543,10 +4538,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45005</v>
+        <v>45098</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4559,23 +4554,23 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.3</v>
+        <v>10.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
@@ -4583,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4599,42 +4594,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 18348-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4648,10 +4643,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46255</v>
+        <v>44685</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4663,8 +4658,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4700,46 +4700,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klotullört</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45231</v>
+        <v>44741</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>5.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4793,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4809,42 +4809,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22569-2024</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45447</v>
+        <v>45174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4874,20 +4874,20 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4910,50 +4910,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 22569-2024 artfynd.xlsx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 22569-2024 karta.png", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 22569-2024 georefererad karta.tif", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 22569-2024 FSC-klagomål.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 22569-2024 FSC-klagomål mail.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 22569-2024 tillsynsbegäran.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 22569-2024 tillsynsbegäran mail.docx", "A 22569-2024")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 22569-2024 prioriterade fågelarter.docx", "A 22569-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 48926-2024</t>
+          <t>A 22569-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4967,10 +4963,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45594</v>
+        <v>45447</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4983,10 +4979,10 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10.8</v>
+        <v>2.2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -4995,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5007,10 +5003,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5023,42 +5019,46 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 22569-2024 artfynd.xlsx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 22569-2024 karta.png", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 22569-2024 georefererad karta.tif", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 22569-2024 FSC-klagomål.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 22569-2024 FSC-klagomål mail.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 22569-2024 tillsynsbegäran.docx", "A 22569-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 22569-2024 tillsynsbegäran mail.docx", "A 22569-2024")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 22569-2024 prioriterade fågelarter.docx", "A 22569-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44504</v>
+        <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5088,20 +5088,20 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>37.2</v>
+        <v>20.3</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
@@ -5112,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5124,46 +5124,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44858</v>
+        <v>44504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>15.5</v>
+        <v>37.2</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5229,46 +5229,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44686</v>
+        <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>20.3</v>
+        <v>15.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5338,35 +5338,35 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3480-2022</t>
+          <t>A 6174-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44585</v>
+        <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 35801-2024</t>
+          <t>A 15905-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6213,10 +6213,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45532</v>
+        <v>45405</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10007-2022</t>
+          <t>A 54798-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6282,14 +6282,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44621</v>
+        <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16110-2024</t>
+          <t>A 25934-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6355,14 +6355,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45406</v>
+        <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6374,8 +6374,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6418,7 +6423,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 30087-2023</t>
+          <t>A 53455-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6432,10 +6437,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45110</v>
+        <v>44874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6448,7 +6453,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6491,7 +6496,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 37675-2023</t>
+          <t>A 59702-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6505,10 +6510,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45159</v>
+        <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6520,8 +6525,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6564,7 +6574,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16434-2025</t>
+          <t>A 56596-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6578,10 +6588,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45751</v>
+        <v>44888</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6594,7 +6604,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6637,7 +6647,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31092-2023</t>
+          <t>A 6760-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6647,14 +6657,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45113</v>
+        <v>45342</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6667,7 +6677,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6710,7 +6720,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47136-2022</t>
+          <t>A 17723-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6724,10 +6734,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44848</v>
+        <v>45037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6740,7 +6750,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6783,7 +6793,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 28385-2024</t>
+          <t>A 56231-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6797,10 +6807,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45477</v>
+        <v>44890</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6813,7 +6823,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>7.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6856,7 +6866,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46777-2024</t>
+          <t>A 43891-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6870,10 +6880,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45583</v>
+        <v>44838</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6886,7 +6896,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6929,7 +6939,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12855-2023</t>
+          <t>A 14849-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6939,14 +6949,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45001</v>
+        <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6959,7 +6969,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7002,7 +7012,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11379-2024</t>
+          <t>A 15657-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7016,10 +7026,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45372</v>
+        <v>45748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7032,7 +7042,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7075,7 +7085,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61377-2024</t>
+          <t>A 28332-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7089,10 +7099,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45646</v>
+        <v>45477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7105,7 +7115,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>7.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7148,7 +7158,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 28352-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7162,10 +7172,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45037</v>
+        <v>45477</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7178,7 +7188,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7221,7 +7231,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 531-2025</t>
+          <t>A 4120-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7235,10 +7245,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45664</v>
+        <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7251,7 +7261,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7294,7 +7304,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16665-2022</t>
+          <t>A 50513-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7308,10 +7318,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44672</v>
+        <v>45945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7324,7 +7334,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7367,7 +7377,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 44960-2023</t>
+          <t>A 47136-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7381,10 +7391,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45190</v>
+        <v>44848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7397,7 +7407,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7440,7 +7450,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 4120-2024</t>
+          <t>A 56941-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7450,14 +7460,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45323</v>
+        <v>45978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7470,7 +7480,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7513,7 +7523,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39603-2023</t>
+          <t>A 43871-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7527,10 +7537,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45167</v>
+        <v>44838</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7543,7 +7553,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7586,7 +7596,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 5730-2022</t>
+          <t>A 43884-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7600,10 +7610,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44596</v>
+        <v>44838</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7616,7 +7626,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7659,7 +7669,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13437-2023</t>
+          <t>A 3-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7673,10 +7683,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45005</v>
+        <v>46023</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7689,7 +7699,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7732,7 +7742,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 14515-2023</t>
+          <t>A 11-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7746,10 +7756,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45012</v>
+        <v>46023</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7762,7 +7772,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7805,7 +7815,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 26757-2023</t>
+          <t>A 51232-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7819,10 +7829,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45093</v>
+        <v>45947</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7835,7 +7845,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7878,7 +7888,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 43877-2022</t>
+          <t>A 30951-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7892,10 +7902,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44838</v>
+        <v>45113</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7908,7 +7918,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7951,7 +7961,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 43897-2022</t>
+          <t>A 48921-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7965,10 +7975,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44838</v>
+        <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7981,7 +7991,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8024,7 +8034,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 27219-2022</t>
+          <t>A 52281-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8038,10 +8048,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44741</v>
+        <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8054,7 +8064,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4.3</v>
+        <v>12.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8097,7 +8107,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 63268-2023</t>
+          <t>A 48909-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8111,10 +8121,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45273</v>
+        <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8127,7 +8137,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>28.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8170,7 +8180,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 2114-2025</t>
+          <t>A 60425-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8180,14 +8190,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45672</v>
+        <v>44911</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8200,7 +8210,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8243,7 +8253,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 40083-2025</t>
+          <t>A 53460-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8257,10 +8267,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45894</v>
+        <v>44879</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8273,7 +8283,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8316,7 +8326,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40090-2025</t>
+          <t>A 2852-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8330,10 +8340,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45894</v>
+        <v>46038</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8346,7 +8356,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8389,7 +8399,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21066-2023</t>
+          <t>A 40083-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8403,10 +8413,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45061</v>
+        <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8418,13 +8428,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8467,7 +8472,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 28352-2024</t>
+          <t>A 40090-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8481,10 +8486,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45477</v>
+        <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8497,7 +8502,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8540,7 +8545,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 3182-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8554,10 +8559,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45405</v>
+        <v>46041</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8613,7 +8618,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 28332-2024</t>
+          <t>A 61087-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8623,14 +8628,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45477</v>
+        <v>44915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8643,7 +8648,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>7.5</v>
+        <v>1.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8686,7 +8691,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8696,14 +8701,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45342</v>
+        <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8716,7 +8721,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8759,7 +8764,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 30730-2025</t>
+          <t>A 37082-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8773,10 +8778,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45831</v>
+        <v>45539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8789,7 +8794,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8832,7 +8837,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 30730-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45698</v>
+        <v>45831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8862,7 +8867,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8905,7 +8910,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45164-2025</t>
+          <t>A 14554-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8919,10 +8924,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45919</v>
+        <v>45741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8935,7 +8940,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8978,7 +8983,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 3407-2024</t>
+          <t>A 8290-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8988,14 +8993,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45318</v>
+        <v>46064</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9008,7 +9013,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9051,7 +9056,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 49780-2025</t>
+          <t>A 25749-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9065,10 +9070,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45940</v>
+        <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9081,7 +9086,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9124,7 +9129,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26764-2023</t>
+          <t>A 45164-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45093</v>
+        <v>45919</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9159,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9197,7 +9202,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 10452-2023</t>
+          <t>A 44739-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9211,10 +9216,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44981</v>
+        <v>45574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9232,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9270,7 +9275,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 2950-2024</t>
+          <t>A 57461-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45315</v>
+        <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9300,7 +9305,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9343,7 +9348,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 20512-2023</t>
+          <t>A 8296-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45057</v>
+        <v>46064</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9373,7 +9378,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9416,7 +9421,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43996-2022</t>
+          <t>A 58807-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9430,10 +9435,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44838</v>
+        <v>45987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9446,7 +9451,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9489,7 +9494,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 47222-2022</t>
+          <t>A 28189-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44852</v>
+        <v>45477</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9519,7 +9524,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>12.3</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9562,7 +9567,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 55347-2025</t>
+          <t>A 49780-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9576,10 +9581,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45971</v>
+        <v>45940</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9592,7 +9597,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9635,7 +9640,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 4928-2022</t>
+          <t>A 7306-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9645,14 +9650,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44593</v>
+        <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9665,7 +9670,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9708,7 +9713,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 54711-2024</t>
+          <t>A 46777-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9722,10 +9727,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45618</v>
+        <v>45583</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9738,7 +9743,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9781,7 +9786,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 56304-2025</t>
+          <t>A 16663-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9795,10 +9800,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45974</v>
+        <v>44672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9854,7 +9859,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56307-2025</t>
+          <t>A 10452-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9868,10 +9873,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45974</v>
+        <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9884,7 +9889,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9927,7 +9932,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 45092-2024</t>
+          <t>A 47222-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9941,10 +9946,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45575</v>
+        <v>44852</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9957,7 +9962,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>12.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10000,7 +10005,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57982-2025</t>
+          <t>A 2950-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10014,10 +10019,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45982</v>
+        <v>45315</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10030,7 +10035,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10073,7 +10078,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 21229-2026</t>
+          <t>A 13432-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10087,10 +10092,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46146</v>
+        <v>45005</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10103,7 +10108,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10146,7 +10151,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57428-2023</t>
+          <t>A 18696-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10160,10 +10165,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45240</v>
+        <v>46128</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10176,7 +10181,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10219,7 +10224,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 61169-2025</t>
+          <t>A 17693-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10229,14 +10234,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46000</v>
+        <v>46121</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10249,7 +10254,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10292,7 +10297,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 61175-2025</t>
+          <t>A 55347-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10306,10 +10311,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46000</v>
+        <v>45971</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10322,7 +10327,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10365,7 +10370,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 1475-2022</t>
+          <t>A 14515-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10379,10 +10384,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44573</v>
+        <v>45012</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10395,7 +10400,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10438,7 +10443,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 41623-2023</t>
+          <t>A 12855-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10448,14 +10453,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45175</v>
+        <v>45001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10468,7 +10473,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10511,7 +10516,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 37074-2024</t>
+          <t>A 56304-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10525,10 +10530,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45539</v>
+        <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10541,7 +10546,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10584,7 +10589,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 38813-2025</t>
+          <t>A 56307-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10598,10 +10603,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45887</v>
+        <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10614,7 +10619,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10657,7 +10662,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 3940-2024</t>
+          <t>A 45092-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10671,10 +10676,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45322</v>
+        <v>45575</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10687,7 +10692,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10730,7 +10735,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 20381-2025</t>
+          <t>A 8305-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10744,10 +10749,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45775</v>
+        <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10760,7 +10765,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10803,7 +10808,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53460-2022</t>
+          <t>A 57982-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10817,10 +10822,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44879</v>
+        <v>45982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10833,7 +10838,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10876,7 +10881,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19629-2025</t>
+          <t>A 61169-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10890,10 +10895,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45770</v>
+        <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10906,7 +10911,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10949,7 +10954,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 50513-2025</t>
+          <t>A 61175-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10963,10 +10968,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45945</v>
+        <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10979,7 +10984,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11022,7 +11027,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 22966-2026</t>
+          <t>A 38813-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11036,10 +11041,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46160</v>
+        <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11052,7 +11057,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11095,7 +11100,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 56941-2025</t>
+          <t>A 19629-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11105,14 +11110,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45978</v>
+        <v>45770</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11125,7 +11130,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11168,7 +11173,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3-2026</t>
+          <t>A 16969-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11182,10 +11187,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46023</v>
+        <v>45755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11198,7 +11203,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11241,7 +11246,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 11-2026</t>
+          <t>A 43877-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11255,10 +11260,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46023</v>
+        <v>44838</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11271,7 +11276,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11314,7 +11319,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 51232-2025</t>
+          <t>A 43897-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11328,10 +11333,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45947</v>
+        <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11344,7 +11349,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>4.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11387,7 +11392,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 22964-2026</t>
+          <t>A 65200-2021</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11397,14 +11402,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46160</v>
+        <v>44515</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11417,7 +11422,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11460,7 +11465,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53807-2023</t>
+          <t>A 6589-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11474,10 +11479,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45231</v>
+        <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11533,7 +11538,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 44728-2024</t>
+          <t>A 21229-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11547,10 +11552,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45574</v>
+        <v>46146</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11563,7 +11568,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11606,7 +11611,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26033-2022</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11616,14 +11621,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44734</v>
+        <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11635,13 +11640,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>9.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11684,7 +11684,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 15657-2025</t>
+          <t>A 4928-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11698,10 +11698,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45748</v>
+        <v>44593</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11757,7 +11757,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 3182-2026</t>
+          <t>A 2935-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11771,10 +11771,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46041</v>
+        <v>45315</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>5.4</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11830,7 +11830,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 2852-2026</t>
+          <t>A 26764-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11844,10 +11844,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46038</v>
+        <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11903,7 +11903,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7306-2023</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11913,14 +11913,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44970</v>
+        <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.2</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11976,7 +11976,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 18345-2022</t>
+          <t>A 22966-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11990,10 +11990,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44685</v>
+        <v>46160</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12005,13 +12005,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12054,7 +12049,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 36211-2024</t>
+          <t>A 22964-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12068,10 +12063,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45534</v>
+        <v>46160</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12084,7 +12079,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>7.6</v>
+        <v>3.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12127,7 +12122,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 43891-2022</t>
+          <t>A 8478-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12141,10 +12136,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44838</v>
+        <v>45709</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12157,7 +12152,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12200,7 +12195,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57461-2022</t>
+          <t>A 29285-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12214,10 +12209,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44896</v>
+        <v>45824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12230,7 +12225,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12273,7 +12268,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 65200-2021</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12283,14 +12278,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44515</v>
+        <v>45751</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12303,7 +12298,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12346,7 +12341,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 14554-2025</t>
+          <t>A 19633-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12360,10 +12355,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45741</v>
+        <v>45051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12375,8 +12370,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12419,7 +12419,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8290-2026</t>
+          <t>A 20381-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12429,14 +12429,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46064</v>
+        <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12492,7 +12492,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 28830-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12506,10 +12506,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44734</v>
+        <v>45820</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12521,13 +12521,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12570,7 +12565,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 6440-2024</t>
+          <t>A 53807-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12584,10 +12579,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45338</v>
+        <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12600,7 +12595,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12643,7 +12638,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51235-2025</t>
+          <t>A 26590-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12657,10 +12652,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45947</v>
+        <v>45807</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12673,7 +12668,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12716,7 +12711,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 8296-2026</t>
+          <t>A 26591-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12730,10 +12725,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46064</v>
+        <v>45807</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12746,7 +12741,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12789,7 +12784,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58807-2025</t>
+          <t>A 531-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12803,10 +12798,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45987</v>
+        <v>45664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12819,7 +12814,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12862,7 +12857,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 51235-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12876,10 +12871,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44888</v>
+        <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12892,7 +12887,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12952,7 +12947,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13008,7 +13003,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 16663-2022</t>
+          <t>A 6941-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13022,10 +13017,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44672</v>
+        <v>45343</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13038,7 +13033,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13081,7 +13076,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6941-2024</t>
+          <t>A 6944-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13098,7 +13093,7 @@
         <v>45343</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13111,7 +13106,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13154,7 +13149,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 6944-2024</t>
+          <t>A 7782-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13168,10 +13163,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45343</v>
+        <v>44608</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13184,7 +13179,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13227,7 +13222,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 2935-2024</t>
+          <t>A 28335-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13241,10 +13236,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45315</v>
+        <v>45477</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13257,7 +13252,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.4</v>
+        <v>3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13300,7 +13295,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 14849-2024</t>
+          <t>A 3407-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13314,10 +13309,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45398</v>
+        <v>45318</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13330,7 +13325,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13373,7 +13368,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 13432-2023</t>
+          <t>A 23005-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13387,10 +13382,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45005</v>
+        <v>45450</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13403,7 +13398,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13446,7 +13441,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 63139-2023</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13456,14 +13451,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45273</v>
+        <v>44621</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13476,7 +13471,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13519,7 +13514,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 18696-2026</t>
+          <t>A 41623-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13533,10 +13528,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46128</v>
+        <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13549,7 +13544,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13592,7 +13587,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 17693-2026</t>
+          <t>A 39603-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13602,14 +13597,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46121</v>
+        <v>45167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13622,7 +13617,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13665,7 +13660,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 5138-2022</t>
+          <t>A 54711-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13679,10 +13674,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44594</v>
+        <v>45618</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13695,7 +13690,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13738,7 +13733,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13752,10 +13747,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44874</v>
+        <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13768,7 +13763,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13811,7 +13806,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 37074-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13825,10 +13820,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44908</v>
+        <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13840,13 +13835,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13889,7 +13879,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8305-2026</t>
+          <t>A 28597-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13903,10 +13893,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46064</v>
+        <v>46197</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13919,7 +13909,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13962,7 +13952,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28597-2026</t>
+          <t>A 12833-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13976,10 +13966,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46197</v>
+        <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13992,7 +13982,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14035,7 +14025,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 16969-2025</t>
+          <t>A 5730-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14049,10 +14039,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45755</v>
+        <v>44596</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14065,7 +14055,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14125,7 +14115,7 @@
         <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14181,7 +14171,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 43871-2022</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14195,10 +14185,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44838</v>
+        <v>45159</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14211,7 +14201,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14254,7 +14244,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43884-2022</t>
+          <t>A 29867-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14268,10 +14258,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44838</v>
+        <v>46205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14284,7 +14274,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14327,7 +14317,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45349-2023</t>
+          <t>A 30339-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -14341,10 +14331,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45191</v>
+        <v>46209</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14400,7 +14390,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 36884-2023</t>
+          <t>A 53848-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14414,10 +14404,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45154</v>
+        <v>45231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14430,7 +14420,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14473,7 +14463,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 50196-2022</t>
+          <t>A 34495-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14487,10 +14477,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44860</v>
+        <v>46255</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14503,7 +14493,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14546,7 +14536,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30951-2023</t>
+          <t>A 34670-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14560,10 +14550,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45113</v>
+        <v>46258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14576,7 +14566,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14619,7 +14609,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 29867-2026</t>
+          <t>A 34494-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14633,10 +14623,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46205</v>
+        <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14649,7 +14639,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14692,7 +14682,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 50330-2023</t>
+          <t>A 5138-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14706,10 +14696,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45216</v>
+        <v>44594</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14722,7 +14712,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14765,7 +14755,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 50332-2023</t>
+          <t>A 12025-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14779,10 +14769,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45216</v>
+        <v>45728</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14795,7 +14785,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14838,7 +14828,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 23005-2024</t>
+          <t>A 44728-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14852,10 +14842,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45450</v>
+        <v>45574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14868,7 +14858,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14911,7 +14901,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28335-2024</t>
+          <t>A 43996-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14925,10 +14915,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45477</v>
+        <v>44838</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14941,7 +14931,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14984,7 +14974,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 53848-2023</t>
+          <t>A 18345-2022</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14998,10 +14988,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45231</v>
+        <v>44685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15013,8 +15003,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15057,7 +15052,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 34704-2024</t>
+          <t>A 34870-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15071,10 +15066,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45526</v>
+        <v>46258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15087,7 +15082,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15130,7 +15125,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 30339-2026</t>
+          <t>A 36884-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15144,10 +15139,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46209</v>
+        <v>45154</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15160,7 +15155,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15203,7 +15198,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 34495-2026</t>
+          <t>A 16665-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15217,10 +15212,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46255</v>
+        <v>44672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15233,7 +15228,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -15276,7 +15271,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 12833-2023</t>
+          <t>A 27219-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -15290,10 +15285,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45001</v>
+        <v>44741</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15306,7 +15301,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -15349,7 +15344,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34494-2026</t>
+          <t>A 36392-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -15359,14 +15354,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46255</v>
+        <v>46268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15379,7 +15374,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15422,7 +15417,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 34870-2026</t>
+          <t>A 34075-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15436,10 +15431,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15452,7 +15447,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15495,7 +15490,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37082-2024</t>
+          <t>A 37057-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15509,10 +15504,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45539</v>
+        <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15525,7 +15520,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15568,7 +15563,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 34670-2026</t>
+          <t>A 1475-2022</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15582,10 +15577,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46258</v>
+        <v>44573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15598,7 +15593,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>4.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15641,7 +15636,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 19633-2023</t>
+          <t>A 27723-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15655,10 +15650,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45051</v>
+        <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15670,13 +15665,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15719,7 +15709,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 4245-2025</t>
+          <t>A 63139-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15733,10 +15723,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45685</v>
+        <v>45273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15749,7 +15739,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15792,7 +15782,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 6589-2025</t>
+          <t>A 25559-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15806,10 +15796,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45700</v>
+        <v>46177</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15822,7 +15812,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15865,7 +15855,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 34075-2026</t>
+          <t>A 38003-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15879,10 +15869,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46251</v>
+        <v>46280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15895,7 +15885,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15938,7 +15928,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 61011-2023</t>
+          <t>A 45349-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15952,10 +15942,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45261</v>
+        <v>45191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15968,7 +15958,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16011,7 +16001,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36392-2026</t>
+          <t>A 44960-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16021,14 +16011,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46268</v>
+        <v>45190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16041,7 +16031,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16084,7 +16074,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37057-2026</t>
+          <t>A 38392-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16098,10 +16088,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46273</v>
+        <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16157,7 +16147,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 27723-2026</t>
+          <t>A 36211-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16171,10 +16161,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46191</v>
+        <v>45534</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16187,7 +16177,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16230,7 +16220,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 18246-2023</t>
+          <t>A 28223-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16244,10 +16234,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45041</v>
+        <v>46196</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16260,7 +16250,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0.2</v>
+        <v>4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -16303,7 +16293,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 4501-2024</t>
+          <t>A 61011-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -16317,10 +16307,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45327</v>
+        <v>45261</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16333,7 +16323,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16376,7 +16366,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 13437-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16390,10 +16380,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44890</v>
+        <v>45005</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16406,7 +16396,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16449,7 +16439,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 9701-2023</t>
+          <t>A 25795-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16463,10 +16453,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44984</v>
+        <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16479,7 +16469,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16522,7 +16512,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 7782-2022</t>
+          <t>A 27368-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16536,10 +16526,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44608</v>
+        <v>46184</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16552,7 +16542,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16595,7 +16585,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 25559-2026</t>
+          <t>A 20329-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16609,10 +16599,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46177</v>
+        <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16625,7 +16615,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16668,7 +16658,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 44739-2024</t>
+          <t>A 37758-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16682,10 +16672,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45574</v>
+        <v>46279</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16698,7 +16688,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16741,7 +16731,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12025-2025</t>
+          <t>A 35642-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16755,10 +16745,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45728</v>
+        <v>46265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16771,7 +16761,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16814,7 +16804,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 38003-2026</t>
+          <t>A 50196-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16828,10 +16818,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46280</v>
+        <v>44860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16844,7 +16834,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16887,7 +16877,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 38392-2026</t>
+          <t>A 21066-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16901,10 +16891,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46282</v>
+        <v>45061</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16916,8 +16906,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16960,7 +16955,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 57428-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16974,10 +16969,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45236</v>
+        <v>45240</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16990,7 +16985,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17033,7 +17028,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 28223-2026</t>
+          <t>A 26033-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17047,10 +17042,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46196</v>
+        <v>44734</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17062,8 +17057,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17106,7 +17106,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 25795-2026</t>
+          <t>A 3940-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17120,10 +17120,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46178</v>
+        <v>45322</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17179,7 +17179,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 43469-2024</t>
+          <t>A 34704-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17193,10 +17193,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45568</v>
+        <v>45526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -17252,7 +17252,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 73544-2021</t>
+          <t>A 6440-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -17266,10 +17266,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>44551</v>
+        <v>45338</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17281,13 +17281,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -17330,7 +17325,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 50250-2024</t>
+          <t>A 20512-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -17344,10 +17339,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45600</v>
+        <v>45057</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17360,7 +17355,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17403,7 +17398,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 9466-2025</t>
+          <t>A 9701-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17417,10 +17412,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45715</v>
+        <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17433,7 +17428,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>4.5</v>
+        <v>0.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17476,7 +17471,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 12028-2025</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17490,10 +17485,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45728</v>
+        <v>45532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17506,7 +17501,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17549,7 +17544,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 23116-2025</t>
+          <t>A 63268-2023</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17563,10 +17558,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45791</v>
+        <v>45273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17579,7 +17574,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17622,7 +17617,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 61019-2024</t>
+          <t>A 50330-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17632,14 +17627,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45645</v>
+        <v>45216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17651,13 +17646,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17700,7 +17690,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 37758-2026</t>
+          <t>A 50332-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17714,10 +17704,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46279</v>
+        <v>45216</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17730,7 +17720,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17773,7 +17763,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 27251-2024</t>
+          <t>A 11379-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17787,10 +17777,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45471</v>
+        <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17803,7 +17793,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17846,7 +17836,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 48921-2024</t>
+          <t>A 18246-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17860,10 +17850,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45594</v>
+        <v>45041</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17876,7 +17866,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>6.3</v>
+        <v>0.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17919,7 +17909,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 27368-2026</t>
+          <t>A 4501-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17933,10 +17923,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46184</v>
+        <v>45327</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17949,7 +17939,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17992,7 +17982,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 20329-2026</t>
+          <t>A 26757-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18006,10 +17996,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46136</v>
+        <v>45093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18022,7 +18012,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18065,7 +18055,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 48909-2024</t>
+          <t>A 4245-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18079,10 +18069,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45594</v>
+        <v>45685</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18095,7 +18085,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>28.4</v>
+        <v>0.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18138,7 +18128,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 35642-2026</t>
+          <t>A 61377-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18152,10 +18142,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46265</v>
+        <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18168,7 +18158,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -18211,7 +18201,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 52281-2024</t>
+          <t>A 2114-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -18225,10 +18215,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45608</v>
+        <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18241,7 +18231,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>12.3</v>
+        <v>1.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -18284,7 +18274,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 60425-2022</t>
+          <t>A 28385-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -18294,14 +18284,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>44911</v>
+        <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18314,7 +18304,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -18357,7 +18347,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 61087-2022</t>
+          <t>A 73544-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18367,14 +18357,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>44915</v>
+        <v>44551</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18386,8 +18376,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18430,7 +18425,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 25749-2025</t>
+          <t>A 43469-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18444,10 +18439,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45804</v>
+        <v>45568</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18460,7 +18455,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18503,7 +18498,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 28189-2024</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18517,10 +18512,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45477</v>
+        <v>45715</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18533,7 +18528,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18576,7 +18571,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 8478-2025</t>
+          <t>A 27251-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18590,10 +18585,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45709</v>
+        <v>45471</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18606,7 +18601,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18649,7 +18644,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 29285-2025</t>
+          <t>A 23116-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18663,10 +18658,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45824</v>
+        <v>45791</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18679,7 +18674,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18722,7 +18717,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28830-2025</t>
+          <t>A 61019-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18732,14 +18727,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45820</v>
+        <v>45645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18751,8 +18746,13 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I227" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18795,7 +18795,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 26590-2025</t>
+          <t>A 12028-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18809,10 +18809,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45807</v>
+        <v>45728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18868,7 +18868,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 26591-2025</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18882,10 +18882,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45807</v>
+        <v>45600</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>3.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18958,7 +18958,7 @@
         <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45079</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>46210</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45314</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45348</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45315</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>46282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>46252</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45231</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45322</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45594</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45005</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46255</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45098</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>44685</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44741</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45447</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45405</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44888</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45342</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44890</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44838</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45477</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44838</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44838</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>46023</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>46023</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45947</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45113</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44911</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44879</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46038</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>46041</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>46064</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45919</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46064</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45477</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45940</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45583</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>44852</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45315</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45005</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>46128</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46121</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45971</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45012</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45575</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45770</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>45755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44838</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44515</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>46146</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44593</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45315</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46160</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>46160</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45709</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>45824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45751</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45820</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>45807</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45807</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45343</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45343</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>44608</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45477</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45318</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45450</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44621</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45618</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46197</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44596</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45159</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>46205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>46209</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46255</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>46258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44594</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45728</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44838</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45154</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>44672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44741</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>46268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46251</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>46177</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45534</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>46196</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45261</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45005</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>46184</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>46279</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>44860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45061</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45240</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44734</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45322</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45338</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45057</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45216</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45041</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45327</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45685</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44551</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45568</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45715</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45471</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45791</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45600</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45079</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>46064</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>46210</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>45314</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>44763</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>45729</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         <v>45348</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>46064</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>45315</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>46170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>46282</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>46252</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>45231</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>45322</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>44883</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45594</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>45922</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45005</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
         <v>46255</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
         <v>45098</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         <v>44685</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>44741</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45447</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5075,7 +5075,7 @@
         <v>44686</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>44858</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6143,7 +6143,7 @@
         <v>45698</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45405</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>44874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
         <v>44908</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6591,7 +6591,7 @@
         <v>44888</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>45342</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6810,7 +6810,7 @@
         <v>44890</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         <v>44838</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45398</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>45748</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45477</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45477</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45323</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>45945</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
         <v>45978</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44838</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>44838</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>46023</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>46023</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45947</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45113</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>45594</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>45608</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44911</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44879</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46038</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>46041</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>44915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45113</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45539</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>46064</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45804</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45919</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45574</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44896</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46064</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45477</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45940</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44970</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45583</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44672</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>44981</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>44852</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45315</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45005</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>46128</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46121</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45971</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45012</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45001</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45974</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45974</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45575</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>46064</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>46000</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>46000</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45770</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>45755</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44838</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44838</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44515</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45700</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>46146</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45406</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>44593</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45315</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>45093</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>45110</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>46160</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>46160</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>45709</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>45824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12285,7 +12285,7 @@
         <v>45751</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>45051</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>45775</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
         <v>45820</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>45231</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>45807</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12728,7 +12728,7 @@
         <v>45807</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>45947</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45945</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45343</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>45343</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>44608</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45477</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45318</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45450</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44621</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>45175</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13604,7 +13604,7 @@
         <v>45167</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45618</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44585</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45539</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46197</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45001</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44596</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14115,7 +14115,7 @@
         <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14188,7 +14188,7 @@
         <v>45159</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14261,7 +14261,7 @@
         <v>46205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>46209</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>45231</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>46255</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>46258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>46255</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>44594</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45728</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>44838</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>44685</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15069,7 +15069,7 @@
         <v>46258</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45154</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>44672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44741</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>46268</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>46251</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>46273</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44573</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>46191</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45273</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>46177</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46280</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>45191</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45190</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>45534</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>46196</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45261</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45005</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>46184</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46136</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>46279</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46265</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>44860</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>45061</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>45240</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>44734</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45322</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45526</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>45338</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>45057</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44984</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45532</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45216</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45372</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>45041</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45327</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45093</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18072,7 +18072,7 @@
         <v>45685</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18145,7 +18145,7 @@
         <v>45646</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18218,7 +18218,7 @@
         <v>45672</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18291,7 +18291,7 @@
         <v>45477</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44551</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45568</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45715</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45471</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>45791</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45645</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45728</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45600</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>44691</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19031,7 +19031,7 @@
         <v>45265</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>44509</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45680</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45539</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45114</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45558</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45688</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45791</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46127</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>46162</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>

--- a/Översikt HÖÖR.xlsx
+++ b/Översikt HÖÖR.xlsx
@@ -601,7 +601,7 @@
         <v>45251</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
         <v>44503</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>44911</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>44538</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>44713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>45387</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>45050</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
         <v>44503</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 24278-2023</t>
+          <t>A 8315-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45079</v>
+        <v>46064</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1575,9 +1575,122 @@
         <v>5</v>
       </c>
       <c r="U10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Småjungfrukam
+Spillkråka
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 24278-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45079</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>5</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Björktrast
 Rödvingetrast
@@ -1586,149 +1699,36 @@
 Trana</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24278-2023 artfynd.xlsx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24278-2023 karta.png", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24278-2023 georefererad karta.tif", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24278-2023 FSC-klagomål.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24278-2023 FSC-klagomål mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24278-2023 tillsynsbegäran.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24278-2023 tillsynsbegäran mail.docx", "A 24278-2023")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24278-2023 prioriterade fågelarter.docx", "A 24278-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 8315-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46064</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>4</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Småjungfrukam
-Spillkråka
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8315-2026 artfynd.xlsx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8315-2026 karta.png", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8315-2026 georefererad karta.tif", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8315-2026 FSC-klagomål.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8315-2026 FSC-klagomål mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8315-2026 tillsynsbegäran.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8315-2026 tillsynsbegäran mail.docx", "A 8315-2026")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8315-2026 prioriterade fågelarter.docx", "A 8315-2026")</f>
         <v/>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
         <v>44832</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30603-2026</t>
+          <t>A 2787-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1854,14 +1854,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46210</v>
+        <v>45314</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1898,21 +1898,129 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
       </c>
       <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Brunlångöra
+Nordfladdermus
+Större brunfladdermus
+Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 30603-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Kungsfiskare
@@ -1920,151 +2028,43 @@
 Fiskgjuse</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30603-2026 artfynd.xlsx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30603-2026 karta.png", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30603-2026 georefererad karta.tif", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30603-2026 FSC-klagomål.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30603-2026 FSC-klagomål mail.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30603-2026 tillsynsbegäran.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30603-2026 tillsynsbegäran mail.docx", "A 30603-2026")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE14">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 30603-2026 prioriterade fågelarter.docx", "A 30603-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 2787-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45314</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Brunlångöra
-Nordfladdermus
-Större brunfladdermus
-Vattenfladdermus</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2787-2024 artfynd.xlsx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2787-2024 karta.png", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2787-2024 georefererad karta.tif", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2787-2024 FSC-klagomål.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2787-2024 FSC-klagomål mail.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2787-2024 tillsynsbegäran.docx", "A 2787-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2787-2024 tillsynsbegäran mail.docx", "A 2787-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30645-2022</t>
+          <t>A 12111-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44763</v>
+        <v>45729</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2094,22 +2094,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2118,10 +2118,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2130,152 +2130,152 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Tofsvipa
+Tornseglare
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 30645-2022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44763</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Ask
 Murgröna
 Nattviol</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 30645-2022 artfynd.xlsx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 30645-2022 karta.png", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 30645-2022 georefererad karta.tif", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 30645-2022 FSC-klagomål.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 30645-2022 FSC-klagomål mail.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 30645-2022 tillsynsbegäran.docx", "A 30645-2022")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 30645-2022 tillsynsbegäran mail.docx", "A 30645-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 12111-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45729</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Tofsvipa
-Tornseglare
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 12111-2025 artfynd.xlsx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 12111-2025 karta.png", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 12111-2025 georefererad karta.tif", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 12111-2025 FSC-klagomål.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 12111-2025 FSC-klagomål mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 12111-2025 tillsynsbegäran.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 12111-2025 tillsynsbegäran mail.docx", "A 12111-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 12111-2025 prioriterade fågelarter.docx", "A 12111-2025")</f>
         <v/>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
         <v>45348</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>44711</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>45194</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>44503</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>44612</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8329-2026</t>
+          <t>A 2942-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46064</v>
+        <v>45315</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>11.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2894,153 +2894,153 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
+          <t>Skogsbräsma
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 8329-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>Grönsångare
 Spillkråka</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 8329-2026 artfynd.xlsx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 8329-2026 karta.png", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 8329-2026 georefererad karta.tif", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 8329-2026 FSC-klagomål.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 8329-2026 FSC-klagomål mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 8329-2026 tillsynsbegäran.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 8329-2026 tillsynsbegäran mail.docx", "A 8329-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 8329-2026 prioriterade fågelarter.docx", "A 8329-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 2942-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45315</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsbräsma
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 2942-2024 artfynd.xlsx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 2942-2024 karta.png", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 2942-2024 georefererad karta.tif", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 2942-2024 FSC-klagomål.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 2942-2024 FSC-klagomål mail.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 2942-2024 tillsynsbegäran.docx", "A 2942-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 2942-2024 tillsynsbegäran mail.docx", "A 2942-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 24597-2026</t>
+          <t>A 38317-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46170</v>
+        <v>46282</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3097,159 +3097,159 @@
         <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>2</v>
       </c>
       <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra</t>
+        </is>
+      </c>
+      <c r="W24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="X24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 24597-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>HÖÖR</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" t="n">
         <v>4</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>4</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 24597-2026 artfynd.xlsx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 24597-2026 karta.png", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 24597-2026 georefererad karta.tif", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 24597-2026 FSC-klagomål.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 24597-2026 FSC-klagomål mail.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 24597-2026 tillsynsbegäran.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 24597-2026 tillsynsbegäran mail.docx", "A 24597-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1267/fåglar/A 24597-2026 prioriterade fågelarter.docx", "A 24597-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 38317-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>HÖÖR</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 38317-2026 artfynd.xlsx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 38317-2026 karta.png", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 38317-2026 georefererad karta.tif", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 38317-2026 FSC-klagomål.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 38317-2026 FSC-klagomål mail.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 38317-2026 tillsynsbegäran.docx", "A 38317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 38317-2026 tillsynsbegäran mail.docx", "A 38317-2026")</f>
         <v/>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
         <v>46252</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>44504</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>44860</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         <v>44690</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53956-2023</t>
+          <t>A 42053-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45231</v>
+        <v>45174</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3733,10 +3733,10 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3749,42 +3749,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3924-2024</t>
+          <t>A 27233-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45322</v>
+        <v>44741</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3826,10 +3826,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -3854,42 +3854,42 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vitnoppa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54753-2022</t>
+          <t>A 48926-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3903,10 +3903,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44883</v>
+        <v>45594</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3919,20 +3919,20 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.9</v>
+        <v>10.8</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -3943,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3955,46 +3955,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48926-2024</t>
+          <t>A 45550-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45594</v>
+        <v>45922</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>10.8</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
@@ -4068,38 +4068,38 @@
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 48926-2024 artfynd.xlsx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 48926-2024 karta.png", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 48926-2024 georefererad karta.tif", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 48926-2024 FSC-klagomål.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 48926-2024 FSC-klagomål mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 48926-2024 tillsynsbegäran.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 48926-2024 tillsynsbegäran mail.docx", "A 48926-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45550-2025</t>
+          <t>A 54753-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45922</v>
+        <v>44883</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4153,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4169,42 +4169,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 45550-2025 artfynd.xlsx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 54753-2022 artfynd.xlsx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 45550-2025 karta.png", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 54753-2022 karta.png", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 45550-2025 georefererad karta.tif", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 54753-2022 georefererad karta.tif", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 45550-2025 FSC-klagomål.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 54753-2022 FSC-klagomål.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 45550-2025 FSC-klagomål mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 54753-2022 FSC-klagomål mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 45550-2025 tillsynsbegäran.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 54753-2022 tillsynsbegäran.docx", "A 54753-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 45550-2025 tillsynsbegäran mail.docx", "A 45550-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 54753-2022 tillsynsbegäran mail.docx", "A 54753-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13429-2023</t>
+          <t>A 3924-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4218,10 +4218,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45005</v>
+        <v>45322</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4234,23 +4234,23 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
@@ -4258,10 +4258,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4270,39 +4270,39 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Vitnoppa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 3924-2024 artfynd.xlsx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 3924-2024 karta.png", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 3924-2024 georefererad karta.tif", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 3924-2024 FSC-klagomål.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 3924-2024 FSC-klagomål mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 3924-2024 tillsynsbegäran.docx", "A 3924-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 3924-2024 tillsynsbegäran mail.docx", "A 3924-2024")</f>
         <v/>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
         <v>45645</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34500-2026</t>
+          <t>A 27902-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46255</v>
+        <v>45098</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4449,23 +4449,23 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.1</v>
+        <v>10.3</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4489,42 +4489,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27902-2023</t>
+          <t>A 18348-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45098</v>
+        <v>44685</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4553,11 +4553,16 @@
           <t>HÖÖR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>10.3</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -4569,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4578,10 +4583,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4590,46 +4595,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Klotullört</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27902-2023 artfynd.xlsx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27902-2023 karta.png", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27902-2023 georefererad karta.tif", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27902-2023 FSC-klagomål.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27902-2023 FSC-klagomål mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27902-2023 tillsynsbegäran.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27902-2023 tillsynsbegäran mail.docx", "A 27902-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 18348-2022</t>
+          <t>A 13429-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4643,10 +4648,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44685</v>
+        <v>45005</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4658,19 +4663,14 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4700,46 +4700,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Klotullört</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 18348-2022 artfynd.xlsx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 13429-2023 artfynd.xlsx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 18348-2022 karta.png", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 13429-2023 karta.png", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 18348-2022 georefererad karta.tif", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 13429-2023 georefererad karta.tif", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 18348-2022 FSC-klagomål.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 13429-2023 FSC-klagomål.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 18348-2022 FSC-klagomål mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 13429-2023 FSC-klagomål mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 18348-2022 tillsynsbegäran.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 13429-2023 tillsynsbegäran.docx", "A 13429-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 18348-2022 tillsynsbegäran mail.docx", "A 18348-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 13429-2023 tillsynsbegäran mail.docx", "A 13429-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27233-2022</t>
+          <t>A 34500-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44741</v>
+        <v>46255</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.4</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4793,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -4805,46 +4805,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 27233-2022 artfynd.xlsx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 34500-2026 artfynd.xlsx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 27233-2022 karta.png", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 34500-2026 karta.png", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 27233-2022 georefererad karta.tif", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 34500-2026 georefererad karta.tif", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 27233-2022 FSC-klagomål.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 34500-2026 FSC-klagomål.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 27233-2022 FSC-klagomål mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 34500-2026 FSC-klagomål mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 27233-2022 tillsynsbegäran.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 34500-2026 tillsynsbegäran.docx", "A 34500-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 27233-2022 tillsynsbegäran mail.docx", "A 27233-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 34500-2026 tillsynsbegäran mail.docx", "A 34500-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 42053-2023</t>
+          <t>A 53956-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45174</v>
+        <v>45231</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4886,7 +4886,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4914,35 +4914,35 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 42053-2023 artfynd.xlsx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/A 53956-2023 artfynd.xlsx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 42053-2023 karta.png", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/A 53956-2023 karta.png", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 42053-2023 georefererad karta.tif", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/A 53956-2023 georefererad karta.tif", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 42053-2023 FSC-klagomål.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/A 53956-2023 FSC-klagomål.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 42053-2023 FSC-klagomål mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/A 53956-2023 FSC-klagomål mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 42053-2023 tillsynsbegäran.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/A 53956-2023 tillsynsbegäran.docx", "A 53956-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 42053-2023 tillsynsbegäran mail.docx", "A 42053-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/A 53956-2023 tillsynsbegäran mail.docx", "A 53956-2023")</f>
         <v/>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
         <v>45447</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 2339-2022</t>
+          <t>S 8915-2021</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44686</v>
+        <v>44504</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>20.3</v>
+        <v>37.2</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5112,10 +5112,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5124,46 +5124,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 8915-2021</t>
+          <t>S 5973-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44504</v>
+        <v>44858</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>37.2</v>
+        <v>15.5</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5229,46 +5229,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 8915-2021 artfynd.xlsx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 8915-2021 karta.png", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 8915-2021 georefererad karta.tif", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 8915-2021 FSC-klagomål.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 8915-2021 FSC-klagomål mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 8915-2021 tillsynsbegäran.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 8915-2021 tillsynsbegäran mail.docx", "S 8915-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 5973-2022</t>
+          <t>S 2339-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5282,10 +5282,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44858</v>
+        <v>44686</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5298,20 +5298,20 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5338,35 +5338,35 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 5973-2022 artfynd.xlsx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/artfynd/S 2339-2022 artfynd.xlsx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 5973-2022 karta.png", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor/S 2339-2022 karta.png", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 5973-2022 georefererad karta.tif", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/kartor_geotiff/S 2339-2022 georefererad karta.tif", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 5973-2022 FSC-klagomål.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomål/S 2339-2022 FSC-klagomål.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 5973-2022 FSC-klagomål mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/klagomålsmail/S 2339-2022 FSC-klagomål mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 5973-2022 tillsynsbegäran.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsyn/S 2339-2022 tillsynsbegäran.docx", "S 2339-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 5973-2022 tillsynsbegäran mail.docx", "S 5973-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1267/tillsynsmail/S 2339-2022 tillsynsbegäran mail.docx", "S 2339-2022")</f>
         <v/>
       </c>
     </row>
@@ -5390,7 +5390,7 @@
         <v>45688</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         <v>45729</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         <v>44882</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>44883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         <v>44538</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>44596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>44515</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6174-2025</t>
+          <t>A 3480-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45698</v>
+        <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6199,7 +6199,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15905-2024</t>
+          <t>A 10007-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6209,14 +6209,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45405</v>
+        <v>44621</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6272,7 +6272,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 54798-2023</t>
+          <t>A 37675-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6286,10 +6286,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45236</v>
+        <v>45159</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6345,7 +6345,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 25934-2022</t>
+          <t>A 16434-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6359,10 +6359,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44734</v>
+        <v>45751</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6374,13 +6374,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6423,7 +6418,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 53455-2022</t>
+          <t>A 31092-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6433,14 +6428,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44874</v>
+        <v>45113</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6453,7 +6448,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>7.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6496,7 +6491,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59702-2022</t>
+          <t>A 35801-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6510,10 +6505,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44908</v>
+        <v>45532</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6525,13 +6520,8 @@
           <t>HÖÖR</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6574,7 +6564,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56596-2022</t>
+          <t>A 16110-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6584,14 +6574,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44888</v>
+        <v>45406</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6604,7 +6594,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6647,7 +6637,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6760-2024</t>
+          <t>A 30087-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6661,10 +6651,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45342</v>
+        <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6677,7 +6667,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6720,7 +6710,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17723-2023</t>
+          <t>A 50250-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6734,10 +6724,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45037</v>
+        <v>45600</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6750,7 +6740,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6793,7 +6783,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 56231-2022</t>
+          <t>A 9466-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6807,10 +6797,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44890</v>
+        <v>45715</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+       